--- a/STL_Study_Tracker.xlsx
+++ b/STL_Study_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B37AE2-4461-4BCF-926B-F7AA4566685A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68E8AAF-4377-4E16-963B-65CD89A98B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="174">
   <si>
     <t>📘 C++ STL Study Tracker — March 27 to June 30, 2026</t>
   </si>
@@ -900,10 +900,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -911,13 +914,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="17" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1233,7 +1233,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:100" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="31"/>
@@ -1243,7 +1243,7 @@
       <c r="F1" s="31"/>
     </row>
     <row r="2" spans="1:100" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="34" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="31"/>
@@ -1257,46 +1257,46 @@
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="36" t="s">
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="36"/>
-      <c r="P3" s="36"/>
-      <c r="Q3" s="36"/>
-      <c r="R3" s="36"/>
-      <c r="S3" s="36"/>
-      <c r="T3" s="36"/>
-      <c r="U3" s="36"/>
-      <c r="V3" s="36"/>
-      <c r="W3" s="36"/>
-      <c r="X3" s="36"/>
-      <c r="Y3" s="36"/>
-      <c r="Z3" s="36"/>
-      <c r="AA3" s="36"/>
-      <c r="AB3" s="36"/>
-      <c r="AC3" s="36"/>
-      <c r="AD3" s="36"/>
-      <c r="AE3" s="36"/>
-      <c r="AF3" s="36"/>
-      <c r="AG3" s="36"/>
-      <c r="AH3" s="36"/>
-      <c r="AI3" s="36"/>
-      <c r="AJ3" s="36"/>
-      <c r="AK3" s="36"/>
-      <c r="AL3" s="36"/>
-      <c r="AM3" s="36"/>
-      <c r="AN3" s="32" t="s">
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
+      <c r="S3" s="37"/>
+      <c r="T3" s="37"/>
+      <c r="U3" s="37"/>
+      <c r="V3" s="37"/>
+      <c r="W3" s="37"/>
+      <c r="X3" s="37"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="37"/>
+      <c r="AA3" s="37"/>
+      <c r="AB3" s="37"/>
+      <c r="AC3" s="37"/>
+      <c r="AD3" s="37"/>
+      <c r="AE3" s="37"/>
+      <c r="AF3" s="37"/>
+      <c r="AG3" s="37"/>
+      <c r="AH3" s="37"/>
+      <c r="AI3" s="37"/>
+      <c r="AJ3" s="37"/>
+      <c r="AK3" s="37"/>
+      <c r="AL3" s="37"/>
+      <c r="AM3" s="37"/>
+      <c r="AN3" s="33" t="s">
         <v>4</v>
       </c>
       <c r="AO3" s="31"/>
@@ -1329,7 +1329,7 @@
       <c r="BP3" s="31"/>
       <c r="BQ3" s="31"/>
       <c r="BR3" s="31"/>
-      <c r="BS3" s="30" t="s">
+      <c r="BS3" s="32" t="s">
         <v>5</v>
       </c>
       <c r="BT3" s="31"/>
@@ -1683,7 +1683,9 @@
       <c r="F5" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="G5" s="10"/>
+      <c r="G5" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>

--- a/STL_Study_Tracker.xlsx
+++ b/STL_Study_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68E8AAF-4377-4E16-963B-65CD89A98B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FCCD8E-4B0C-45DC-A8B5-B21C4AE2F704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="174">
   <si>
     <t>📘 C++ STL Study Tracker — March 27 to June 30, 2026</t>
   </si>
@@ -1686,7 +1686,9 @@
       <c r="G5" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="H5" s="8"/>
+      <c r="H5" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>

--- a/STL_Study_Tracker.xlsx
+++ b/STL_Study_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FCCD8E-4B0C-45DC-A8B5-B21C4AE2F704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF612294-CF4C-41D4-A2E9-0C65C10D8172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="174">
   <si>
     <t>📘 C++ STL Study Tracker — March 27 to June 30, 2026</t>
   </si>
@@ -1689,7 +1689,9 @@
       <c r="H5" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="I5" s="8"/>
+      <c r="I5" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
@@ -1803,7 +1805,9 @@
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
+      <c r="I6" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>

--- a/STL_Study_Tracker.xlsx
+++ b/STL_Study_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF612294-CF4C-41D4-A2E9-0C65C10D8172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CD8E9E-8674-41E8-B80E-E22E528C389D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="174">
   <si>
     <t>📘 C++ STL Study Tracker — March 27 to June 30, 2026</t>
   </si>
@@ -1692,7 +1692,9 @@
       <c r="I5" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="J5" s="8"/>
+      <c r="J5" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
       <c r="M5" s="9"/>
@@ -1808,7 +1810,9 @@
       <c r="I6" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="J6" s="8"/>
+      <c r="J6" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
       <c r="M6" s="9"/>
@@ -1922,7 +1926,9 @@
       <c r="G7" s="10"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
+      <c r="J7" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
       <c r="M7" s="9"/>

--- a/STL_Study_Tracker.xlsx
+++ b/STL_Study_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3CD8E9E-8674-41E8-B80E-E22E528C389D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B361BF12-F124-40D9-B171-D3E1C1CEE6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="174">
   <si>
     <t>📘 C++ STL Study Tracker — March 27 to June 30, 2026</t>
   </si>
@@ -1695,7 +1695,9 @@
       <c r="J5" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="K5" s="8"/>
+      <c r="K5" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="L5" s="8"/>
       <c r="M5" s="9"/>
       <c r="N5" s="10"/>
@@ -1813,7 +1815,9 @@
       <c r="J6" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="K6" s="8"/>
+      <c r="K6" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="L6" s="8"/>
       <c r="M6" s="9"/>
       <c r="N6" s="10"/>
@@ -1929,7 +1933,9 @@
       <c r="J7" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="K7" s="8"/>
+      <c r="K7" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="L7" s="8"/>
       <c r="M7" s="9"/>
       <c r="N7" s="10"/>
@@ -2043,7 +2049,9 @@
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
+      <c r="K8" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="L8" s="8"/>
       <c r="M8" s="9"/>
       <c r="N8" s="10"/>

--- a/STL_Study_Tracker.xlsx
+++ b/STL_Study_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B361BF12-F124-40D9-B171-D3E1C1CEE6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC908DB-8CE5-4EAE-81C8-72512580D8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="174">
   <si>
     <t>📘 C++ STL Study Tracker — March 27 to June 30, 2026</t>
   </si>
@@ -1698,7 +1698,9 @@
       <c r="K5" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="L5" s="8"/>
+      <c r="L5" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="M5" s="9"/>
       <c r="N5" s="10"/>
       <c r="O5" s="8"/>
@@ -1818,7 +1820,9 @@
       <c r="K6" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="L6" s="8"/>
+      <c r="L6" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="M6" s="9"/>
       <c r="N6" s="10"/>
       <c r="O6" s="8"/>
@@ -1936,7 +1940,9 @@
       <c r="K7" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="L7" s="8"/>
+      <c r="L7" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="M7" s="9"/>
       <c r="N7" s="10"/>
       <c r="O7" s="8"/>
@@ -2052,7 +2058,9 @@
       <c r="K8" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="L8" s="8"/>
+      <c r="L8" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="M8" s="9"/>
       <c r="N8" s="10"/>
       <c r="O8" s="8"/>
@@ -2166,7 +2174,9 @@
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
+      <c r="L9" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="M9" s="9"/>
       <c r="N9" s="10"/>
       <c r="O9" s="8"/>

--- a/STL_Study_Tracker.xlsx
+++ b/STL_Study_Tracker.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="174">
   <si>
     <t>STL Topics — Detailed Breakdown</t>
   </si>
@@ -544,7 +544,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -556,6 +556,12 @@
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -755,154 +761,154 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="10" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="8" applyFont="1" fillId="12" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="12" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="14" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="14" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1984,7 +1990,9 @@
       <c r="Q5" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="R5" s="33"/>
+      <c r="R5" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="S5" s="33"/>
       <c r="T5" s="34"/>
       <c r="U5" s="35"/>
@@ -2116,7 +2124,9 @@
       <c r="Q6" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="R6" s="33"/>
+      <c r="R6" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="S6" s="33"/>
       <c r="T6" s="34"/>
       <c r="U6" s="35"/>
@@ -2246,7 +2256,9 @@
       <c r="Q7" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="R7" s="33"/>
+      <c r="R7" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="S7" s="33"/>
       <c r="T7" s="34"/>
       <c r="U7" s="35"/>
@@ -2374,7 +2386,9 @@
       <c r="Q8" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="R8" s="33"/>
+      <c r="R8" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="S8" s="33"/>
       <c r="T8" s="34"/>
       <c r="U8" s="35"/>
@@ -2500,7 +2514,9 @@
       <c r="Q9" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="R9" s="33"/>
+      <c r="R9" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="S9" s="33"/>
       <c r="T9" s="34"/>
       <c r="U9" s="35"/>
@@ -2624,7 +2640,9 @@
       <c r="Q10" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="R10" s="33"/>
+      <c r="R10" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="S10" s="33"/>
       <c r="T10" s="34"/>
       <c r="U10" s="35"/>
@@ -2746,7 +2764,9 @@
       <c r="Q11" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="R11" s="33"/>
+      <c r="R11" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="S11" s="33"/>
       <c r="T11" s="34"/>
       <c r="U11" s="35"/>
@@ -2866,7 +2886,9 @@
       <c r="Q12" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="R12" s="33"/>
+      <c r="R12" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="S12" s="33"/>
       <c r="T12" s="34"/>
       <c r="U12" s="35"/>
@@ -2984,7 +3006,9 @@
       <c r="Q13" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="R13" s="33"/>
+      <c r="R13" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="S13" s="33"/>
       <c r="T13" s="34"/>
       <c r="U13" s="35"/>
@@ -3100,7 +3124,9 @@
       <c r="Q14" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="R14" s="33"/>
+      <c r="R14" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="S14" s="33"/>
       <c r="T14" s="34"/>
       <c r="U14" s="35"/>
@@ -3214,7 +3240,9 @@
       <c r="O15" s="33"/>
       <c r="P15" s="33"/>
       <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
+      <c r="R15" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="S15" s="33"/>
       <c r="T15" s="34"/>
       <c r="U15" s="35"/>
@@ -3868,7 +3896,7 @@
       <c r="CU20" s="33"/>
       <c r="CV20" s="33"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="44">
         <v>17</v>
       </c>
@@ -3982,7 +4010,7 @@
       <c r="CU21" s="33"/>
       <c r="CV21" s="33"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="44">
         <v>18</v>
       </c>
@@ -4096,7 +4124,7 @@
       <c r="CU22" s="33"/>
       <c r="CV22" s="33"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="44">
         <v>19</v>
       </c>
@@ -4210,7 +4238,7 @@
       <c r="CU23" s="33"/>
       <c r="CV23" s="33"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="20.25">
       <c r="A24" s="48">
         <v>20</v>
       </c>

--- a/STL_Study_Tracker.xlsx
+++ b/STL_Study_Tracker.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="174">
   <si>
     <t>STL Topics — Detailed Breakdown</t>
   </si>
@@ -544,7 +544,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -561,7 +561,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -569,12 +569,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFffffff"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -776,31 +770,31 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -812,19 +806,19 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
@@ -839,76 +833,76 @@
     <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="11" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="12" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="8" applyFont="1" fillId="12" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="14" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="13" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="14" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="10" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1993,7 +1987,9 @@
       <c r="R5" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="S5" s="33"/>
+      <c r="S5" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="T5" s="34"/>
       <c r="U5" s="35"/>
       <c r="V5" s="33"/>
@@ -2127,7 +2123,9 @@
       <c r="R6" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="S6" s="33"/>
+      <c r="S6" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="T6" s="34"/>
       <c r="U6" s="35"/>
       <c r="V6" s="33"/>
@@ -2259,7 +2257,9 @@
       <c r="R7" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="S7" s="33"/>
+      <c r="S7" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="T7" s="34"/>
       <c r="U7" s="35"/>
       <c r="V7" s="33"/>
@@ -2389,7 +2389,9 @@
       <c r="R8" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="S8" s="33"/>
+      <c r="S8" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="T8" s="34"/>
       <c r="U8" s="35"/>
       <c r="V8" s="33"/>
@@ -2517,7 +2519,9 @@
       <c r="R9" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="S9" s="33"/>
+      <c r="S9" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="T9" s="34"/>
       <c r="U9" s="35"/>
       <c r="V9" s="33"/>
@@ -2643,7 +2647,9 @@
       <c r="R10" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="S10" s="33"/>
+      <c r="S10" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="T10" s="34"/>
       <c r="U10" s="35"/>
       <c r="V10" s="33"/>
@@ -2767,7 +2773,9 @@
       <c r="R11" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="S11" s="33"/>
+      <c r="S11" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="T11" s="34"/>
       <c r="U11" s="35"/>
       <c r="V11" s="33"/>
@@ -2889,7 +2897,9 @@
       <c r="R12" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="S12" s="33"/>
+      <c r="S12" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="T12" s="34"/>
       <c r="U12" s="35"/>
       <c r="V12" s="33"/>
@@ -3009,7 +3019,9 @@
       <c r="R13" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="S13" s="33"/>
+      <c r="S13" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="T13" s="34"/>
       <c r="U13" s="35"/>
       <c r="V13" s="33"/>
@@ -3127,7 +3139,9 @@
       <c r="R14" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="S14" s="33"/>
+      <c r="S14" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="T14" s="34"/>
       <c r="U14" s="35"/>
       <c r="V14" s="33"/>
@@ -3243,7 +3257,9 @@
       <c r="R15" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="S15" s="33"/>
+      <c r="S15" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="T15" s="34"/>
       <c r="U15" s="35"/>
       <c r="V15" s="33"/>
@@ -3357,7 +3373,9 @@
       <c r="P16" s="33"/>
       <c r="Q16" s="33"/>
       <c r="R16" s="33"/>
-      <c r="S16" s="33"/>
+      <c r="S16" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="T16" s="34"/>
       <c r="U16" s="35"/>
       <c r="V16" s="33"/>

--- a/STL_Study_Tracker.xlsx
+++ b/STL_Study_Tracker.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="174">
   <si>
     <t>STL Topics — Detailed Breakdown</t>
   </si>
@@ -677,12 +677,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFf2f2f2"/>
+        <fgColor rgb="FFe8e8e8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8e8e8"/>
+        <fgColor rgb="FFf2f2f2"/>
       </patternFill>
     </fill>
   </fills>
@@ -1990,85 +1990,87 @@
       <c r="S5" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="T5" s="34"/>
-      <c r="U5" s="35"/>
+      <c r="T5" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="U5" s="34"/>
       <c r="V5" s="33"/>
       <c r="W5" s="33"/>
       <c r="X5" s="33"/>
       <c r="Y5" s="33"/>
       <c r="Z5" s="33"/>
-      <c r="AA5" s="34"/>
-      <c r="AB5" s="35"/>
+      <c r="AA5" s="35"/>
+      <c r="AB5" s="34"/>
       <c r="AC5" s="33"/>
       <c r="AD5" s="33"/>
       <c r="AE5" s="33"/>
       <c r="AF5" s="33"/>
       <c r="AG5" s="33"/>
-      <c r="AH5" s="34"/>
-      <c r="AI5" s="35"/>
+      <c r="AH5" s="35"/>
+      <c r="AI5" s="34"/>
       <c r="AJ5" s="33"/>
       <c r="AK5" s="33"/>
       <c r="AL5" s="33"/>
       <c r="AM5" s="33"/>
       <c r="AN5" s="33"/>
-      <c r="AO5" s="34"/>
-      <c r="AP5" s="35"/>
+      <c r="AO5" s="35"/>
+      <c r="AP5" s="34"/>
       <c r="AQ5" s="33"/>
       <c r="AR5" s="33"/>
       <c r="AS5" s="33"/>
       <c r="AT5" s="33"/>
       <c r="AU5" s="33"/>
-      <c r="AV5" s="34"/>
-      <c r="AW5" s="35"/>
+      <c r="AV5" s="35"/>
+      <c r="AW5" s="34"/>
       <c r="AX5" s="33"/>
       <c r="AY5" s="33"/>
       <c r="AZ5" s="33"/>
       <c r="BA5" s="33"/>
       <c r="BB5" s="33"/>
-      <c r="BC5" s="34"/>
-      <c r="BD5" s="35"/>
+      <c r="BC5" s="35"/>
+      <c r="BD5" s="34"/>
       <c r="BE5" s="33"/>
       <c r="BF5" s="33"/>
       <c r="BG5" s="33"/>
       <c r="BH5" s="33"/>
       <c r="BI5" s="33"/>
-      <c r="BJ5" s="34"/>
-      <c r="BK5" s="35"/>
+      <c r="BJ5" s="35"/>
+      <c r="BK5" s="34"/>
       <c r="BL5" s="33"/>
       <c r="BM5" s="33"/>
       <c r="BN5" s="33"/>
       <c r="BO5" s="33"/>
       <c r="BP5" s="33"/>
-      <c r="BQ5" s="34"/>
-      <c r="BR5" s="35"/>
+      <c r="BQ5" s="35"/>
+      <c r="BR5" s="34"/>
       <c r="BS5" s="33"/>
       <c r="BT5" s="33"/>
       <c r="BU5" s="33"/>
       <c r="BV5" s="33"/>
       <c r="BW5" s="33"/>
-      <c r="BX5" s="34"/>
-      <c r="BY5" s="35"/>
+      <c r="BX5" s="35"/>
+      <c r="BY5" s="34"/>
       <c r="BZ5" s="33"/>
       <c r="CA5" s="33"/>
       <c r="CB5" s="33"/>
       <c r="CC5" s="33"/>
       <c r="CD5" s="33"/>
-      <c r="CE5" s="34"/>
-      <c r="CF5" s="35"/>
+      <c r="CE5" s="35"/>
+      <c r="CF5" s="34"/>
       <c r="CG5" s="33"/>
       <c r="CH5" s="33"/>
       <c r="CI5" s="33"/>
       <c r="CJ5" s="33"/>
       <c r="CK5" s="33"/>
-      <c r="CL5" s="34"/>
-      <c r="CM5" s="35"/>
+      <c r="CL5" s="35"/>
+      <c r="CM5" s="34"/>
       <c r="CN5" s="33"/>
       <c r="CO5" s="33"/>
       <c r="CP5" s="33"/>
       <c r="CQ5" s="33"/>
       <c r="CR5" s="33"/>
-      <c r="CS5" s="34"/>
-      <c r="CT5" s="35"/>
+      <c r="CS5" s="35"/>
+      <c r="CT5" s="34"/>
       <c r="CU5" s="33"/>
       <c r="CV5" s="33"/>
     </row>
@@ -2091,7 +2093,7 @@
       <c r="F6" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G6" s="35"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="33"/>
       <c r="I6" s="33" t="s">
         <v>173</v>
@@ -2126,85 +2128,87 @@
       <c r="S6" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="T6" s="34"/>
-      <c r="U6" s="35"/>
+      <c r="T6" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="U6" s="34"/>
       <c r="V6" s="33"/>
       <c r="W6" s="33"/>
       <c r="X6" s="33"/>
       <c r="Y6" s="33"/>
       <c r="Z6" s="33"/>
-      <c r="AA6" s="34"/>
-      <c r="AB6" s="35"/>
+      <c r="AA6" s="35"/>
+      <c r="AB6" s="34"/>
       <c r="AC6" s="33"/>
       <c r="AD6" s="33"/>
       <c r="AE6" s="33"/>
       <c r="AF6" s="33"/>
       <c r="AG6" s="33"/>
-      <c r="AH6" s="34"/>
-      <c r="AI6" s="35"/>
+      <c r="AH6" s="35"/>
+      <c r="AI6" s="34"/>
       <c r="AJ6" s="33"/>
       <c r="AK6" s="33"/>
       <c r="AL6" s="33"/>
       <c r="AM6" s="33"/>
       <c r="AN6" s="33"/>
-      <c r="AO6" s="34"/>
-      <c r="AP6" s="35"/>
+      <c r="AO6" s="35"/>
+      <c r="AP6" s="34"/>
       <c r="AQ6" s="33"/>
       <c r="AR6" s="33"/>
       <c r="AS6" s="33"/>
       <c r="AT6" s="33"/>
       <c r="AU6" s="33"/>
-      <c r="AV6" s="34"/>
-      <c r="AW6" s="35"/>
+      <c r="AV6" s="35"/>
+      <c r="AW6" s="34"/>
       <c r="AX6" s="33"/>
       <c r="AY6" s="33"/>
       <c r="AZ6" s="33"/>
       <c r="BA6" s="33"/>
       <c r="BB6" s="33"/>
-      <c r="BC6" s="34"/>
-      <c r="BD6" s="35"/>
+      <c r="BC6" s="35"/>
+      <c r="BD6" s="34"/>
       <c r="BE6" s="33"/>
       <c r="BF6" s="33"/>
       <c r="BG6" s="33"/>
       <c r="BH6" s="33"/>
       <c r="BI6" s="33"/>
-      <c r="BJ6" s="34"/>
-      <c r="BK6" s="35"/>
+      <c r="BJ6" s="35"/>
+      <c r="BK6" s="34"/>
       <c r="BL6" s="33"/>
       <c r="BM6" s="33"/>
       <c r="BN6" s="33"/>
       <c r="BO6" s="33"/>
       <c r="BP6" s="33"/>
-      <c r="BQ6" s="34"/>
-      <c r="BR6" s="35"/>
+      <c r="BQ6" s="35"/>
+      <c r="BR6" s="34"/>
       <c r="BS6" s="33"/>
       <c r="BT6" s="33"/>
       <c r="BU6" s="33"/>
       <c r="BV6" s="33"/>
       <c r="BW6" s="33"/>
-      <c r="BX6" s="34"/>
-      <c r="BY6" s="35"/>
+      <c r="BX6" s="35"/>
+      <c r="BY6" s="34"/>
       <c r="BZ6" s="33"/>
       <c r="CA6" s="33"/>
       <c r="CB6" s="33"/>
       <c r="CC6" s="33"/>
       <c r="CD6" s="33"/>
-      <c r="CE6" s="34"/>
-      <c r="CF6" s="35"/>
+      <c r="CE6" s="35"/>
+      <c r="CF6" s="34"/>
       <c r="CG6" s="33"/>
       <c r="CH6" s="33"/>
       <c r="CI6" s="33"/>
       <c r="CJ6" s="33"/>
       <c r="CK6" s="33"/>
-      <c r="CL6" s="34"/>
-      <c r="CM6" s="35"/>
+      <c r="CL6" s="35"/>
+      <c r="CM6" s="34"/>
       <c r="CN6" s="33"/>
       <c r="CO6" s="33"/>
       <c r="CP6" s="33"/>
       <c r="CQ6" s="33"/>
       <c r="CR6" s="33"/>
-      <c r="CS6" s="34"/>
-      <c r="CT6" s="35"/>
+      <c r="CS6" s="35"/>
+      <c r="CT6" s="34"/>
       <c r="CU6" s="33"/>
       <c r="CV6" s="33"/>
     </row>
@@ -2227,7 +2231,7 @@
       <c r="F7" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
       <c r="J7" s="33" t="s">
@@ -2260,85 +2264,87 @@
       <c r="S7" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="T7" s="34"/>
-      <c r="U7" s="35"/>
+      <c r="T7" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="U7" s="34"/>
       <c r="V7" s="33"/>
       <c r="W7" s="33"/>
       <c r="X7" s="33"/>
       <c r="Y7" s="33"/>
       <c r="Z7" s="33"/>
-      <c r="AA7" s="34"/>
-      <c r="AB7" s="35"/>
+      <c r="AA7" s="35"/>
+      <c r="AB7" s="34"/>
       <c r="AC7" s="33"/>
       <c r="AD7" s="33"/>
       <c r="AE7" s="33"/>
       <c r="AF7" s="33"/>
       <c r="AG7" s="33"/>
-      <c r="AH7" s="34"/>
-      <c r="AI7" s="35"/>
+      <c r="AH7" s="35"/>
+      <c r="AI7" s="34"/>
       <c r="AJ7" s="33"/>
       <c r="AK7" s="33"/>
       <c r="AL7" s="33"/>
       <c r="AM7" s="33"/>
       <c r="AN7" s="33"/>
-      <c r="AO7" s="34"/>
-      <c r="AP7" s="35"/>
+      <c r="AO7" s="35"/>
+      <c r="AP7" s="34"/>
       <c r="AQ7" s="33"/>
       <c r="AR7" s="33"/>
       <c r="AS7" s="33"/>
       <c r="AT7" s="33"/>
       <c r="AU7" s="33"/>
-      <c r="AV7" s="34"/>
-      <c r="AW7" s="35"/>
+      <c r="AV7" s="35"/>
+      <c r="AW7" s="34"/>
       <c r="AX7" s="33"/>
       <c r="AY7" s="33"/>
       <c r="AZ7" s="33"/>
       <c r="BA7" s="33"/>
       <c r="BB7" s="33"/>
-      <c r="BC7" s="34"/>
-      <c r="BD7" s="35"/>
+      <c r="BC7" s="35"/>
+      <c r="BD7" s="34"/>
       <c r="BE7" s="33"/>
       <c r="BF7" s="33"/>
       <c r="BG7" s="33"/>
       <c r="BH7" s="33"/>
       <c r="BI7" s="33"/>
-      <c r="BJ7" s="34"/>
-      <c r="BK7" s="35"/>
+      <c r="BJ7" s="35"/>
+      <c r="BK7" s="34"/>
       <c r="BL7" s="33"/>
       <c r="BM7" s="33"/>
       <c r="BN7" s="33"/>
       <c r="BO7" s="33"/>
       <c r="BP7" s="33"/>
-      <c r="BQ7" s="34"/>
-      <c r="BR7" s="35"/>
+      <c r="BQ7" s="35"/>
+      <c r="BR7" s="34"/>
       <c r="BS7" s="33"/>
       <c r="BT7" s="33"/>
       <c r="BU7" s="33"/>
       <c r="BV7" s="33"/>
       <c r="BW7" s="33"/>
-      <c r="BX7" s="34"/>
-      <c r="BY7" s="35"/>
+      <c r="BX7" s="35"/>
+      <c r="BY7" s="34"/>
       <c r="BZ7" s="33"/>
       <c r="CA7" s="33"/>
       <c r="CB7" s="33"/>
       <c r="CC7" s="33"/>
       <c r="CD7" s="33"/>
-      <c r="CE7" s="34"/>
-      <c r="CF7" s="35"/>
+      <c r="CE7" s="35"/>
+      <c r="CF7" s="34"/>
       <c r="CG7" s="33"/>
       <c r="CH7" s="33"/>
       <c r="CI7" s="33"/>
       <c r="CJ7" s="33"/>
       <c r="CK7" s="33"/>
-      <c r="CL7" s="34"/>
-      <c r="CM7" s="35"/>
+      <c r="CL7" s="35"/>
+      <c r="CM7" s="34"/>
       <c r="CN7" s="33"/>
       <c r="CO7" s="33"/>
       <c r="CP7" s="33"/>
       <c r="CQ7" s="33"/>
       <c r="CR7" s="33"/>
-      <c r="CS7" s="34"/>
-      <c r="CT7" s="35"/>
+      <c r="CS7" s="35"/>
+      <c r="CT7" s="34"/>
       <c r="CU7" s="33"/>
       <c r="CV7" s="33"/>
     </row>
@@ -2361,7 +2367,7 @@
       <c r="F8" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G8" s="35"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
       <c r="J8" s="33"/>
@@ -2392,85 +2398,87 @@
       <c r="S8" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="T8" s="34"/>
-      <c r="U8" s="35"/>
+      <c r="T8" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="U8" s="34"/>
       <c r="V8" s="33"/>
       <c r="W8" s="33"/>
       <c r="X8" s="33"/>
       <c r="Y8" s="33"/>
       <c r="Z8" s="33"/>
-      <c r="AA8" s="34"/>
-      <c r="AB8" s="35"/>
+      <c r="AA8" s="35"/>
+      <c r="AB8" s="34"/>
       <c r="AC8" s="33"/>
       <c r="AD8" s="33"/>
       <c r="AE8" s="33"/>
       <c r="AF8" s="33"/>
       <c r="AG8" s="33"/>
-      <c r="AH8" s="34"/>
-      <c r="AI8" s="35"/>
+      <c r="AH8" s="35"/>
+      <c r="AI8" s="34"/>
       <c r="AJ8" s="33"/>
       <c r="AK8" s="33"/>
       <c r="AL8" s="33"/>
       <c r="AM8" s="33"/>
       <c r="AN8" s="33"/>
-      <c r="AO8" s="34"/>
-      <c r="AP8" s="35"/>
+      <c r="AO8" s="35"/>
+      <c r="AP8" s="34"/>
       <c r="AQ8" s="33"/>
       <c r="AR8" s="33"/>
       <c r="AS8" s="33"/>
       <c r="AT8" s="33"/>
       <c r="AU8" s="33"/>
-      <c r="AV8" s="34"/>
-      <c r="AW8" s="35"/>
+      <c r="AV8" s="35"/>
+      <c r="AW8" s="34"/>
       <c r="AX8" s="33"/>
       <c r="AY8" s="33"/>
       <c r="AZ8" s="33"/>
       <c r="BA8" s="33"/>
       <c r="BB8" s="33"/>
-      <c r="BC8" s="34"/>
-      <c r="BD8" s="35"/>
+      <c r="BC8" s="35"/>
+      <c r="BD8" s="34"/>
       <c r="BE8" s="33"/>
       <c r="BF8" s="33"/>
       <c r="BG8" s="33"/>
       <c r="BH8" s="33"/>
       <c r="BI8" s="33"/>
-      <c r="BJ8" s="34"/>
-      <c r="BK8" s="35"/>
+      <c r="BJ8" s="35"/>
+      <c r="BK8" s="34"/>
       <c r="BL8" s="33"/>
       <c r="BM8" s="33"/>
       <c r="BN8" s="33"/>
       <c r="BO8" s="33"/>
       <c r="BP8" s="33"/>
-      <c r="BQ8" s="34"/>
-      <c r="BR8" s="35"/>
+      <c r="BQ8" s="35"/>
+      <c r="BR8" s="34"/>
       <c r="BS8" s="33"/>
       <c r="BT8" s="33"/>
       <c r="BU8" s="33"/>
       <c r="BV8" s="33"/>
       <c r="BW8" s="33"/>
-      <c r="BX8" s="34"/>
-      <c r="BY8" s="35"/>
+      <c r="BX8" s="35"/>
+      <c r="BY8" s="34"/>
       <c r="BZ8" s="33"/>
       <c r="CA8" s="33"/>
       <c r="CB8" s="33"/>
       <c r="CC8" s="33"/>
       <c r="CD8" s="33"/>
-      <c r="CE8" s="34"/>
-      <c r="CF8" s="35"/>
+      <c r="CE8" s="35"/>
+      <c r="CF8" s="34"/>
       <c r="CG8" s="33"/>
       <c r="CH8" s="33"/>
       <c r="CI8" s="33"/>
       <c r="CJ8" s="33"/>
       <c r="CK8" s="33"/>
-      <c r="CL8" s="34"/>
-      <c r="CM8" s="35"/>
+      <c r="CL8" s="35"/>
+      <c r="CM8" s="34"/>
       <c r="CN8" s="33"/>
       <c r="CO8" s="33"/>
       <c r="CP8" s="33"/>
       <c r="CQ8" s="33"/>
       <c r="CR8" s="33"/>
-      <c r="CS8" s="34"/>
-      <c r="CT8" s="35"/>
+      <c r="CS8" s="35"/>
+      <c r="CT8" s="34"/>
       <c r="CU8" s="33"/>
       <c r="CV8" s="33"/>
     </row>
@@ -2493,7 +2501,7 @@
       <c r="F9" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
       <c r="J9" s="33"/>
@@ -2522,85 +2530,87 @@
       <c r="S9" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="T9" s="34"/>
-      <c r="U9" s="35"/>
+      <c r="T9" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="U9" s="34"/>
       <c r="V9" s="33"/>
       <c r="W9" s="33"/>
       <c r="X9" s="33"/>
       <c r="Y9" s="33"/>
       <c r="Z9" s="33"/>
-      <c r="AA9" s="34"/>
-      <c r="AB9" s="35"/>
+      <c r="AA9" s="35"/>
+      <c r="AB9" s="34"/>
       <c r="AC9" s="33"/>
       <c r="AD9" s="33"/>
       <c r="AE9" s="33"/>
       <c r="AF9" s="33"/>
       <c r="AG9" s="33"/>
-      <c r="AH9" s="34"/>
-      <c r="AI9" s="35"/>
+      <c r="AH9" s="35"/>
+      <c r="AI9" s="34"/>
       <c r="AJ9" s="33"/>
       <c r="AK9" s="33"/>
       <c r="AL9" s="33"/>
       <c r="AM9" s="33"/>
       <c r="AN9" s="33"/>
-      <c r="AO9" s="34"/>
-      <c r="AP9" s="35"/>
+      <c r="AO9" s="35"/>
+      <c r="AP9" s="34"/>
       <c r="AQ9" s="33"/>
       <c r="AR9" s="33"/>
       <c r="AS9" s="33"/>
       <c r="AT9" s="33"/>
       <c r="AU9" s="33"/>
-      <c r="AV9" s="34"/>
-      <c r="AW9" s="35"/>
+      <c r="AV9" s="35"/>
+      <c r="AW9" s="34"/>
       <c r="AX9" s="33"/>
       <c r="AY9" s="33"/>
       <c r="AZ9" s="33"/>
       <c r="BA9" s="33"/>
       <c r="BB9" s="33"/>
-      <c r="BC9" s="34"/>
-      <c r="BD9" s="35"/>
+      <c r="BC9" s="35"/>
+      <c r="BD9" s="34"/>
       <c r="BE9" s="33"/>
       <c r="BF9" s="33"/>
       <c r="BG9" s="33"/>
       <c r="BH9" s="33"/>
       <c r="BI9" s="33"/>
-      <c r="BJ9" s="34"/>
-      <c r="BK9" s="35"/>
+      <c r="BJ9" s="35"/>
+      <c r="BK9" s="34"/>
       <c r="BL9" s="33"/>
       <c r="BM9" s="33"/>
       <c r="BN9" s="33"/>
       <c r="BO9" s="33"/>
       <c r="BP9" s="33"/>
-      <c r="BQ9" s="34"/>
-      <c r="BR9" s="35"/>
+      <c r="BQ9" s="35"/>
+      <c r="BR9" s="34"/>
       <c r="BS9" s="33"/>
       <c r="BT9" s="33"/>
       <c r="BU9" s="33"/>
       <c r="BV9" s="33"/>
       <c r="BW9" s="33"/>
-      <c r="BX9" s="34"/>
-      <c r="BY9" s="35"/>
+      <c r="BX9" s="35"/>
+      <c r="BY9" s="34"/>
       <c r="BZ9" s="33"/>
       <c r="CA9" s="33"/>
       <c r="CB9" s="33"/>
       <c r="CC9" s="33"/>
       <c r="CD9" s="33"/>
-      <c r="CE9" s="34"/>
-      <c r="CF9" s="35"/>
+      <c r="CE9" s="35"/>
+      <c r="CF9" s="34"/>
       <c r="CG9" s="33"/>
       <c r="CH9" s="33"/>
       <c r="CI9" s="33"/>
       <c r="CJ9" s="33"/>
       <c r="CK9" s="33"/>
-      <c r="CL9" s="34"/>
-      <c r="CM9" s="35"/>
+      <c r="CL9" s="35"/>
+      <c r="CM9" s="34"/>
       <c r="CN9" s="33"/>
       <c r="CO9" s="33"/>
       <c r="CP9" s="33"/>
       <c r="CQ9" s="33"/>
       <c r="CR9" s="33"/>
-      <c r="CS9" s="34"/>
-      <c r="CT9" s="35"/>
+      <c r="CS9" s="35"/>
+      <c r="CT9" s="34"/>
       <c r="CU9" s="33"/>
       <c r="CV9" s="33"/>
     </row>
@@ -2623,7 +2633,7 @@
       <c r="F10" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G10" s="35"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="33"/>
       <c r="I10" s="33"/>
       <c r="J10" s="33"/>
@@ -2650,85 +2660,87 @@
       <c r="S10" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="T10" s="34"/>
-      <c r="U10" s="35"/>
+      <c r="T10" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="U10" s="34"/>
       <c r="V10" s="33"/>
       <c r="W10" s="33"/>
       <c r="X10" s="33"/>
       <c r="Y10" s="33"/>
       <c r="Z10" s="33"/>
-      <c r="AA10" s="34"/>
-      <c r="AB10" s="35"/>
+      <c r="AA10" s="35"/>
+      <c r="AB10" s="34"/>
       <c r="AC10" s="33"/>
       <c r="AD10" s="33"/>
       <c r="AE10" s="33"/>
       <c r="AF10" s="33"/>
       <c r="AG10" s="33"/>
-      <c r="AH10" s="34"/>
-      <c r="AI10" s="35"/>
+      <c r="AH10" s="35"/>
+      <c r="AI10" s="34"/>
       <c r="AJ10" s="33"/>
       <c r="AK10" s="33"/>
       <c r="AL10" s="33"/>
       <c r="AM10" s="33"/>
       <c r="AN10" s="33"/>
-      <c r="AO10" s="34"/>
-      <c r="AP10" s="35"/>
+      <c r="AO10" s="35"/>
+      <c r="AP10" s="34"/>
       <c r="AQ10" s="33"/>
       <c r="AR10" s="33"/>
       <c r="AS10" s="33"/>
       <c r="AT10" s="33"/>
       <c r="AU10" s="33"/>
-      <c r="AV10" s="34"/>
-      <c r="AW10" s="35"/>
+      <c r="AV10" s="35"/>
+      <c r="AW10" s="34"/>
       <c r="AX10" s="33"/>
       <c r="AY10" s="33"/>
       <c r="AZ10" s="33"/>
       <c r="BA10" s="33"/>
       <c r="BB10" s="33"/>
-      <c r="BC10" s="34"/>
-      <c r="BD10" s="35"/>
+      <c r="BC10" s="35"/>
+      <c r="BD10" s="34"/>
       <c r="BE10" s="33"/>
       <c r="BF10" s="33"/>
       <c r="BG10" s="33"/>
       <c r="BH10" s="33"/>
       <c r="BI10" s="33"/>
-      <c r="BJ10" s="34"/>
-      <c r="BK10" s="35"/>
+      <c r="BJ10" s="35"/>
+      <c r="BK10" s="34"/>
       <c r="BL10" s="33"/>
       <c r="BM10" s="33"/>
       <c r="BN10" s="33"/>
       <c r="BO10" s="33"/>
       <c r="BP10" s="33"/>
-      <c r="BQ10" s="34"/>
-      <c r="BR10" s="35"/>
+      <c r="BQ10" s="35"/>
+      <c r="BR10" s="34"/>
       <c r="BS10" s="33"/>
       <c r="BT10" s="33"/>
       <c r="BU10" s="33"/>
       <c r="BV10" s="33"/>
       <c r="BW10" s="33"/>
-      <c r="BX10" s="34"/>
-      <c r="BY10" s="35"/>
+      <c r="BX10" s="35"/>
+      <c r="BY10" s="34"/>
       <c r="BZ10" s="33"/>
       <c r="CA10" s="33"/>
       <c r="CB10" s="33"/>
       <c r="CC10" s="33"/>
       <c r="CD10" s="33"/>
-      <c r="CE10" s="34"/>
-      <c r="CF10" s="35"/>
+      <c r="CE10" s="35"/>
+      <c r="CF10" s="34"/>
       <c r="CG10" s="33"/>
       <c r="CH10" s="33"/>
       <c r="CI10" s="33"/>
       <c r="CJ10" s="33"/>
       <c r="CK10" s="33"/>
-      <c r="CL10" s="34"/>
-      <c r="CM10" s="35"/>
+      <c r="CL10" s="35"/>
+      <c r="CM10" s="34"/>
       <c r="CN10" s="33"/>
       <c r="CO10" s="33"/>
       <c r="CP10" s="33"/>
       <c r="CQ10" s="33"/>
       <c r="CR10" s="33"/>
-      <c r="CS10" s="34"/>
-      <c r="CT10" s="35"/>
+      <c r="CS10" s="35"/>
+      <c r="CT10" s="34"/>
       <c r="CU10" s="33"/>
       <c r="CV10" s="33"/>
     </row>
@@ -2751,13 +2763,13 @@
       <c r="F11" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G11" s="35"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="33"/>
       <c r="I11" s="33"/>
       <c r="J11" s="33"/>
       <c r="K11" s="33"/>
       <c r="L11" s="33"/>
-      <c r="M11" s="34"/>
+      <c r="M11" s="35"/>
       <c r="N11" s="33" t="s">
         <v>173</v>
       </c>
@@ -2776,85 +2788,87 @@
       <c r="S11" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="T11" s="34"/>
-      <c r="U11" s="35"/>
+      <c r="T11" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="U11" s="34"/>
       <c r="V11" s="33"/>
       <c r="W11" s="33"/>
       <c r="X11" s="33"/>
       <c r="Y11" s="33"/>
       <c r="Z11" s="33"/>
-      <c r="AA11" s="34"/>
-      <c r="AB11" s="35"/>
+      <c r="AA11" s="35"/>
+      <c r="AB11" s="34"/>
       <c r="AC11" s="33"/>
       <c r="AD11" s="33"/>
       <c r="AE11" s="33"/>
       <c r="AF11" s="33"/>
       <c r="AG11" s="33"/>
-      <c r="AH11" s="34"/>
-      <c r="AI11" s="35"/>
+      <c r="AH11" s="35"/>
+      <c r="AI11" s="34"/>
       <c r="AJ11" s="33"/>
       <c r="AK11" s="33"/>
       <c r="AL11" s="33"/>
       <c r="AM11" s="33"/>
       <c r="AN11" s="33"/>
-      <c r="AO11" s="34"/>
-      <c r="AP11" s="35"/>
+      <c r="AO11" s="35"/>
+      <c r="AP11" s="34"/>
       <c r="AQ11" s="33"/>
       <c r="AR11" s="33"/>
       <c r="AS11" s="33"/>
       <c r="AT11" s="33"/>
       <c r="AU11" s="33"/>
-      <c r="AV11" s="34"/>
-      <c r="AW11" s="35"/>
+      <c r="AV11" s="35"/>
+      <c r="AW11" s="34"/>
       <c r="AX11" s="33"/>
       <c r="AY11" s="33"/>
       <c r="AZ11" s="33"/>
       <c r="BA11" s="33"/>
       <c r="BB11" s="33"/>
-      <c r="BC11" s="34"/>
-      <c r="BD11" s="35"/>
+      <c r="BC11" s="35"/>
+      <c r="BD11" s="34"/>
       <c r="BE11" s="33"/>
       <c r="BF11" s="33"/>
       <c r="BG11" s="33"/>
       <c r="BH11" s="33"/>
       <c r="BI11" s="33"/>
-      <c r="BJ11" s="34"/>
-      <c r="BK11" s="35"/>
+      <c r="BJ11" s="35"/>
+      <c r="BK11" s="34"/>
       <c r="BL11" s="33"/>
       <c r="BM11" s="33"/>
       <c r="BN11" s="33"/>
       <c r="BO11" s="33"/>
       <c r="BP11" s="33"/>
-      <c r="BQ11" s="34"/>
-      <c r="BR11" s="35"/>
+      <c r="BQ11" s="35"/>
+      <c r="BR11" s="34"/>
       <c r="BS11" s="33"/>
       <c r="BT11" s="33"/>
       <c r="BU11" s="33"/>
       <c r="BV11" s="33"/>
       <c r="BW11" s="33"/>
-      <c r="BX11" s="34"/>
-      <c r="BY11" s="35"/>
+      <c r="BX11" s="35"/>
+      <c r="BY11" s="34"/>
       <c r="BZ11" s="33"/>
       <c r="CA11" s="33"/>
       <c r="CB11" s="33"/>
       <c r="CC11" s="33"/>
       <c r="CD11" s="33"/>
-      <c r="CE11" s="34"/>
-      <c r="CF11" s="35"/>
+      <c r="CE11" s="35"/>
+      <c r="CF11" s="34"/>
       <c r="CG11" s="33"/>
       <c r="CH11" s="33"/>
       <c r="CI11" s="33"/>
       <c r="CJ11" s="33"/>
       <c r="CK11" s="33"/>
-      <c r="CL11" s="34"/>
-      <c r="CM11" s="35"/>
+      <c r="CL11" s="35"/>
+      <c r="CM11" s="34"/>
       <c r="CN11" s="33"/>
       <c r="CO11" s="33"/>
       <c r="CP11" s="33"/>
       <c r="CQ11" s="33"/>
       <c r="CR11" s="33"/>
-      <c r="CS11" s="34"/>
-      <c r="CT11" s="35"/>
+      <c r="CS11" s="35"/>
+      <c r="CT11" s="34"/>
       <c r="CU11" s="33"/>
       <c r="CV11" s="33"/>
     </row>
@@ -2877,14 +2891,14 @@
       <c r="F12" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G12" s="35"/>
+      <c r="G12" s="34"/>
       <c r="H12" s="33"/>
       <c r="I12" s="33"/>
       <c r="J12" s="33"/>
       <c r="K12" s="33"/>
       <c r="L12" s="33"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="34"/>
       <c r="O12" s="33" t="s">
         <v>173</v>
       </c>
@@ -2900,85 +2914,87 @@
       <c r="S12" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="T12" s="34"/>
-      <c r="U12" s="35"/>
+      <c r="T12" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="U12" s="34"/>
       <c r="V12" s="33"/>
       <c r="W12" s="33"/>
       <c r="X12" s="33"/>
       <c r="Y12" s="33"/>
       <c r="Z12" s="33"/>
-      <c r="AA12" s="34"/>
-      <c r="AB12" s="35"/>
+      <c r="AA12" s="35"/>
+      <c r="AB12" s="34"/>
       <c r="AC12" s="33"/>
       <c r="AD12" s="33"/>
       <c r="AE12" s="33"/>
       <c r="AF12" s="33"/>
       <c r="AG12" s="33"/>
-      <c r="AH12" s="34"/>
-      <c r="AI12" s="35"/>
+      <c r="AH12" s="35"/>
+      <c r="AI12" s="34"/>
       <c r="AJ12" s="33"/>
       <c r="AK12" s="33"/>
       <c r="AL12" s="33"/>
       <c r="AM12" s="33"/>
       <c r="AN12" s="33"/>
-      <c r="AO12" s="34"/>
-      <c r="AP12" s="35"/>
+      <c r="AO12" s="35"/>
+      <c r="AP12" s="34"/>
       <c r="AQ12" s="33"/>
       <c r="AR12" s="33"/>
       <c r="AS12" s="33"/>
       <c r="AT12" s="33"/>
       <c r="AU12" s="33"/>
-      <c r="AV12" s="34"/>
-      <c r="AW12" s="35"/>
+      <c r="AV12" s="35"/>
+      <c r="AW12" s="34"/>
       <c r="AX12" s="33"/>
       <c r="AY12" s="33"/>
       <c r="AZ12" s="33"/>
       <c r="BA12" s="33"/>
       <c r="BB12" s="33"/>
-      <c r="BC12" s="34"/>
-      <c r="BD12" s="35"/>
+      <c r="BC12" s="35"/>
+      <c r="BD12" s="34"/>
       <c r="BE12" s="33"/>
       <c r="BF12" s="33"/>
       <c r="BG12" s="33"/>
       <c r="BH12" s="33"/>
       <c r="BI12" s="33"/>
-      <c r="BJ12" s="34"/>
-      <c r="BK12" s="35"/>
+      <c r="BJ12" s="35"/>
+      <c r="BK12" s="34"/>
       <c r="BL12" s="33"/>
       <c r="BM12" s="33"/>
       <c r="BN12" s="33"/>
       <c r="BO12" s="33"/>
       <c r="BP12" s="33"/>
-      <c r="BQ12" s="34"/>
-      <c r="BR12" s="35"/>
+      <c r="BQ12" s="35"/>
+      <c r="BR12" s="34"/>
       <c r="BS12" s="33"/>
       <c r="BT12" s="33"/>
       <c r="BU12" s="33"/>
       <c r="BV12" s="33"/>
       <c r="BW12" s="33"/>
-      <c r="BX12" s="34"/>
-      <c r="BY12" s="35"/>
+      <c r="BX12" s="35"/>
+      <c r="BY12" s="34"/>
       <c r="BZ12" s="33"/>
       <c r="CA12" s="33"/>
       <c r="CB12" s="33"/>
       <c r="CC12" s="33"/>
       <c r="CD12" s="33"/>
-      <c r="CE12" s="34"/>
-      <c r="CF12" s="35"/>
+      <c r="CE12" s="35"/>
+      <c r="CF12" s="34"/>
       <c r="CG12" s="33"/>
       <c r="CH12" s="33"/>
       <c r="CI12" s="33"/>
       <c r="CJ12" s="33"/>
       <c r="CK12" s="33"/>
-      <c r="CL12" s="34"/>
-      <c r="CM12" s="35"/>
+      <c r="CL12" s="35"/>
+      <c r="CM12" s="34"/>
       <c r="CN12" s="33"/>
       <c r="CO12" s="33"/>
       <c r="CP12" s="33"/>
       <c r="CQ12" s="33"/>
       <c r="CR12" s="33"/>
-      <c r="CS12" s="34"/>
-      <c r="CT12" s="35"/>
+      <c r="CS12" s="35"/>
+      <c r="CT12" s="34"/>
       <c r="CU12" s="33"/>
       <c r="CV12" s="33"/>
     </row>
@@ -3001,14 +3017,14 @@
       <c r="F13" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G13" s="35"/>
+      <c r="G13" s="34"/>
       <c r="H13" s="33"/>
       <c r="I13" s="33"/>
       <c r="J13" s="33"/>
       <c r="K13" s="33"/>
       <c r="L13" s="33"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="34"/>
       <c r="O13" s="33"/>
       <c r="P13" s="33" t="s">
         <v>173</v>
@@ -3022,85 +3038,87 @@
       <c r="S13" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="T13" s="34"/>
-      <c r="U13" s="35"/>
+      <c r="T13" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="U13" s="34"/>
       <c r="V13" s="33"/>
       <c r="W13" s="33"/>
       <c r="X13" s="33"/>
       <c r="Y13" s="33"/>
       <c r="Z13" s="33"/>
-      <c r="AA13" s="34"/>
-      <c r="AB13" s="35"/>
+      <c r="AA13" s="35"/>
+      <c r="AB13" s="34"/>
       <c r="AC13" s="33"/>
       <c r="AD13" s="33"/>
       <c r="AE13" s="33"/>
       <c r="AF13" s="33"/>
       <c r="AG13" s="33"/>
-      <c r="AH13" s="34"/>
-      <c r="AI13" s="35"/>
+      <c r="AH13" s="35"/>
+      <c r="AI13" s="34"/>
       <c r="AJ13" s="33"/>
       <c r="AK13" s="33"/>
       <c r="AL13" s="33"/>
       <c r="AM13" s="33"/>
       <c r="AN13" s="33"/>
-      <c r="AO13" s="34"/>
-      <c r="AP13" s="35"/>
+      <c r="AO13" s="35"/>
+      <c r="AP13" s="34"/>
       <c r="AQ13" s="33"/>
       <c r="AR13" s="33"/>
       <c r="AS13" s="33"/>
       <c r="AT13" s="33"/>
       <c r="AU13" s="33"/>
-      <c r="AV13" s="34"/>
-      <c r="AW13" s="35"/>
+      <c r="AV13" s="35"/>
+      <c r="AW13" s="34"/>
       <c r="AX13" s="33"/>
       <c r="AY13" s="33"/>
       <c r="AZ13" s="33"/>
       <c r="BA13" s="33"/>
       <c r="BB13" s="33"/>
-      <c r="BC13" s="34"/>
-      <c r="BD13" s="35"/>
+      <c r="BC13" s="35"/>
+      <c r="BD13" s="34"/>
       <c r="BE13" s="33"/>
       <c r="BF13" s="33"/>
       <c r="BG13" s="33"/>
       <c r="BH13" s="33"/>
       <c r="BI13" s="33"/>
-      <c r="BJ13" s="34"/>
-      <c r="BK13" s="35"/>
+      <c r="BJ13" s="35"/>
+      <c r="BK13" s="34"/>
       <c r="BL13" s="33"/>
       <c r="BM13" s="33"/>
       <c r="BN13" s="33"/>
       <c r="BO13" s="33"/>
       <c r="BP13" s="33"/>
-      <c r="BQ13" s="34"/>
-      <c r="BR13" s="35"/>
+      <c r="BQ13" s="35"/>
+      <c r="BR13" s="34"/>
       <c r="BS13" s="33"/>
       <c r="BT13" s="33"/>
       <c r="BU13" s="33"/>
       <c r="BV13" s="33"/>
       <c r="BW13" s="33"/>
-      <c r="BX13" s="34"/>
-      <c r="BY13" s="35"/>
+      <c r="BX13" s="35"/>
+      <c r="BY13" s="34"/>
       <c r="BZ13" s="33"/>
       <c r="CA13" s="33"/>
       <c r="CB13" s="33"/>
       <c r="CC13" s="33"/>
       <c r="CD13" s="33"/>
-      <c r="CE13" s="34"/>
-      <c r="CF13" s="35"/>
+      <c r="CE13" s="35"/>
+      <c r="CF13" s="34"/>
       <c r="CG13" s="33"/>
       <c r="CH13" s="33"/>
       <c r="CI13" s="33"/>
       <c r="CJ13" s="33"/>
       <c r="CK13" s="33"/>
-      <c r="CL13" s="34"/>
-      <c r="CM13" s="35"/>
+      <c r="CL13" s="35"/>
+      <c r="CM13" s="34"/>
       <c r="CN13" s="33"/>
       <c r="CO13" s="33"/>
       <c r="CP13" s="33"/>
       <c r="CQ13" s="33"/>
       <c r="CR13" s="33"/>
-      <c r="CS13" s="34"/>
-      <c r="CT13" s="35"/>
+      <c r="CS13" s="35"/>
+      <c r="CT13" s="34"/>
       <c r="CU13" s="33"/>
       <c r="CV13" s="33"/>
     </row>
@@ -3123,14 +3141,14 @@
       <c r="F14" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G14" s="35"/>
+      <c r="G14" s="34"/>
       <c r="H14" s="33"/>
       <c r="I14" s="33"/>
       <c r="J14" s="33"/>
       <c r="K14" s="33"/>
       <c r="L14" s="33"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="34"/>
       <c r="O14" s="33"/>
       <c r="P14" s="33"/>
       <c r="Q14" s="33" t="s">
@@ -3142,85 +3160,87 @@
       <c r="S14" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="T14" s="34"/>
-      <c r="U14" s="35"/>
+      <c r="T14" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="U14" s="34"/>
       <c r="V14" s="33"/>
       <c r="W14" s="33"/>
       <c r="X14" s="33"/>
       <c r="Y14" s="33"/>
       <c r="Z14" s="33"/>
-      <c r="AA14" s="34"/>
-      <c r="AB14" s="35"/>
+      <c r="AA14" s="35"/>
+      <c r="AB14" s="34"/>
       <c r="AC14" s="33"/>
       <c r="AD14" s="33"/>
       <c r="AE14" s="33"/>
       <c r="AF14" s="33"/>
       <c r="AG14" s="33"/>
-      <c r="AH14" s="34"/>
-      <c r="AI14" s="35"/>
+      <c r="AH14" s="35"/>
+      <c r="AI14" s="34"/>
       <c r="AJ14" s="33"/>
       <c r="AK14" s="33"/>
       <c r="AL14" s="33"/>
       <c r="AM14" s="33"/>
       <c r="AN14" s="33"/>
-      <c r="AO14" s="34"/>
-      <c r="AP14" s="35"/>
+      <c r="AO14" s="35"/>
+      <c r="AP14" s="34"/>
       <c r="AQ14" s="33"/>
       <c r="AR14" s="33"/>
       <c r="AS14" s="33"/>
       <c r="AT14" s="33"/>
       <c r="AU14" s="33"/>
-      <c r="AV14" s="34"/>
-      <c r="AW14" s="35"/>
+      <c r="AV14" s="35"/>
+      <c r="AW14" s="34"/>
       <c r="AX14" s="33"/>
       <c r="AY14" s="33"/>
       <c r="AZ14" s="33"/>
       <c r="BA14" s="33"/>
       <c r="BB14" s="33"/>
-      <c r="BC14" s="34"/>
-      <c r="BD14" s="35"/>
+      <c r="BC14" s="35"/>
+      <c r="BD14" s="34"/>
       <c r="BE14" s="33"/>
       <c r="BF14" s="33"/>
       <c r="BG14" s="33"/>
       <c r="BH14" s="33"/>
       <c r="BI14" s="33"/>
-      <c r="BJ14" s="34"/>
-      <c r="BK14" s="35"/>
+      <c r="BJ14" s="35"/>
+      <c r="BK14" s="34"/>
       <c r="BL14" s="33"/>
       <c r="BM14" s="33"/>
       <c r="BN14" s="33"/>
       <c r="BO14" s="33"/>
       <c r="BP14" s="33"/>
-      <c r="BQ14" s="34"/>
-      <c r="BR14" s="35"/>
+      <c r="BQ14" s="35"/>
+      <c r="BR14" s="34"/>
       <c r="BS14" s="33"/>
       <c r="BT14" s="33"/>
       <c r="BU14" s="33"/>
       <c r="BV14" s="33"/>
       <c r="BW14" s="33"/>
-      <c r="BX14" s="34"/>
-      <c r="BY14" s="35"/>
+      <c r="BX14" s="35"/>
+      <c r="BY14" s="34"/>
       <c r="BZ14" s="33"/>
       <c r="CA14" s="33"/>
       <c r="CB14" s="33"/>
       <c r="CC14" s="33"/>
       <c r="CD14" s="33"/>
-      <c r="CE14" s="34"/>
-      <c r="CF14" s="35"/>
+      <c r="CE14" s="35"/>
+      <c r="CF14" s="34"/>
       <c r="CG14" s="33"/>
       <c r="CH14" s="33"/>
       <c r="CI14" s="33"/>
       <c r="CJ14" s="33"/>
       <c r="CK14" s="33"/>
-      <c r="CL14" s="34"/>
-      <c r="CM14" s="35"/>
+      <c r="CL14" s="35"/>
+      <c r="CM14" s="34"/>
       <c r="CN14" s="33"/>
       <c r="CO14" s="33"/>
       <c r="CP14" s="33"/>
       <c r="CQ14" s="33"/>
       <c r="CR14" s="33"/>
-      <c r="CS14" s="34"/>
-      <c r="CT14" s="35"/>
+      <c r="CS14" s="35"/>
+      <c r="CT14" s="34"/>
       <c r="CU14" s="33"/>
       <c r="CV14" s="33"/>
     </row>
@@ -3243,14 +3263,14 @@
       <c r="F15" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G15" s="35"/>
+      <c r="G15" s="34"/>
       <c r="H15" s="33"/>
       <c r="I15" s="33"/>
       <c r="J15" s="33"/>
       <c r="K15" s="33"/>
       <c r="L15" s="33"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="34"/>
       <c r="O15" s="33"/>
       <c r="P15" s="33"/>
       <c r="Q15" s="33"/>
@@ -3260,85 +3280,87 @@
       <c r="S15" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="T15" s="34"/>
-      <c r="U15" s="35"/>
+      <c r="T15" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="U15" s="34"/>
       <c r="V15" s="33"/>
       <c r="W15" s="33"/>
       <c r="X15" s="33"/>
       <c r="Y15" s="33"/>
       <c r="Z15" s="33"/>
-      <c r="AA15" s="34"/>
-      <c r="AB15" s="35"/>
+      <c r="AA15" s="35"/>
+      <c r="AB15" s="34"/>
       <c r="AC15" s="33"/>
       <c r="AD15" s="33"/>
       <c r="AE15" s="33"/>
       <c r="AF15" s="33"/>
       <c r="AG15" s="33"/>
-      <c r="AH15" s="34"/>
-      <c r="AI15" s="35"/>
+      <c r="AH15" s="35"/>
+      <c r="AI15" s="34"/>
       <c r="AJ15" s="33"/>
       <c r="AK15" s="33"/>
       <c r="AL15" s="33"/>
       <c r="AM15" s="33"/>
       <c r="AN15" s="33"/>
-      <c r="AO15" s="34"/>
-      <c r="AP15" s="35"/>
+      <c r="AO15" s="35"/>
+      <c r="AP15" s="34"/>
       <c r="AQ15" s="33"/>
       <c r="AR15" s="33"/>
       <c r="AS15" s="33"/>
       <c r="AT15" s="33"/>
       <c r="AU15" s="33"/>
-      <c r="AV15" s="34"/>
-      <c r="AW15" s="35"/>
+      <c r="AV15" s="35"/>
+      <c r="AW15" s="34"/>
       <c r="AX15" s="33"/>
       <c r="AY15" s="33"/>
       <c r="AZ15" s="33"/>
       <c r="BA15" s="33"/>
       <c r="BB15" s="33"/>
-      <c r="BC15" s="34"/>
-      <c r="BD15" s="35"/>
+      <c r="BC15" s="35"/>
+      <c r="BD15" s="34"/>
       <c r="BE15" s="33"/>
       <c r="BF15" s="33"/>
       <c r="BG15" s="33"/>
       <c r="BH15" s="33"/>
       <c r="BI15" s="33"/>
-      <c r="BJ15" s="34"/>
-      <c r="BK15" s="35"/>
+      <c r="BJ15" s="35"/>
+      <c r="BK15" s="34"/>
       <c r="BL15" s="33"/>
       <c r="BM15" s="33"/>
       <c r="BN15" s="33"/>
       <c r="BO15" s="33"/>
       <c r="BP15" s="33"/>
-      <c r="BQ15" s="34"/>
-      <c r="BR15" s="35"/>
+      <c r="BQ15" s="35"/>
+      <c r="BR15" s="34"/>
       <c r="BS15" s="33"/>
       <c r="BT15" s="33"/>
       <c r="BU15" s="33"/>
       <c r="BV15" s="33"/>
       <c r="BW15" s="33"/>
-      <c r="BX15" s="34"/>
-      <c r="BY15" s="35"/>
+      <c r="BX15" s="35"/>
+      <c r="BY15" s="34"/>
       <c r="BZ15" s="33"/>
       <c r="CA15" s="33"/>
       <c r="CB15" s="33"/>
       <c r="CC15" s="33"/>
       <c r="CD15" s="33"/>
-      <c r="CE15" s="34"/>
-      <c r="CF15" s="35"/>
+      <c r="CE15" s="35"/>
+      <c r="CF15" s="34"/>
       <c r="CG15" s="33"/>
       <c r="CH15" s="33"/>
       <c r="CI15" s="33"/>
       <c r="CJ15" s="33"/>
       <c r="CK15" s="33"/>
-      <c r="CL15" s="34"/>
-      <c r="CM15" s="35"/>
+      <c r="CL15" s="35"/>
+      <c r="CM15" s="34"/>
       <c r="CN15" s="33"/>
       <c r="CO15" s="33"/>
       <c r="CP15" s="33"/>
       <c r="CQ15" s="33"/>
       <c r="CR15" s="33"/>
-      <c r="CS15" s="34"/>
-      <c r="CT15" s="35"/>
+      <c r="CS15" s="35"/>
+      <c r="CT15" s="34"/>
       <c r="CU15" s="33"/>
       <c r="CV15" s="33"/>
     </row>
@@ -3361,14 +3383,14 @@
       <c r="F16" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G16" s="35"/>
+      <c r="G16" s="34"/>
       <c r="H16" s="33"/>
       <c r="I16" s="33"/>
       <c r="J16" s="33"/>
       <c r="K16" s="33"/>
       <c r="L16" s="33"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="34"/>
       <c r="O16" s="33"/>
       <c r="P16" s="33"/>
       <c r="Q16" s="33"/>
@@ -3376,85 +3398,87 @@
       <c r="S16" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="T16" s="34"/>
-      <c r="U16" s="35"/>
+      <c r="T16" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="U16" s="34"/>
       <c r="V16" s="33"/>
       <c r="W16" s="33"/>
       <c r="X16" s="33"/>
       <c r="Y16" s="33"/>
       <c r="Z16" s="33"/>
-      <c r="AA16" s="34"/>
-      <c r="AB16" s="35"/>
+      <c r="AA16" s="35"/>
+      <c r="AB16" s="34"/>
       <c r="AC16" s="33"/>
       <c r="AD16" s="33"/>
       <c r="AE16" s="33"/>
       <c r="AF16" s="33"/>
       <c r="AG16" s="33"/>
-      <c r="AH16" s="34"/>
-      <c r="AI16" s="35"/>
+      <c r="AH16" s="35"/>
+      <c r="AI16" s="34"/>
       <c r="AJ16" s="33"/>
       <c r="AK16" s="33"/>
       <c r="AL16" s="33"/>
       <c r="AM16" s="33"/>
       <c r="AN16" s="33"/>
-      <c r="AO16" s="34"/>
-      <c r="AP16" s="35"/>
+      <c r="AO16" s="35"/>
+      <c r="AP16" s="34"/>
       <c r="AQ16" s="33"/>
       <c r="AR16" s="33"/>
       <c r="AS16" s="33"/>
       <c r="AT16" s="33"/>
       <c r="AU16" s="33"/>
-      <c r="AV16" s="34"/>
-      <c r="AW16" s="35"/>
+      <c r="AV16" s="35"/>
+      <c r="AW16" s="34"/>
       <c r="AX16" s="33"/>
       <c r="AY16" s="33"/>
       <c r="AZ16" s="33"/>
       <c r="BA16" s="33"/>
       <c r="BB16" s="33"/>
-      <c r="BC16" s="34"/>
-      <c r="BD16" s="35"/>
+      <c r="BC16" s="35"/>
+      <c r="BD16" s="34"/>
       <c r="BE16" s="33"/>
       <c r="BF16" s="33"/>
       <c r="BG16" s="33"/>
       <c r="BH16" s="33"/>
       <c r="BI16" s="33"/>
-      <c r="BJ16" s="34"/>
-      <c r="BK16" s="35"/>
+      <c r="BJ16" s="35"/>
+      <c r="BK16" s="34"/>
       <c r="BL16" s="33"/>
       <c r="BM16" s="33"/>
       <c r="BN16" s="33"/>
       <c r="BO16" s="33"/>
       <c r="BP16" s="33"/>
-      <c r="BQ16" s="34"/>
-      <c r="BR16" s="35"/>
+      <c r="BQ16" s="35"/>
+      <c r="BR16" s="34"/>
       <c r="BS16" s="33"/>
       <c r="BT16" s="33"/>
       <c r="BU16" s="33"/>
       <c r="BV16" s="33"/>
       <c r="BW16" s="33"/>
-      <c r="BX16" s="34"/>
-      <c r="BY16" s="35"/>
+      <c r="BX16" s="35"/>
+      <c r="BY16" s="34"/>
       <c r="BZ16" s="33"/>
       <c r="CA16" s="33"/>
       <c r="CB16" s="33"/>
       <c r="CC16" s="33"/>
       <c r="CD16" s="33"/>
-      <c r="CE16" s="34"/>
-      <c r="CF16" s="35"/>
+      <c r="CE16" s="35"/>
+      <c r="CF16" s="34"/>
       <c r="CG16" s="33"/>
       <c r="CH16" s="33"/>
       <c r="CI16" s="33"/>
       <c r="CJ16" s="33"/>
       <c r="CK16" s="33"/>
-      <c r="CL16" s="34"/>
-      <c r="CM16" s="35"/>
+      <c r="CL16" s="35"/>
+      <c r="CM16" s="34"/>
       <c r="CN16" s="33"/>
       <c r="CO16" s="33"/>
       <c r="CP16" s="33"/>
       <c r="CQ16" s="33"/>
       <c r="CR16" s="33"/>
-      <c r="CS16" s="34"/>
-      <c r="CT16" s="35"/>
+      <c r="CS16" s="35"/>
+      <c r="CT16" s="34"/>
       <c r="CU16" s="33"/>
       <c r="CV16" s="33"/>
     </row>
@@ -3477,98 +3501,100 @@
       <c r="F17" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G17" s="35"/>
+      <c r="G17" s="34"/>
       <c r="H17" s="33"/>
       <c r="I17" s="33"/>
       <c r="J17" s="33"/>
       <c r="K17" s="33"/>
       <c r="L17" s="33"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="34"/>
       <c r="O17" s="33"/>
       <c r="P17" s="33"/>
       <c r="Q17" s="33"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
-      <c r="T17" s="34"/>
-      <c r="U17" s="35"/>
+      <c r="T17" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="U17" s="34"/>
       <c r="V17" s="33"/>
       <c r="W17" s="33"/>
       <c r="X17" s="33"/>
       <c r="Y17" s="33"/>
       <c r="Z17" s="33"/>
-      <c r="AA17" s="34"/>
-      <c r="AB17" s="35"/>
+      <c r="AA17" s="35"/>
+      <c r="AB17" s="34"/>
       <c r="AC17" s="33"/>
       <c r="AD17" s="33"/>
       <c r="AE17" s="33"/>
       <c r="AF17" s="33"/>
       <c r="AG17" s="33"/>
-      <c r="AH17" s="34"/>
-      <c r="AI17" s="35"/>
+      <c r="AH17" s="35"/>
+      <c r="AI17" s="34"/>
       <c r="AJ17" s="33"/>
       <c r="AK17" s="33"/>
       <c r="AL17" s="33"/>
       <c r="AM17" s="33"/>
       <c r="AN17" s="33"/>
-      <c r="AO17" s="34"/>
-      <c r="AP17" s="35"/>
+      <c r="AO17" s="35"/>
+      <c r="AP17" s="34"/>
       <c r="AQ17" s="33"/>
       <c r="AR17" s="33"/>
       <c r="AS17" s="33"/>
       <c r="AT17" s="33"/>
       <c r="AU17" s="33"/>
-      <c r="AV17" s="34"/>
-      <c r="AW17" s="35"/>
+      <c r="AV17" s="35"/>
+      <c r="AW17" s="34"/>
       <c r="AX17" s="33"/>
       <c r="AY17" s="33"/>
       <c r="AZ17" s="33"/>
       <c r="BA17" s="33"/>
       <c r="BB17" s="33"/>
-      <c r="BC17" s="34"/>
-      <c r="BD17" s="35"/>
+      <c r="BC17" s="35"/>
+      <c r="BD17" s="34"/>
       <c r="BE17" s="33"/>
       <c r="BF17" s="33"/>
       <c r="BG17" s="33"/>
       <c r="BH17" s="33"/>
       <c r="BI17" s="33"/>
-      <c r="BJ17" s="34"/>
-      <c r="BK17" s="35"/>
+      <c r="BJ17" s="35"/>
+      <c r="BK17" s="34"/>
       <c r="BL17" s="33"/>
       <c r="BM17" s="33"/>
       <c r="BN17" s="33"/>
       <c r="BO17" s="33"/>
       <c r="BP17" s="33"/>
-      <c r="BQ17" s="34"/>
-      <c r="BR17" s="35"/>
+      <c r="BQ17" s="35"/>
+      <c r="BR17" s="34"/>
       <c r="BS17" s="33"/>
       <c r="BT17" s="33"/>
       <c r="BU17" s="33"/>
       <c r="BV17" s="33"/>
       <c r="BW17" s="33"/>
-      <c r="BX17" s="34"/>
-      <c r="BY17" s="35"/>
+      <c r="BX17" s="35"/>
+      <c r="BY17" s="34"/>
       <c r="BZ17" s="33"/>
       <c r="CA17" s="33"/>
       <c r="CB17" s="33"/>
       <c r="CC17" s="33"/>
       <c r="CD17" s="33"/>
-      <c r="CE17" s="34"/>
-      <c r="CF17" s="35"/>
+      <c r="CE17" s="35"/>
+      <c r="CF17" s="34"/>
       <c r="CG17" s="33"/>
       <c r="CH17" s="33"/>
       <c r="CI17" s="33"/>
       <c r="CJ17" s="33"/>
       <c r="CK17" s="33"/>
-      <c r="CL17" s="34"/>
-      <c r="CM17" s="35"/>
+      <c r="CL17" s="35"/>
+      <c r="CM17" s="34"/>
       <c r="CN17" s="33"/>
       <c r="CO17" s="33"/>
       <c r="CP17" s="33"/>
       <c r="CQ17" s="33"/>
       <c r="CR17" s="33"/>
-      <c r="CS17" s="34"/>
-      <c r="CT17" s="35"/>
+      <c r="CS17" s="35"/>
+      <c r="CT17" s="34"/>
       <c r="CU17" s="33"/>
       <c r="CV17" s="33"/>
     </row>
@@ -3591,98 +3617,98 @@
       <c r="F18" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G18" s="35"/>
+      <c r="G18" s="34"/>
       <c r="H18" s="33"/>
       <c r="I18" s="33"/>
       <c r="J18" s="33"/>
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="34"/>
       <c r="O18" s="33"/>
       <c r="P18" s="33"/>
       <c r="Q18" s="33"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
-      <c r="T18" s="34"/>
-      <c r="U18" s="35"/>
+      <c r="T18" s="35"/>
+      <c r="U18" s="34"/>
       <c r="V18" s="33"/>
       <c r="W18" s="33"/>
       <c r="X18" s="33"/>
       <c r="Y18" s="33"/>
       <c r="Z18" s="33"/>
-      <c r="AA18" s="34"/>
-      <c r="AB18" s="35"/>
+      <c r="AA18" s="35"/>
+      <c r="AB18" s="34"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
       <c r="AF18" s="33"/>
       <c r="AG18" s="33"/>
-      <c r="AH18" s="34"/>
-      <c r="AI18" s="35"/>
+      <c r="AH18" s="35"/>
+      <c r="AI18" s="34"/>
       <c r="AJ18" s="33"/>
       <c r="AK18" s="33"/>
       <c r="AL18" s="33"/>
       <c r="AM18" s="33"/>
       <c r="AN18" s="33"/>
-      <c r="AO18" s="34"/>
-      <c r="AP18" s="35"/>
+      <c r="AO18" s="35"/>
+      <c r="AP18" s="34"/>
       <c r="AQ18" s="33"/>
       <c r="AR18" s="33"/>
       <c r="AS18" s="33"/>
       <c r="AT18" s="33"/>
       <c r="AU18" s="33"/>
-      <c r="AV18" s="34"/>
-      <c r="AW18" s="35"/>
+      <c r="AV18" s="35"/>
+      <c r="AW18" s="34"/>
       <c r="AX18" s="33"/>
       <c r="AY18" s="33"/>
       <c r="AZ18" s="33"/>
       <c r="BA18" s="33"/>
       <c r="BB18" s="33"/>
-      <c r="BC18" s="34"/>
-      <c r="BD18" s="35"/>
+      <c r="BC18" s="35"/>
+      <c r="BD18" s="34"/>
       <c r="BE18" s="33"/>
       <c r="BF18" s="33"/>
       <c r="BG18" s="33"/>
       <c r="BH18" s="33"/>
       <c r="BI18" s="33"/>
-      <c r="BJ18" s="34"/>
-      <c r="BK18" s="35"/>
+      <c r="BJ18" s="35"/>
+      <c r="BK18" s="34"/>
       <c r="BL18" s="33"/>
       <c r="BM18" s="33"/>
       <c r="BN18" s="33"/>
       <c r="BO18" s="33"/>
       <c r="BP18" s="33"/>
-      <c r="BQ18" s="34"/>
-      <c r="BR18" s="35"/>
+      <c r="BQ18" s="35"/>
+      <c r="BR18" s="34"/>
       <c r="BS18" s="33"/>
       <c r="BT18" s="33"/>
       <c r="BU18" s="33"/>
       <c r="BV18" s="33"/>
       <c r="BW18" s="33"/>
-      <c r="BX18" s="34"/>
-      <c r="BY18" s="35"/>
+      <c r="BX18" s="35"/>
+      <c r="BY18" s="34"/>
       <c r="BZ18" s="33"/>
       <c r="CA18" s="33"/>
       <c r="CB18" s="33"/>
       <c r="CC18" s="33"/>
       <c r="CD18" s="33"/>
-      <c r="CE18" s="34"/>
-      <c r="CF18" s="35"/>
+      <c r="CE18" s="35"/>
+      <c r="CF18" s="34"/>
       <c r="CG18" s="33"/>
       <c r="CH18" s="33"/>
       <c r="CI18" s="33"/>
       <c r="CJ18" s="33"/>
       <c r="CK18" s="33"/>
-      <c r="CL18" s="34"/>
-      <c r="CM18" s="35"/>
+      <c r="CL18" s="35"/>
+      <c r="CM18" s="34"/>
       <c r="CN18" s="33"/>
       <c r="CO18" s="33"/>
       <c r="CP18" s="33"/>
       <c r="CQ18" s="33"/>
       <c r="CR18" s="33"/>
-      <c r="CS18" s="34"/>
-      <c r="CT18" s="35"/>
+      <c r="CS18" s="35"/>
+      <c r="CT18" s="34"/>
       <c r="CU18" s="33"/>
       <c r="CV18" s="33"/>
     </row>
@@ -3705,98 +3731,98 @@
       <c r="F19" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G19" s="35"/>
+      <c r="G19" s="34"/>
       <c r="H19" s="33"/>
       <c r="I19" s="33"/>
       <c r="J19" s="33"/>
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="34"/>
       <c r="O19" s="33"/>
       <c r="P19" s="33"/>
       <c r="Q19" s="33"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
-      <c r="T19" s="34"/>
-      <c r="U19" s="35"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="34"/>
       <c r="V19" s="33"/>
       <c r="W19" s="33"/>
       <c r="X19" s="33"/>
       <c r="Y19" s="33"/>
       <c r="Z19" s="33"/>
-      <c r="AA19" s="34"/>
-      <c r="AB19" s="35"/>
+      <c r="AA19" s="35"/>
+      <c r="AB19" s="34"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
       <c r="AF19" s="33"/>
       <c r="AG19" s="33"/>
-      <c r="AH19" s="34"/>
-      <c r="AI19" s="35"/>
+      <c r="AH19" s="35"/>
+      <c r="AI19" s="34"/>
       <c r="AJ19" s="33"/>
       <c r="AK19" s="33"/>
       <c r="AL19" s="33"/>
       <c r="AM19" s="33"/>
       <c r="AN19" s="33"/>
-      <c r="AO19" s="34"/>
-      <c r="AP19" s="35"/>
+      <c r="AO19" s="35"/>
+      <c r="AP19" s="34"/>
       <c r="AQ19" s="33"/>
       <c r="AR19" s="33"/>
       <c r="AS19" s="33"/>
       <c r="AT19" s="33"/>
       <c r="AU19" s="33"/>
-      <c r="AV19" s="34"/>
-      <c r="AW19" s="35"/>
+      <c r="AV19" s="35"/>
+      <c r="AW19" s="34"/>
       <c r="AX19" s="33"/>
       <c r="AY19" s="33"/>
       <c r="AZ19" s="33"/>
       <c r="BA19" s="33"/>
       <c r="BB19" s="33"/>
-      <c r="BC19" s="34"/>
-      <c r="BD19" s="35"/>
+      <c r="BC19" s="35"/>
+      <c r="BD19" s="34"/>
       <c r="BE19" s="33"/>
       <c r="BF19" s="33"/>
       <c r="BG19" s="33"/>
       <c r="BH19" s="33"/>
       <c r="BI19" s="33"/>
-      <c r="BJ19" s="34"/>
-      <c r="BK19" s="35"/>
+      <c r="BJ19" s="35"/>
+      <c r="BK19" s="34"/>
       <c r="BL19" s="33"/>
       <c r="BM19" s="33"/>
       <c r="BN19" s="33"/>
       <c r="BO19" s="33"/>
       <c r="BP19" s="33"/>
-      <c r="BQ19" s="34"/>
-      <c r="BR19" s="35"/>
+      <c r="BQ19" s="35"/>
+      <c r="BR19" s="34"/>
       <c r="BS19" s="33"/>
       <c r="BT19" s="33"/>
       <c r="BU19" s="33"/>
       <c r="BV19" s="33"/>
       <c r="BW19" s="33"/>
-      <c r="BX19" s="34"/>
-      <c r="BY19" s="35"/>
+      <c r="BX19" s="35"/>
+      <c r="BY19" s="34"/>
       <c r="BZ19" s="33"/>
       <c r="CA19" s="33"/>
       <c r="CB19" s="33"/>
       <c r="CC19" s="33"/>
       <c r="CD19" s="33"/>
-      <c r="CE19" s="34"/>
-      <c r="CF19" s="35"/>
+      <c r="CE19" s="35"/>
+      <c r="CF19" s="34"/>
       <c r="CG19" s="33"/>
       <c r="CH19" s="33"/>
       <c r="CI19" s="33"/>
       <c r="CJ19" s="33"/>
       <c r="CK19" s="33"/>
-      <c r="CL19" s="34"/>
-      <c r="CM19" s="35"/>
+      <c r="CL19" s="35"/>
+      <c r="CM19" s="34"/>
       <c r="CN19" s="33"/>
       <c r="CO19" s="33"/>
       <c r="CP19" s="33"/>
       <c r="CQ19" s="33"/>
       <c r="CR19" s="33"/>
-      <c r="CS19" s="34"/>
-      <c r="CT19" s="35"/>
+      <c r="CS19" s="35"/>
+      <c r="CT19" s="34"/>
       <c r="CU19" s="33"/>
       <c r="CV19" s="33"/>
     </row>
@@ -3819,98 +3845,98 @@
       <c r="F20" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G20" s="35"/>
+      <c r="G20" s="34"/>
       <c r="H20" s="33"/>
       <c r="I20" s="33"/>
       <c r="J20" s="33"/>
       <c r="K20" s="33"/>
       <c r="L20" s="33"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="34"/>
       <c r="O20" s="33"/>
       <c r="P20" s="33"/>
       <c r="Q20" s="33"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
-      <c r="T20" s="34"/>
-      <c r="U20" s="35"/>
+      <c r="T20" s="35"/>
+      <c r="U20" s="34"/>
       <c r="V20" s="33"/>
       <c r="W20" s="33"/>
       <c r="X20" s="33"/>
       <c r="Y20" s="33"/>
       <c r="Z20" s="33"/>
-      <c r="AA20" s="34"/>
-      <c r="AB20" s="35"/>
+      <c r="AA20" s="35"/>
+      <c r="AB20" s="34"/>
       <c r="AC20" s="33"/>
       <c r="AD20" s="33"/>
       <c r="AE20" s="33"/>
       <c r="AF20" s="33"/>
       <c r="AG20" s="33"/>
-      <c r="AH20" s="34"/>
-      <c r="AI20" s="35"/>
+      <c r="AH20" s="35"/>
+      <c r="AI20" s="34"/>
       <c r="AJ20" s="33"/>
       <c r="AK20" s="33"/>
       <c r="AL20" s="33"/>
       <c r="AM20" s="33"/>
       <c r="AN20" s="33"/>
-      <c r="AO20" s="34"/>
-      <c r="AP20" s="35"/>
+      <c r="AO20" s="35"/>
+      <c r="AP20" s="34"/>
       <c r="AQ20" s="33"/>
       <c r="AR20" s="33"/>
       <c r="AS20" s="33"/>
       <c r="AT20" s="33"/>
       <c r="AU20" s="33"/>
-      <c r="AV20" s="34"/>
-      <c r="AW20" s="35"/>
+      <c r="AV20" s="35"/>
+      <c r="AW20" s="34"/>
       <c r="AX20" s="33"/>
       <c r="AY20" s="33"/>
       <c r="AZ20" s="33"/>
       <c r="BA20" s="33"/>
       <c r="BB20" s="33"/>
-      <c r="BC20" s="34"/>
-      <c r="BD20" s="35"/>
+      <c r="BC20" s="35"/>
+      <c r="BD20" s="34"/>
       <c r="BE20" s="33"/>
       <c r="BF20" s="33"/>
       <c r="BG20" s="33"/>
       <c r="BH20" s="33"/>
       <c r="BI20" s="33"/>
-      <c r="BJ20" s="34"/>
-      <c r="BK20" s="35"/>
+      <c r="BJ20" s="35"/>
+      <c r="BK20" s="34"/>
       <c r="BL20" s="33"/>
       <c r="BM20" s="33"/>
       <c r="BN20" s="33"/>
       <c r="BO20" s="33"/>
       <c r="BP20" s="33"/>
-      <c r="BQ20" s="34"/>
-      <c r="BR20" s="35"/>
+      <c r="BQ20" s="35"/>
+      <c r="BR20" s="34"/>
       <c r="BS20" s="33"/>
       <c r="BT20" s="33"/>
       <c r="BU20" s="33"/>
       <c r="BV20" s="33"/>
       <c r="BW20" s="33"/>
-      <c r="BX20" s="34"/>
-      <c r="BY20" s="35"/>
+      <c r="BX20" s="35"/>
+      <c r="BY20" s="34"/>
       <c r="BZ20" s="33"/>
       <c r="CA20" s="33"/>
       <c r="CB20" s="33"/>
       <c r="CC20" s="33"/>
       <c r="CD20" s="33"/>
-      <c r="CE20" s="34"/>
-      <c r="CF20" s="35"/>
+      <c r="CE20" s="35"/>
+      <c r="CF20" s="34"/>
       <c r="CG20" s="33"/>
       <c r="CH20" s="33"/>
       <c r="CI20" s="33"/>
       <c r="CJ20" s="33"/>
       <c r="CK20" s="33"/>
-      <c r="CL20" s="34"/>
-      <c r="CM20" s="35"/>
+      <c r="CL20" s="35"/>
+      <c r="CM20" s="34"/>
       <c r="CN20" s="33"/>
       <c r="CO20" s="33"/>
       <c r="CP20" s="33"/>
       <c r="CQ20" s="33"/>
       <c r="CR20" s="33"/>
-      <c r="CS20" s="34"/>
-      <c r="CT20" s="35"/>
+      <c r="CS20" s="35"/>
+      <c r="CT20" s="34"/>
       <c r="CU20" s="33"/>
       <c r="CV20" s="33"/>
     </row>
@@ -3933,98 +3959,98 @@
       <c r="F21" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G21" s="35"/>
+      <c r="G21" s="34"/>
       <c r="H21" s="33"/>
       <c r="I21" s="33"/>
       <c r="J21" s="33"/>
       <c r="K21" s="33"/>
       <c r="L21" s="33"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="34"/>
       <c r="O21" s="33"/>
       <c r="P21" s="33"/>
       <c r="Q21" s="33"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
-      <c r="T21" s="34"/>
-      <c r="U21" s="35"/>
+      <c r="T21" s="35"/>
+      <c r="U21" s="34"/>
       <c r="V21" s="33"/>
       <c r="W21" s="33"/>
       <c r="X21" s="33"/>
       <c r="Y21" s="33"/>
       <c r="Z21" s="33"/>
-      <c r="AA21" s="34"/>
-      <c r="AB21" s="35"/>
+      <c r="AA21" s="35"/>
+      <c r="AB21" s="34"/>
       <c r="AC21" s="33"/>
       <c r="AD21" s="33"/>
       <c r="AE21" s="33"/>
       <c r="AF21" s="33"/>
       <c r="AG21" s="33"/>
-      <c r="AH21" s="34"/>
-      <c r="AI21" s="35"/>
+      <c r="AH21" s="35"/>
+      <c r="AI21" s="34"/>
       <c r="AJ21" s="33"/>
       <c r="AK21" s="33"/>
       <c r="AL21" s="33"/>
       <c r="AM21" s="33"/>
       <c r="AN21" s="33"/>
-      <c r="AO21" s="34"/>
-      <c r="AP21" s="35"/>
+      <c r="AO21" s="35"/>
+      <c r="AP21" s="34"/>
       <c r="AQ21" s="33"/>
       <c r="AR21" s="33"/>
       <c r="AS21" s="33"/>
       <c r="AT21" s="33"/>
       <c r="AU21" s="33"/>
-      <c r="AV21" s="34"/>
-      <c r="AW21" s="35"/>
+      <c r="AV21" s="35"/>
+      <c r="AW21" s="34"/>
       <c r="AX21" s="33"/>
       <c r="AY21" s="33"/>
       <c r="AZ21" s="33"/>
       <c r="BA21" s="33"/>
       <c r="BB21" s="33"/>
-      <c r="BC21" s="34"/>
-      <c r="BD21" s="35"/>
+      <c r="BC21" s="35"/>
+      <c r="BD21" s="34"/>
       <c r="BE21" s="33"/>
       <c r="BF21" s="33"/>
       <c r="BG21" s="33"/>
       <c r="BH21" s="33"/>
       <c r="BI21" s="33"/>
-      <c r="BJ21" s="34"/>
-      <c r="BK21" s="35"/>
+      <c r="BJ21" s="35"/>
+      <c r="BK21" s="34"/>
       <c r="BL21" s="33"/>
       <c r="BM21" s="33"/>
       <c r="BN21" s="33"/>
       <c r="BO21" s="33"/>
       <c r="BP21" s="33"/>
-      <c r="BQ21" s="34"/>
-      <c r="BR21" s="35"/>
+      <c r="BQ21" s="35"/>
+      <c r="BR21" s="34"/>
       <c r="BS21" s="33"/>
       <c r="BT21" s="33"/>
       <c r="BU21" s="33"/>
       <c r="BV21" s="33"/>
       <c r="BW21" s="33"/>
-      <c r="BX21" s="34"/>
-      <c r="BY21" s="35"/>
+      <c r="BX21" s="35"/>
+      <c r="BY21" s="34"/>
       <c r="BZ21" s="33"/>
       <c r="CA21" s="33"/>
       <c r="CB21" s="33"/>
       <c r="CC21" s="33"/>
       <c r="CD21" s="33"/>
-      <c r="CE21" s="34"/>
-      <c r="CF21" s="35"/>
+      <c r="CE21" s="35"/>
+      <c r="CF21" s="34"/>
       <c r="CG21" s="33"/>
       <c r="CH21" s="33"/>
       <c r="CI21" s="33"/>
       <c r="CJ21" s="33"/>
       <c r="CK21" s="33"/>
-      <c r="CL21" s="34"/>
-      <c r="CM21" s="35"/>
+      <c r="CL21" s="35"/>
+      <c r="CM21" s="34"/>
       <c r="CN21" s="33"/>
       <c r="CO21" s="33"/>
       <c r="CP21" s="33"/>
       <c r="CQ21" s="33"/>
       <c r="CR21" s="33"/>
-      <c r="CS21" s="34"/>
-      <c r="CT21" s="35"/>
+      <c r="CS21" s="35"/>
+      <c r="CT21" s="34"/>
       <c r="CU21" s="33"/>
       <c r="CV21" s="33"/>
     </row>
@@ -4047,98 +4073,98 @@
       <c r="F22" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G22" s="35"/>
+      <c r="G22" s="34"/>
       <c r="H22" s="33"/>
       <c r="I22" s="33"/>
       <c r="J22" s="33"/>
       <c r="K22" s="33"/>
       <c r="L22" s="33"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="34"/>
       <c r="O22" s="33"/>
       <c r="P22" s="33"/>
       <c r="Q22" s="33"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
-      <c r="T22" s="34"/>
-      <c r="U22" s="35"/>
+      <c r="T22" s="35"/>
+      <c r="U22" s="34"/>
       <c r="V22" s="33"/>
       <c r="W22" s="33"/>
       <c r="X22" s="33"/>
       <c r="Y22" s="33"/>
       <c r="Z22" s="33"/>
-      <c r="AA22" s="34"/>
-      <c r="AB22" s="35"/>
+      <c r="AA22" s="35"/>
+      <c r="AB22" s="34"/>
       <c r="AC22" s="33"/>
       <c r="AD22" s="33"/>
       <c r="AE22" s="33"/>
       <c r="AF22" s="33"/>
       <c r="AG22" s="33"/>
-      <c r="AH22" s="34"/>
-      <c r="AI22" s="35"/>
+      <c r="AH22" s="35"/>
+      <c r="AI22" s="34"/>
       <c r="AJ22" s="33"/>
       <c r="AK22" s="33"/>
       <c r="AL22" s="33"/>
       <c r="AM22" s="33"/>
       <c r="AN22" s="33"/>
-      <c r="AO22" s="34"/>
-      <c r="AP22" s="35"/>
+      <c r="AO22" s="35"/>
+      <c r="AP22" s="34"/>
       <c r="AQ22" s="33"/>
       <c r="AR22" s="33"/>
       <c r="AS22" s="33"/>
       <c r="AT22" s="33"/>
       <c r="AU22" s="33"/>
-      <c r="AV22" s="34"/>
-      <c r="AW22" s="35"/>
+      <c r="AV22" s="35"/>
+      <c r="AW22" s="34"/>
       <c r="AX22" s="33"/>
       <c r="AY22" s="33"/>
       <c r="AZ22" s="33"/>
       <c r="BA22" s="33"/>
       <c r="BB22" s="33"/>
-      <c r="BC22" s="34"/>
-      <c r="BD22" s="35"/>
+      <c r="BC22" s="35"/>
+      <c r="BD22" s="34"/>
       <c r="BE22" s="33"/>
       <c r="BF22" s="33"/>
       <c r="BG22" s="33"/>
       <c r="BH22" s="33"/>
       <c r="BI22" s="33"/>
-      <c r="BJ22" s="34"/>
-      <c r="BK22" s="35"/>
+      <c r="BJ22" s="35"/>
+      <c r="BK22" s="34"/>
       <c r="BL22" s="33"/>
       <c r="BM22" s="33"/>
       <c r="BN22" s="33"/>
       <c r="BO22" s="33"/>
       <c r="BP22" s="33"/>
-      <c r="BQ22" s="34"/>
-      <c r="BR22" s="35"/>
+      <c r="BQ22" s="35"/>
+      <c r="BR22" s="34"/>
       <c r="BS22" s="33"/>
       <c r="BT22" s="33"/>
       <c r="BU22" s="33"/>
       <c r="BV22" s="33"/>
       <c r="BW22" s="33"/>
-      <c r="BX22" s="34"/>
-      <c r="BY22" s="35"/>
+      <c r="BX22" s="35"/>
+      <c r="BY22" s="34"/>
       <c r="BZ22" s="33"/>
       <c r="CA22" s="33"/>
       <c r="CB22" s="33"/>
       <c r="CC22" s="33"/>
       <c r="CD22" s="33"/>
-      <c r="CE22" s="34"/>
-      <c r="CF22" s="35"/>
+      <c r="CE22" s="35"/>
+      <c r="CF22" s="34"/>
       <c r="CG22" s="33"/>
       <c r="CH22" s="33"/>
       <c r="CI22" s="33"/>
       <c r="CJ22" s="33"/>
       <c r="CK22" s="33"/>
-      <c r="CL22" s="34"/>
-      <c r="CM22" s="35"/>
+      <c r="CL22" s="35"/>
+      <c r="CM22" s="34"/>
       <c r="CN22" s="33"/>
       <c r="CO22" s="33"/>
       <c r="CP22" s="33"/>
       <c r="CQ22" s="33"/>
       <c r="CR22" s="33"/>
-      <c r="CS22" s="34"/>
-      <c r="CT22" s="35"/>
+      <c r="CS22" s="35"/>
+      <c r="CT22" s="34"/>
       <c r="CU22" s="33"/>
       <c r="CV22" s="33"/>
     </row>
@@ -4161,98 +4187,98 @@
       <c r="F23" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G23" s="35"/>
+      <c r="G23" s="34"/>
       <c r="H23" s="33"/>
       <c r="I23" s="33"/>
       <c r="J23" s="33"/>
       <c r="K23" s="33"/>
       <c r="L23" s="33"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="34"/>
       <c r="O23" s="33"/>
       <c r="P23" s="33"/>
       <c r="Q23" s="33"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
-      <c r="T23" s="34"/>
-      <c r="U23" s="35"/>
+      <c r="T23" s="35"/>
+      <c r="U23" s="34"/>
       <c r="V23" s="33"/>
       <c r="W23" s="33"/>
       <c r="X23" s="33"/>
       <c r="Y23" s="33"/>
       <c r="Z23" s="33"/>
-      <c r="AA23" s="34"/>
-      <c r="AB23" s="35"/>
+      <c r="AA23" s="35"/>
+      <c r="AB23" s="34"/>
       <c r="AC23" s="33"/>
       <c r="AD23" s="33"/>
       <c r="AE23" s="33"/>
       <c r="AF23" s="33"/>
       <c r="AG23" s="33"/>
-      <c r="AH23" s="34"/>
-      <c r="AI23" s="35"/>
+      <c r="AH23" s="35"/>
+      <c r="AI23" s="34"/>
       <c r="AJ23" s="33"/>
       <c r="AK23" s="33"/>
       <c r="AL23" s="33"/>
       <c r="AM23" s="33"/>
       <c r="AN23" s="33"/>
-      <c r="AO23" s="34"/>
-      <c r="AP23" s="35"/>
+      <c r="AO23" s="35"/>
+      <c r="AP23" s="34"/>
       <c r="AQ23" s="33"/>
       <c r="AR23" s="33"/>
       <c r="AS23" s="33"/>
       <c r="AT23" s="33"/>
       <c r="AU23" s="33"/>
-      <c r="AV23" s="34"/>
-      <c r="AW23" s="35"/>
+      <c r="AV23" s="35"/>
+      <c r="AW23" s="34"/>
       <c r="AX23" s="33"/>
       <c r="AY23" s="33"/>
       <c r="AZ23" s="33"/>
       <c r="BA23" s="33"/>
       <c r="BB23" s="33"/>
-      <c r="BC23" s="34"/>
-      <c r="BD23" s="35"/>
+      <c r="BC23" s="35"/>
+      <c r="BD23" s="34"/>
       <c r="BE23" s="33"/>
       <c r="BF23" s="33"/>
       <c r="BG23" s="33"/>
       <c r="BH23" s="33"/>
       <c r="BI23" s="33"/>
-      <c r="BJ23" s="34"/>
-      <c r="BK23" s="35"/>
+      <c r="BJ23" s="35"/>
+      <c r="BK23" s="34"/>
       <c r="BL23" s="33"/>
       <c r="BM23" s="33"/>
       <c r="BN23" s="33"/>
       <c r="BO23" s="33"/>
       <c r="BP23" s="33"/>
-      <c r="BQ23" s="34"/>
-      <c r="BR23" s="35"/>
+      <c r="BQ23" s="35"/>
+      <c r="BR23" s="34"/>
       <c r="BS23" s="33"/>
       <c r="BT23" s="33"/>
       <c r="BU23" s="33"/>
       <c r="BV23" s="33"/>
       <c r="BW23" s="33"/>
-      <c r="BX23" s="34"/>
-      <c r="BY23" s="35"/>
+      <c r="BX23" s="35"/>
+      <c r="BY23" s="34"/>
       <c r="BZ23" s="33"/>
       <c r="CA23" s="33"/>
       <c r="CB23" s="33"/>
       <c r="CC23" s="33"/>
       <c r="CD23" s="33"/>
-      <c r="CE23" s="34"/>
-      <c r="CF23" s="35"/>
+      <c r="CE23" s="35"/>
+      <c r="CF23" s="34"/>
       <c r="CG23" s="33"/>
       <c r="CH23" s="33"/>
       <c r="CI23" s="33"/>
       <c r="CJ23" s="33"/>
       <c r="CK23" s="33"/>
-      <c r="CL23" s="34"/>
-      <c r="CM23" s="35"/>
+      <c r="CL23" s="35"/>
+      <c r="CM23" s="34"/>
       <c r="CN23" s="33"/>
       <c r="CO23" s="33"/>
       <c r="CP23" s="33"/>
       <c r="CQ23" s="33"/>
       <c r="CR23" s="33"/>
-      <c r="CS23" s="34"/>
-      <c r="CT23" s="35"/>
+      <c r="CS23" s="35"/>
+      <c r="CT23" s="34"/>
       <c r="CU23" s="33"/>
       <c r="CV23" s="33"/>
     </row>
@@ -4275,98 +4301,98 @@
       <c r="F24" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G24" s="35"/>
+      <c r="G24" s="34"/>
       <c r="H24" s="33"/>
       <c r="I24" s="33"/>
       <c r="J24" s="33"/>
       <c r="K24" s="33"/>
       <c r="L24" s="33"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="34"/>
       <c r="O24" s="33"/>
       <c r="P24" s="33"/>
       <c r="Q24" s="33"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
-      <c r="T24" s="34"/>
-      <c r="U24" s="35"/>
+      <c r="T24" s="35"/>
+      <c r="U24" s="34"/>
       <c r="V24" s="33"/>
       <c r="W24" s="33"/>
       <c r="X24" s="33"/>
       <c r="Y24" s="33"/>
       <c r="Z24" s="33"/>
-      <c r="AA24" s="34"/>
-      <c r="AB24" s="35"/>
+      <c r="AA24" s="35"/>
+      <c r="AB24" s="34"/>
       <c r="AC24" s="33"/>
       <c r="AD24" s="33"/>
       <c r="AE24" s="33"/>
       <c r="AF24" s="33"/>
       <c r="AG24" s="33"/>
-      <c r="AH24" s="34"/>
-      <c r="AI24" s="35"/>
+      <c r="AH24" s="35"/>
+      <c r="AI24" s="34"/>
       <c r="AJ24" s="33"/>
       <c r="AK24" s="33"/>
       <c r="AL24" s="33"/>
       <c r="AM24" s="33"/>
       <c r="AN24" s="33"/>
-      <c r="AO24" s="34"/>
-      <c r="AP24" s="35"/>
+      <c r="AO24" s="35"/>
+      <c r="AP24" s="34"/>
       <c r="AQ24" s="33"/>
       <c r="AR24" s="33"/>
       <c r="AS24" s="33"/>
       <c r="AT24" s="33"/>
       <c r="AU24" s="33"/>
-      <c r="AV24" s="34"/>
-      <c r="AW24" s="35"/>
+      <c r="AV24" s="35"/>
+      <c r="AW24" s="34"/>
       <c r="AX24" s="33"/>
       <c r="AY24" s="33"/>
       <c r="AZ24" s="33"/>
       <c r="BA24" s="33"/>
       <c r="BB24" s="33"/>
-      <c r="BC24" s="34"/>
-      <c r="BD24" s="35"/>
+      <c r="BC24" s="35"/>
+      <c r="BD24" s="34"/>
       <c r="BE24" s="33"/>
       <c r="BF24" s="33"/>
       <c r="BG24" s="33"/>
       <c r="BH24" s="33"/>
       <c r="BI24" s="33"/>
-      <c r="BJ24" s="34"/>
-      <c r="BK24" s="35"/>
+      <c r="BJ24" s="35"/>
+      <c r="BK24" s="34"/>
       <c r="BL24" s="33"/>
       <c r="BM24" s="33"/>
       <c r="BN24" s="33"/>
       <c r="BO24" s="33"/>
       <c r="BP24" s="33"/>
-      <c r="BQ24" s="34"/>
-      <c r="BR24" s="35"/>
+      <c r="BQ24" s="35"/>
+      <c r="BR24" s="34"/>
       <c r="BS24" s="33"/>
       <c r="BT24" s="33"/>
       <c r="BU24" s="33"/>
       <c r="BV24" s="33"/>
       <c r="BW24" s="33"/>
-      <c r="BX24" s="34"/>
-      <c r="BY24" s="35"/>
+      <c r="BX24" s="35"/>
+      <c r="BY24" s="34"/>
       <c r="BZ24" s="33"/>
       <c r="CA24" s="33"/>
       <c r="CB24" s="33"/>
       <c r="CC24" s="33"/>
       <c r="CD24" s="33"/>
-      <c r="CE24" s="34"/>
-      <c r="CF24" s="35"/>
+      <c r="CE24" s="35"/>
+      <c r="CF24" s="34"/>
       <c r="CG24" s="33"/>
       <c r="CH24" s="33"/>
       <c r="CI24" s="33"/>
       <c r="CJ24" s="33"/>
       <c r="CK24" s="33"/>
-      <c r="CL24" s="34"/>
-      <c r="CM24" s="35"/>
+      <c r="CL24" s="35"/>
+      <c r="CM24" s="34"/>
       <c r="CN24" s="33"/>
       <c r="CO24" s="33"/>
       <c r="CP24" s="33"/>
       <c r="CQ24" s="33"/>
       <c r="CR24" s="33"/>
-      <c r="CS24" s="34"/>
-      <c r="CT24" s="35"/>
+      <c r="CS24" s="35"/>
+      <c r="CT24" s="34"/>
       <c r="CU24" s="33"/>
       <c r="CV24" s="33"/>
     </row>

--- a/STL_Study_Tracker.xlsx
+++ b/STL_Study_Tracker.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="174">
   <si>
     <t>STL Topics — Detailed Breakdown</t>
   </si>
@@ -677,12 +677,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8e8e8"/>
+        <fgColor rgb="FFf2f2f2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFf2f2f2"/>
+        <fgColor rgb="FFe8e8e8"/>
       </patternFill>
     </fill>
   </fills>
@@ -1993,84 +1993,86 @@
       <c r="T5" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="U5" s="34"/>
+      <c r="U5" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="V5" s="33"/>
       <c r="W5" s="33"/>
       <c r="X5" s="33"/>
       <c r="Y5" s="33"/>
       <c r="Z5" s="33"/>
-      <c r="AA5" s="35"/>
-      <c r="AB5" s="34"/>
+      <c r="AA5" s="34"/>
+      <c r="AB5" s="35"/>
       <c r="AC5" s="33"/>
       <c r="AD5" s="33"/>
       <c r="AE5" s="33"/>
       <c r="AF5" s="33"/>
       <c r="AG5" s="33"/>
-      <c r="AH5" s="35"/>
-      <c r="AI5" s="34"/>
+      <c r="AH5" s="34"/>
+      <c r="AI5" s="35"/>
       <c r="AJ5" s="33"/>
       <c r="AK5" s="33"/>
       <c r="AL5" s="33"/>
       <c r="AM5" s="33"/>
       <c r="AN5" s="33"/>
-      <c r="AO5" s="35"/>
-      <c r="AP5" s="34"/>
+      <c r="AO5" s="34"/>
+      <c r="AP5" s="35"/>
       <c r="AQ5" s="33"/>
       <c r="AR5" s="33"/>
       <c r="AS5" s="33"/>
       <c r="AT5" s="33"/>
       <c r="AU5" s="33"/>
-      <c r="AV5" s="35"/>
-      <c r="AW5" s="34"/>
+      <c r="AV5" s="34"/>
+      <c r="AW5" s="35"/>
       <c r="AX5" s="33"/>
       <c r="AY5" s="33"/>
       <c r="AZ5" s="33"/>
       <c r="BA5" s="33"/>
       <c r="BB5" s="33"/>
-      <c r="BC5" s="35"/>
-      <c r="BD5" s="34"/>
+      <c r="BC5" s="34"/>
+      <c r="BD5" s="35"/>
       <c r="BE5" s="33"/>
       <c r="BF5" s="33"/>
       <c r="BG5" s="33"/>
       <c r="BH5" s="33"/>
       <c r="BI5" s="33"/>
-      <c r="BJ5" s="35"/>
-      <c r="BK5" s="34"/>
+      <c r="BJ5" s="34"/>
+      <c r="BK5" s="35"/>
       <c r="BL5" s="33"/>
       <c r="BM5" s="33"/>
       <c r="BN5" s="33"/>
       <c r="BO5" s="33"/>
       <c r="BP5" s="33"/>
-      <c r="BQ5" s="35"/>
-      <c r="BR5" s="34"/>
+      <c r="BQ5" s="34"/>
+      <c r="BR5" s="35"/>
       <c r="BS5" s="33"/>
       <c r="BT5" s="33"/>
       <c r="BU5" s="33"/>
       <c r="BV5" s="33"/>
       <c r="BW5" s="33"/>
-      <c r="BX5" s="35"/>
-      <c r="BY5" s="34"/>
+      <c r="BX5" s="34"/>
+      <c r="BY5" s="35"/>
       <c r="BZ5" s="33"/>
       <c r="CA5" s="33"/>
       <c r="CB5" s="33"/>
       <c r="CC5" s="33"/>
       <c r="CD5" s="33"/>
-      <c r="CE5" s="35"/>
-      <c r="CF5" s="34"/>
+      <c r="CE5" s="34"/>
+      <c r="CF5" s="35"/>
       <c r="CG5" s="33"/>
       <c r="CH5" s="33"/>
       <c r="CI5" s="33"/>
       <c r="CJ5" s="33"/>
       <c r="CK5" s="33"/>
-      <c r="CL5" s="35"/>
-      <c r="CM5" s="34"/>
+      <c r="CL5" s="34"/>
+      <c r="CM5" s="35"/>
       <c r="CN5" s="33"/>
       <c r="CO5" s="33"/>
       <c r="CP5" s="33"/>
       <c r="CQ5" s="33"/>
       <c r="CR5" s="33"/>
-      <c r="CS5" s="35"/>
-      <c r="CT5" s="34"/>
+      <c r="CS5" s="34"/>
+      <c r="CT5" s="35"/>
       <c r="CU5" s="33"/>
       <c r="CV5" s="33"/>
     </row>
@@ -2093,7 +2095,7 @@
       <c r="F6" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="35"/>
       <c r="H6" s="33"/>
       <c r="I6" s="33" t="s">
         <v>173</v>
@@ -2131,84 +2133,86 @@
       <c r="T6" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="U6" s="34"/>
+      <c r="U6" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="V6" s="33"/>
       <c r="W6" s="33"/>
       <c r="X6" s="33"/>
       <c r="Y6" s="33"/>
       <c r="Z6" s="33"/>
-      <c r="AA6" s="35"/>
-      <c r="AB6" s="34"/>
+      <c r="AA6" s="34"/>
+      <c r="AB6" s="35"/>
       <c r="AC6" s="33"/>
       <c r="AD6" s="33"/>
       <c r="AE6" s="33"/>
       <c r="AF6" s="33"/>
       <c r="AG6" s="33"/>
-      <c r="AH6" s="35"/>
-      <c r="AI6" s="34"/>
+      <c r="AH6" s="34"/>
+      <c r="AI6" s="35"/>
       <c r="AJ6" s="33"/>
       <c r="AK6" s="33"/>
       <c r="AL6" s="33"/>
       <c r="AM6" s="33"/>
       <c r="AN6" s="33"/>
-      <c r="AO6" s="35"/>
-      <c r="AP6" s="34"/>
+      <c r="AO6" s="34"/>
+      <c r="AP6" s="35"/>
       <c r="AQ6" s="33"/>
       <c r="AR6" s="33"/>
       <c r="AS6" s="33"/>
       <c r="AT6" s="33"/>
       <c r="AU6" s="33"/>
-      <c r="AV6" s="35"/>
-      <c r="AW6" s="34"/>
+      <c r="AV6" s="34"/>
+      <c r="AW6" s="35"/>
       <c r="AX6" s="33"/>
       <c r="AY6" s="33"/>
       <c r="AZ6" s="33"/>
       <c r="BA6" s="33"/>
       <c r="BB6" s="33"/>
-      <c r="BC6" s="35"/>
-      <c r="BD6" s="34"/>
+      <c r="BC6" s="34"/>
+      <c r="BD6" s="35"/>
       <c r="BE6" s="33"/>
       <c r="BF6" s="33"/>
       <c r="BG6" s="33"/>
       <c r="BH6" s="33"/>
       <c r="BI6" s="33"/>
-      <c r="BJ6" s="35"/>
-      <c r="BK6" s="34"/>
+      <c r="BJ6" s="34"/>
+      <c r="BK6" s="35"/>
       <c r="BL6" s="33"/>
       <c r="BM6" s="33"/>
       <c r="BN6" s="33"/>
       <c r="BO6" s="33"/>
       <c r="BP6" s="33"/>
-      <c r="BQ6" s="35"/>
-      <c r="BR6" s="34"/>
+      <c r="BQ6" s="34"/>
+      <c r="BR6" s="35"/>
       <c r="BS6" s="33"/>
       <c r="BT6" s="33"/>
       <c r="BU6" s="33"/>
       <c r="BV6" s="33"/>
       <c r="BW6" s="33"/>
-      <c r="BX6" s="35"/>
-      <c r="BY6" s="34"/>
+      <c r="BX6" s="34"/>
+      <c r="BY6" s="35"/>
       <c r="BZ6" s="33"/>
       <c r="CA6" s="33"/>
       <c r="CB6" s="33"/>
       <c r="CC6" s="33"/>
       <c r="CD6" s="33"/>
-      <c r="CE6" s="35"/>
-      <c r="CF6" s="34"/>
+      <c r="CE6" s="34"/>
+      <c r="CF6" s="35"/>
       <c r="CG6" s="33"/>
       <c r="CH6" s="33"/>
       <c r="CI6" s="33"/>
       <c r="CJ6" s="33"/>
       <c r="CK6" s="33"/>
-      <c r="CL6" s="35"/>
-      <c r="CM6" s="34"/>
+      <c r="CL6" s="34"/>
+      <c r="CM6" s="35"/>
       <c r="CN6" s="33"/>
       <c r="CO6" s="33"/>
       <c r="CP6" s="33"/>
       <c r="CQ6" s="33"/>
       <c r="CR6" s="33"/>
-      <c r="CS6" s="35"/>
-      <c r="CT6" s="34"/>
+      <c r="CS6" s="34"/>
+      <c r="CT6" s="35"/>
       <c r="CU6" s="33"/>
       <c r="CV6" s="33"/>
     </row>
@@ -2231,7 +2235,7 @@
       <c r="F7" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
       <c r="J7" s="33" t="s">
@@ -2267,84 +2271,86 @@
       <c r="T7" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="U7" s="34"/>
+      <c r="U7" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="V7" s="33"/>
       <c r="W7" s="33"/>
       <c r="X7" s="33"/>
       <c r="Y7" s="33"/>
       <c r="Z7" s="33"/>
-      <c r="AA7" s="35"/>
-      <c r="AB7" s="34"/>
+      <c r="AA7" s="34"/>
+      <c r="AB7" s="35"/>
       <c r="AC7" s="33"/>
       <c r="AD7" s="33"/>
       <c r="AE7" s="33"/>
       <c r="AF7" s="33"/>
       <c r="AG7" s="33"/>
-      <c r="AH7" s="35"/>
-      <c r="AI7" s="34"/>
+      <c r="AH7" s="34"/>
+      <c r="AI7" s="35"/>
       <c r="AJ7" s="33"/>
       <c r="AK7" s="33"/>
       <c r="AL7" s="33"/>
       <c r="AM7" s="33"/>
       <c r="AN7" s="33"/>
-      <c r="AO7" s="35"/>
-      <c r="AP7" s="34"/>
+      <c r="AO7" s="34"/>
+      <c r="AP7" s="35"/>
       <c r="AQ7" s="33"/>
       <c r="AR7" s="33"/>
       <c r="AS7" s="33"/>
       <c r="AT7" s="33"/>
       <c r="AU7" s="33"/>
-      <c r="AV7" s="35"/>
-      <c r="AW7" s="34"/>
+      <c r="AV7" s="34"/>
+      <c r="AW7" s="35"/>
       <c r="AX7" s="33"/>
       <c r="AY7" s="33"/>
       <c r="AZ7" s="33"/>
       <c r="BA7" s="33"/>
       <c r="BB7" s="33"/>
-      <c r="BC7" s="35"/>
-      <c r="BD7" s="34"/>
+      <c r="BC7" s="34"/>
+      <c r="BD7" s="35"/>
       <c r="BE7" s="33"/>
       <c r="BF7" s="33"/>
       <c r="BG7" s="33"/>
       <c r="BH7" s="33"/>
       <c r="BI7" s="33"/>
-      <c r="BJ7" s="35"/>
-      <c r="BK7" s="34"/>
+      <c r="BJ7" s="34"/>
+      <c r="BK7" s="35"/>
       <c r="BL7" s="33"/>
       <c r="BM7" s="33"/>
       <c r="BN7" s="33"/>
       <c r="BO7" s="33"/>
       <c r="BP7" s="33"/>
-      <c r="BQ7" s="35"/>
-      <c r="BR7" s="34"/>
+      <c r="BQ7" s="34"/>
+      <c r="BR7" s="35"/>
       <c r="BS7" s="33"/>
       <c r="BT7" s="33"/>
       <c r="BU7" s="33"/>
       <c r="BV7" s="33"/>
       <c r="BW7" s="33"/>
-      <c r="BX7" s="35"/>
-      <c r="BY7" s="34"/>
+      <c r="BX7" s="34"/>
+      <c r="BY7" s="35"/>
       <c r="BZ7" s="33"/>
       <c r="CA7" s="33"/>
       <c r="CB7" s="33"/>
       <c r="CC7" s="33"/>
       <c r="CD7" s="33"/>
-      <c r="CE7" s="35"/>
-      <c r="CF7" s="34"/>
+      <c r="CE7" s="34"/>
+      <c r="CF7" s="35"/>
       <c r="CG7" s="33"/>
       <c r="CH7" s="33"/>
       <c r="CI7" s="33"/>
       <c r="CJ7" s="33"/>
       <c r="CK7" s="33"/>
-      <c r="CL7" s="35"/>
-      <c r="CM7" s="34"/>
+      <c r="CL7" s="34"/>
+      <c r="CM7" s="35"/>
       <c r="CN7" s="33"/>
       <c r="CO7" s="33"/>
       <c r="CP7" s="33"/>
       <c r="CQ7" s="33"/>
       <c r="CR7" s="33"/>
-      <c r="CS7" s="35"/>
-      <c r="CT7" s="34"/>
+      <c r="CS7" s="34"/>
+      <c r="CT7" s="35"/>
       <c r="CU7" s="33"/>
       <c r="CV7" s="33"/>
     </row>
@@ -2367,7 +2373,7 @@
       <c r="F8" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="35"/>
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
       <c r="J8" s="33"/>
@@ -2401,84 +2407,86 @@
       <c r="T8" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="U8" s="34"/>
+      <c r="U8" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="V8" s="33"/>
       <c r="W8" s="33"/>
       <c r="X8" s="33"/>
       <c r="Y8" s="33"/>
       <c r="Z8" s="33"/>
-      <c r="AA8" s="35"/>
-      <c r="AB8" s="34"/>
+      <c r="AA8" s="34"/>
+      <c r="AB8" s="35"/>
       <c r="AC8" s="33"/>
       <c r="AD8" s="33"/>
       <c r="AE8" s="33"/>
       <c r="AF8" s="33"/>
       <c r="AG8" s="33"/>
-      <c r="AH8" s="35"/>
-      <c r="AI8" s="34"/>
+      <c r="AH8" s="34"/>
+      <c r="AI8" s="35"/>
       <c r="AJ8" s="33"/>
       <c r="AK8" s="33"/>
       <c r="AL8" s="33"/>
       <c r="AM8" s="33"/>
       <c r="AN8" s="33"/>
-      <c r="AO8" s="35"/>
-      <c r="AP8" s="34"/>
+      <c r="AO8" s="34"/>
+      <c r="AP8" s="35"/>
       <c r="AQ8" s="33"/>
       <c r="AR8" s="33"/>
       <c r="AS8" s="33"/>
       <c r="AT8" s="33"/>
       <c r="AU8" s="33"/>
-      <c r="AV8" s="35"/>
-      <c r="AW8" s="34"/>
+      <c r="AV8" s="34"/>
+      <c r="AW8" s="35"/>
       <c r="AX8" s="33"/>
       <c r="AY8" s="33"/>
       <c r="AZ8" s="33"/>
       <c r="BA8" s="33"/>
       <c r="BB8" s="33"/>
-      <c r="BC8" s="35"/>
-      <c r="BD8" s="34"/>
+      <c r="BC8" s="34"/>
+      <c r="BD8" s="35"/>
       <c r="BE8" s="33"/>
       <c r="BF8" s="33"/>
       <c r="BG8" s="33"/>
       <c r="BH8" s="33"/>
       <c r="BI8" s="33"/>
-      <c r="BJ8" s="35"/>
-      <c r="BK8" s="34"/>
+      <c r="BJ8" s="34"/>
+      <c r="BK8" s="35"/>
       <c r="BL8" s="33"/>
       <c r="BM8" s="33"/>
       <c r="BN8" s="33"/>
       <c r="BO8" s="33"/>
       <c r="BP8" s="33"/>
-      <c r="BQ8" s="35"/>
-      <c r="BR8" s="34"/>
+      <c r="BQ8" s="34"/>
+      <c r="BR8" s="35"/>
       <c r="BS8" s="33"/>
       <c r="BT8" s="33"/>
       <c r="BU8" s="33"/>
       <c r="BV8" s="33"/>
       <c r="BW8" s="33"/>
-      <c r="BX8" s="35"/>
-      <c r="BY8" s="34"/>
+      <c r="BX8" s="34"/>
+      <c r="BY8" s="35"/>
       <c r="BZ8" s="33"/>
       <c r="CA8" s="33"/>
       <c r="CB8" s="33"/>
       <c r="CC8" s="33"/>
       <c r="CD8" s="33"/>
-      <c r="CE8" s="35"/>
-      <c r="CF8" s="34"/>
+      <c r="CE8" s="34"/>
+      <c r="CF8" s="35"/>
       <c r="CG8" s="33"/>
       <c r="CH8" s="33"/>
       <c r="CI8" s="33"/>
       <c r="CJ8" s="33"/>
       <c r="CK8" s="33"/>
-      <c r="CL8" s="35"/>
-      <c r="CM8" s="34"/>
+      <c r="CL8" s="34"/>
+      <c r="CM8" s="35"/>
       <c r="CN8" s="33"/>
       <c r="CO8" s="33"/>
       <c r="CP8" s="33"/>
       <c r="CQ8" s="33"/>
       <c r="CR8" s="33"/>
-      <c r="CS8" s="35"/>
-      <c r="CT8" s="34"/>
+      <c r="CS8" s="34"/>
+      <c r="CT8" s="35"/>
       <c r="CU8" s="33"/>
       <c r="CV8" s="33"/>
     </row>
@@ -2501,7 +2509,7 @@
       <c r="F9" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
       <c r="J9" s="33"/>
@@ -2533,84 +2541,86 @@
       <c r="T9" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="U9" s="34"/>
+      <c r="U9" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="V9" s="33"/>
       <c r="W9" s="33"/>
       <c r="X9" s="33"/>
       <c r="Y9" s="33"/>
       <c r="Z9" s="33"/>
-      <c r="AA9" s="35"/>
-      <c r="AB9" s="34"/>
+      <c r="AA9" s="34"/>
+      <c r="AB9" s="35"/>
       <c r="AC9" s="33"/>
       <c r="AD9" s="33"/>
       <c r="AE9" s="33"/>
       <c r="AF9" s="33"/>
       <c r="AG9" s="33"/>
-      <c r="AH9" s="35"/>
-      <c r="AI9" s="34"/>
+      <c r="AH9" s="34"/>
+      <c r="AI9" s="35"/>
       <c r="AJ9" s="33"/>
       <c r="AK9" s="33"/>
       <c r="AL9" s="33"/>
       <c r="AM9" s="33"/>
       <c r="AN9" s="33"/>
-      <c r="AO9" s="35"/>
-      <c r="AP9" s="34"/>
+      <c r="AO9" s="34"/>
+      <c r="AP9" s="35"/>
       <c r="AQ9" s="33"/>
       <c r="AR9" s="33"/>
       <c r="AS9" s="33"/>
       <c r="AT9" s="33"/>
       <c r="AU9" s="33"/>
-      <c r="AV9" s="35"/>
-      <c r="AW9" s="34"/>
+      <c r="AV9" s="34"/>
+      <c r="AW9" s="35"/>
       <c r="AX9" s="33"/>
       <c r="AY9" s="33"/>
       <c r="AZ9" s="33"/>
       <c r="BA9" s="33"/>
       <c r="BB9" s="33"/>
-      <c r="BC9" s="35"/>
-      <c r="BD9" s="34"/>
+      <c r="BC9" s="34"/>
+      <c r="BD9" s="35"/>
       <c r="BE9" s="33"/>
       <c r="BF9" s="33"/>
       <c r="BG9" s="33"/>
       <c r="BH9" s="33"/>
       <c r="BI9" s="33"/>
-      <c r="BJ9" s="35"/>
-      <c r="BK9" s="34"/>
+      <c r="BJ9" s="34"/>
+      <c r="BK9" s="35"/>
       <c r="BL9" s="33"/>
       <c r="BM9" s="33"/>
       <c r="BN9" s="33"/>
       <c r="BO9" s="33"/>
       <c r="BP9" s="33"/>
-      <c r="BQ9" s="35"/>
-      <c r="BR9" s="34"/>
+      <c r="BQ9" s="34"/>
+      <c r="BR9" s="35"/>
       <c r="BS9" s="33"/>
       <c r="BT9" s="33"/>
       <c r="BU9" s="33"/>
       <c r="BV9" s="33"/>
       <c r="BW9" s="33"/>
-      <c r="BX9" s="35"/>
-      <c r="BY9" s="34"/>
+      <c r="BX9" s="34"/>
+      <c r="BY9" s="35"/>
       <c r="BZ9" s="33"/>
       <c r="CA9" s="33"/>
       <c r="CB9" s="33"/>
       <c r="CC9" s="33"/>
       <c r="CD9" s="33"/>
-      <c r="CE9" s="35"/>
-      <c r="CF9" s="34"/>
+      <c r="CE9" s="34"/>
+      <c r="CF9" s="35"/>
       <c r="CG9" s="33"/>
       <c r="CH9" s="33"/>
       <c r="CI9" s="33"/>
       <c r="CJ9" s="33"/>
       <c r="CK9" s="33"/>
-      <c r="CL9" s="35"/>
-      <c r="CM9" s="34"/>
+      <c r="CL9" s="34"/>
+      <c r="CM9" s="35"/>
       <c r="CN9" s="33"/>
       <c r="CO9" s="33"/>
       <c r="CP9" s="33"/>
       <c r="CQ9" s="33"/>
       <c r="CR9" s="33"/>
-      <c r="CS9" s="35"/>
-      <c r="CT9" s="34"/>
+      <c r="CS9" s="34"/>
+      <c r="CT9" s="35"/>
       <c r="CU9" s="33"/>
       <c r="CV9" s="33"/>
     </row>
@@ -2633,7 +2643,7 @@
       <c r="F10" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="35"/>
       <c r="H10" s="33"/>
       <c r="I10" s="33"/>
       <c r="J10" s="33"/>
@@ -2663,84 +2673,86 @@
       <c r="T10" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="U10" s="34"/>
+      <c r="U10" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="V10" s="33"/>
       <c r="W10" s="33"/>
       <c r="X10" s="33"/>
       <c r="Y10" s="33"/>
       <c r="Z10" s="33"/>
-      <c r="AA10" s="35"/>
-      <c r="AB10" s="34"/>
+      <c r="AA10" s="34"/>
+      <c r="AB10" s="35"/>
       <c r="AC10" s="33"/>
       <c r="AD10" s="33"/>
       <c r="AE10" s="33"/>
       <c r="AF10" s="33"/>
       <c r="AG10" s="33"/>
-      <c r="AH10" s="35"/>
-      <c r="AI10" s="34"/>
+      <c r="AH10" s="34"/>
+      <c r="AI10" s="35"/>
       <c r="AJ10" s="33"/>
       <c r="AK10" s="33"/>
       <c r="AL10" s="33"/>
       <c r="AM10" s="33"/>
       <c r="AN10" s="33"/>
-      <c r="AO10" s="35"/>
-      <c r="AP10" s="34"/>
+      <c r="AO10" s="34"/>
+      <c r="AP10" s="35"/>
       <c r="AQ10" s="33"/>
       <c r="AR10" s="33"/>
       <c r="AS10" s="33"/>
       <c r="AT10" s="33"/>
       <c r="AU10" s="33"/>
-      <c r="AV10" s="35"/>
-      <c r="AW10" s="34"/>
+      <c r="AV10" s="34"/>
+      <c r="AW10" s="35"/>
       <c r="AX10" s="33"/>
       <c r="AY10" s="33"/>
       <c r="AZ10" s="33"/>
       <c r="BA10" s="33"/>
       <c r="BB10" s="33"/>
-      <c r="BC10" s="35"/>
-      <c r="BD10" s="34"/>
+      <c r="BC10" s="34"/>
+      <c r="BD10" s="35"/>
       <c r="BE10" s="33"/>
       <c r="BF10" s="33"/>
       <c r="BG10" s="33"/>
       <c r="BH10" s="33"/>
       <c r="BI10" s="33"/>
-      <c r="BJ10" s="35"/>
-      <c r="BK10" s="34"/>
+      <c r="BJ10" s="34"/>
+      <c r="BK10" s="35"/>
       <c r="BL10" s="33"/>
       <c r="BM10" s="33"/>
       <c r="BN10" s="33"/>
       <c r="BO10" s="33"/>
       <c r="BP10" s="33"/>
-      <c r="BQ10" s="35"/>
-      <c r="BR10" s="34"/>
+      <c r="BQ10" s="34"/>
+      <c r="BR10" s="35"/>
       <c r="BS10" s="33"/>
       <c r="BT10" s="33"/>
       <c r="BU10" s="33"/>
       <c r="BV10" s="33"/>
       <c r="BW10" s="33"/>
-      <c r="BX10" s="35"/>
-      <c r="BY10" s="34"/>
+      <c r="BX10" s="34"/>
+      <c r="BY10" s="35"/>
       <c r="BZ10" s="33"/>
       <c r="CA10" s="33"/>
       <c r="CB10" s="33"/>
       <c r="CC10" s="33"/>
       <c r="CD10" s="33"/>
-      <c r="CE10" s="35"/>
-      <c r="CF10" s="34"/>
+      <c r="CE10" s="34"/>
+      <c r="CF10" s="35"/>
       <c r="CG10" s="33"/>
       <c r="CH10" s="33"/>
       <c r="CI10" s="33"/>
       <c r="CJ10" s="33"/>
       <c r="CK10" s="33"/>
-      <c r="CL10" s="35"/>
-      <c r="CM10" s="34"/>
+      <c r="CL10" s="34"/>
+      <c r="CM10" s="35"/>
       <c r="CN10" s="33"/>
       <c r="CO10" s="33"/>
       <c r="CP10" s="33"/>
       <c r="CQ10" s="33"/>
       <c r="CR10" s="33"/>
-      <c r="CS10" s="35"/>
-      <c r="CT10" s="34"/>
+      <c r="CS10" s="34"/>
+      <c r="CT10" s="35"/>
       <c r="CU10" s="33"/>
       <c r="CV10" s="33"/>
     </row>
@@ -2763,13 +2775,13 @@
       <c r="F11" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G11" s="34"/>
+      <c r="G11" s="35"/>
       <c r="H11" s="33"/>
       <c r="I11" s="33"/>
       <c r="J11" s="33"/>
       <c r="K11" s="33"/>
       <c r="L11" s="33"/>
-      <c r="M11" s="35"/>
+      <c r="M11" s="34"/>
       <c r="N11" s="33" t="s">
         <v>173</v>
       </c>
@@ -2791,84 +2803,86 @@
       <c r="T11" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="U11" s="34"/>
+      <c r="U11" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="V11" s="33"/>
       <c r="W11" s="33"/>
       <c r="X11" s="33"/>
       <c r="Y11" s="33"/>
       <c r="Z11" s="33"/>
-      <c r="AA11" s="35"/>
-      <c r="AB11" s="34"/>
+      <c r="AA11" s="34"/>
+      <c r="AB11" s="35"/>
       <c r="AC11" s="33"/>
       <c r="AD11" s="33"/>
       <c r="AE11" s="33"/>
       <c r="AF11" s="33"/>
       <c r="AG11" s="33"/>
-      <c r="AH11" s="35"/>
-      <c r="AI11" s="34"/>
+      <c r="AH11" s="34"/>
+      <c r="AI11" s="35"/>
       <c r="AJ11" s="33"/>
       <c r="AK11" s="33"/>
       <c r="AL11" s="33"/>
       <c r="AM11" s="33"/>
       <c r="AN11" s="33"/>
-      <c r="AO11" s="35"/>
-      <c r="AP11" s="34"/>
+      <c r="AO11" s="34"/>
+      <c r="AP11" s="35"/>
       <c r="AQ11" s="33"/>
       <c r="AR11" s="33"/>
       <c r="AS11" s="33"/>
       <c r="AT11" s="33"/>
       <c r="AU11" s="33"/>
-      <c r="AV11" s="35"/>
-      <c r="AW11" s="34"/>
+      <c r="AV11" s="34"/>
+      <c r="AW11" s="35"/>
       <c r="AX11" s="33"/>
       <c r="AY11" s="33"/>
       <c r="AZ11" s="33"/>
       <c r="BA11" s="33"/>
       <c r="BB11" s="33"/>
-      <c r="BC11" s="35"/>
-      <c r="BD11" s="34"/>
+      <c r="BC11" s="34"/>
+      <c r="BD11" s="35"/>
       <c r="BE11" s="33"/>
       <c r="BF11" s="33"/>
       <c r="BG11" s="33"/>
       <c r="BH11" s="33"/>
       <c r="BI11" s="33"/>
-      <c r="BJ11" s="35"/>
-      <c r="BK11" s="34"/>
+      <c r="BJ11" s="34"/>
+      <c r="BK11" s="35"/>
       <c r="BL11" s="33"/>
       <c r="BM11" s="33"/>
       <c r="BN11" s="33"/>
       <c r="BO11" s="33"/>
       <c r="BP11" s="33"/>
-      <c r="BQ11" s="35"/>
-      <c r="BR11" s="34"/>
+      <c r="BQ11" s="34"/>
+      <c r="BR11" s="35"/>
       <c r="BS11" s="33"/>
       <c r="BT11" s="33"/>
       <c r="BU11" s="33"/>
       <c r="BV11" s="33"/>
       <c r="BW11" s="33"/>
-      <c r="BX11" s="35"/>
-      <c r="BY11" s="34"/>
+      <c r="BX11" s="34"/>
+      <c r="BY11" s="35"/>
       <c r="BZ11" s="33"/>
       <c r="CA11" s="33"/>
       <c r="CB11" s="33"/>
       <c r="CC11" s="33"/>
       <c r="CD11" s="33"/>
-      <c r="CE11" s="35"/>
-      <c r="CF11" s="34"/>
+      <c r="CE11" s="34"/>
+      <c r="CF11" s="35"/>
       <c r="CG11" s="33"/>
       <c r="CH11" s="33"/>
       <c r="CI11" s="33"/>
       <c r="CJ11" s="33"/>
       <c r="CK11" s="33"/>
-      <c r="CL11" s="35"/>
-      <c r="CM11" s="34"/>
+      <c r="CL11" s="34"/>
+      <c r="CM11" s="35"/>
       <c r="CN11" s="33"/>
       <c r="CO11" s="33"/>
       <c r="CP11" s="33"/>
       <c r="CQ11" s="33"/>
       <c r="CR11" s="33"/>
-      <c r="CS11" s="35"/>
-      <c r="CT11" s="34"/>
+      <c r="CS11" s="34"/>
+      <c r="CT11" s="35"/>
       <c r="CU11" s="33"/>
       <c r="CV11" s="33"/>
     </row>
@@ -2891,14 +2905,14 @@
       <c r="F12" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G12" s="34"/>
+      <c r="G12" s="35"/>
       <c r="H12" s="33"/>
       <c r="I12" s="33"/>
       <c r="J12" s="33"/>
       <c r="K12" s="33"/>
       <c r="L12" s="33"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="34"/>
+      <c r="M12" s="34"/>
+      <c r="N12" s="35"/>
       <c r="O12" s="33" t="s">
         <v>173</v>
       </c>
@@ -2917,84 +2931,86 @@
       <c r="T12" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="U12" s="34"/>
+      <c r="U12" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="V12" s="33"/>
       <c r="W12" s="33"/>
       <c r="X12" s="33"/>
       <c r="Y12" s="33"/>
       <c r="Z12" s="33"/>
-      <c r="AA12" s="35"/>
-      <c r="AB12" s="34"/>
+      <c r="AA12" s="34"/>
+      <c r="AB12" s="35"/>
       <c r="AC12" s="33"/>
       <c r="AD12" s="33"/>
       <c r="AE12" s="33"/>
       <c r="AF12" s="33"/>
       <c r="AG12" s="33"/>
-      <c r="AH12" s="35"/>
-      <c r="AI12" s="34"/>
+      <c r="AH12" s="34"/>
+      <c r="AI12" s="35"/>
       <c r="AJ12" s="33"/>
       <c r="AK12" s="33"/>
       <c r="AL12" s="33"/>
       <c r="AM12" s="33"/>
       <c r="AN12" s="33"/>
-      <c r="AO12" s="35"/>
-      <c r="AP12" s="34"/>
+      <c r="AO12" s="34"/>
+      <c r="AP12" s="35"/>
       <c r="AQ12" s="33"/>
       <c r="AR12" s="33"/>
       <c r="AS12" s="33"/>
       <c r="AT12" s="33"/>
       <c r="AU12" s="33"/>
-      <c r="AV12" s="35"/>
-      <c r="AW12" s="34"/>
+      <c r="AV12" s="34"/>
+      <c r="AW12" s="35"/>
       <c r="AX12" s="33"/>
       <c r="AY12" s="33"/>
       <c r="AZ12" s="33"/>
       <c r="BA12" s="33"/>
       <c r="BB12" s="33"/>
-      <c r="BC12" s="35"/>
-      <c r="BD12" s="34"/>
+      <c r="BC12" s="34"/>
+      <c r="BD12" s="35"/>
       <c r="BE12" s="33"/>
       <c r="BF12" s="33"/>
       <c r="BG12" s="33"/>
       <c r="BH12" s="33"/>
       <c r="BI12" s="33"/>
-      <c r="BJ12" s="35"/>
-      <c r="BK12" s="34"/>
+      <c r="BJ12" s="34"/>
+      <c r="BK12" s="35"/>
       <c r="BL12" s="33"/>
       <c r="BM12" s="33"/>
       <c r="BN12" s="33"/>
       <c r="BO12" s="33"/>
       <c r="BP12" s="33"/>
-      <c r="BQ12" s="35"/>
-      <c r="BR12" s="34"/>
+      <c r="BQ12" s="34"/>
+      <c r="BR12" s="35"/>
       <c r="BS12" s="33"/>
       <c r="BT12" s="33"/>
       <c r="BU12" s="33"/>
       <c r="BV12" s="33"/>
       <c r="BW12" s="33"/>
-      <c r="BX12" s="35"/>
-      <c r="BY12" s="34"/>
+      <c r="BX12" s="34"/>
+      <c r="BY12" s="35"/>
       <c r="BZ12" s="33"/>
       <c r="CA12" s="33"/>
       <c r="CB12" s="33"/>
       <c r="CC12" s="33"/>
       <c r="CD12" s="33"/>
-      <c r="CE12" s="35"/>
-      <c r="CF12" s="34"/>
+      <c r="CE12" s="34"/>
+      <c r="CF12" s="35"/>
       <c r="CG12" s="33"/>
       <c r="CH12" s="33"/>
       <c r="CI12" s="33"/>
       <c r="CJ12" s="33"/>
       <c r="CK12" s="33"/>
-      <c r="CL12" s="35"/>
-      <c r="CM12" s="34"/>
+      <c r="CL12" s="34"/>
+      <c r="CM12" s="35"/>
       <c r="CN12" s="33"/>
       <c r="CO12" s="33"/>
       <c r="CP12" s="33"/>
       <c r="CQ12" s="33"/>
       <c r="CR12" s="33"/>
-      <c r="CS12" s="35"/>
-      <c r="CT12" s="34"/>
+      <c r="CS12" s="34"/>
+      <c r="CT12" s="35"/>
       <c r="CU12" s="33"/>
       <c r="CV12" s="33"/>
     </row>
@@ -3017,14 +3033,14 @@
       <c r="F13" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G13" s="34"/>
+      <c r="G13" s="35"/>
       <c r="H13" s="33"/>
       <c r="I13" s="33"/>
       <c r="J13" s="33"/>
       <c r="K13" s="33"/>
       <c r="L13" s="33"/>
-      <c r="M13" s="35"/>
-      <c r="N13" s="34"/>
+      <c r="M13" s="34"/>
+      <c r="N13" s="35"/>
       <c r="O13" s="33"/>
       <c r="P13" s="33" t="s">
         <v>173</v>
@@ -3041,84 +3057,86 @@
       <c r="T13" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="U13" s="34"/>
+      <c r="U13" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="V13" s="33"/>
       <c r="W13" s="33"/>
       <c r="X13" s="33"/>
       <c r="Y13" s="33"/>
       <c r="Z13" s="33"/>
-      <c r="AA13" s="35"/>
-      <c r="AB13" s="34"/>
+      <c r="AA13" s="34"/>
+      <c r="AB13" s="35"/>
       <c r="AC13" s="33"/>
       <c r="AD13" s="33"/>
       <c r="AE13" s="33"/>
       <c r="AF13" s="33"/>
       <c r="AG13" s="33"/>
-      <c r="AH13" s="35"/>
-      <c r="AI13" s="34"/>
+      <c r="AH13" s="34"/>
+      <c r="AI13" s="35"/>
       <c r="AJ13" s="33"/>
       <c r="AK13" s="33"/>
       <c r="AL13" s="33"/>
       <c r="AM13" s="33"/>
       <c r="AN13" s="33"/>
-      <c r="AO13" s="35"/>
-      <c r="AP13" s="34"/>
+      <c r="AO13" s="34"/>
+      <c r="AP13" s="35"/>
       <c r="AQ13" s="33"/>
       <c r="AR13" s="33"/>
       <c r="AS13" s="33"/>
       <c r="AT13" s="33"/>
       <c r="AU13" s="33"/>
-      <c r="AV13" s="35"/>
-      <c r="AW13" s="34"/>
+      <c r="AV13" s="34"/>
+      <c r="AW13" s="35"/>
       <c r="AX13" s="33"/>
       <c r="AY13" s="33"/>
       <c r="AZ13" s="33"/>
       <c r="BA13" s="33"/>
       <c r="BB13" s="33"/>
-      <c r="BC13" s="35"/>
-      <c r="BD13" s="34"/>
+      <c r="BC13" s="34"/>
+      <c r="BD13" s="35"/>
       <c r="BE13" s="33"/>
       <c r="BF13" s="33"/>
       <c r="BG13" s="33"/>
       <c r="BH13" s="33"/>
       <c r="BI13" s="33"/>
-      <c r="BJ13" s="35"/>
-      <c r="BK13" s="34"/>
+      <c r="BJ13" s="34"/>
+      <c r="BK13" s="35"/>
       <c r="BL13" s="33"/>
       <c r="BM13" s="33"/>
       <c r="BN13" s="33"/>
       <c r="BO13" s="33"/>
       <c r="BP13" s="33"/>
-      <c r="BQ13" s="35"/>
-      <c r="BR13" s="34"/>
+      <c r="BQ13" s="34"/>
+      <c r="BR13" s="35"/>
       <c r="BS13" s="33"/>
       <c r="BT13" s="33"/>
       <c r="BU13" s="33"/>
       <c r="BV13" s="33"/>
       <c r="BW13" s="33"/>
-      <c r="BX13" s="35"/>
-      <c r="BY13" s="34"/>
+      <c r="BX13" s="34"/>
+      <c r="BY13" s="35"/>
       <c r="BZ13" s="33"/>
       <c r="CA13" s="33"/>
       <c r="CB13" s="33"/>
       <c r="CC13" s="33"/>
       <c r="CD13" s="33"/>
-      <c r="CE13" s="35"/>
-      <c r="CF13" s="34"/>
+      <c r="CE13" s="34"/>
+      <c r="CF13" s="35"/>
       <c r="CG13" s="33"/>
       <c r="CH13" s="33"/>
       <c r="CI13" s="33"/>
       <c r="CJ13" s="33"/>
       <c r="CK13" s="33"/>
-      <c r="CL13" s="35"/>
-      <c r="CM13" s="34"/>
+      <c r="CL13" s="34"/>
+      <c r="CM13" s="35"/>
       <c r="CN13" s="33"/>
       <c r="CO13" s="33"/>
       <c r="CP13" s="33"/>
       <c r="CQ13" s="33"/>
       <c r="CR13" s="33"/>
-      <c r="CS13" s="35"/>
-      <c r="CT13" s="34"/>
+      <c r="CS13" s="34"/>
+      <c r="CT13" s="35"/>
       <c r="CU13" s="33"/>
       <c r="CV13" s="33"/>
     </row>
@@ -3141,14 +3159,14 @@
       <c r="F14" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G14" s="34"/>
+      <c r="G14" s="35"/>
       <c r="H14" s="33"/>
       <c r="I14" s="33"/>
       <c r="J14" s="33"/>
       <c r="K14" s="33"/>
       <c r="L14" s="33"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="34"/>
+      <c r="M14" s="34"/>
+      <c r="N14" s="35"/>
       <c r="O14" s="33"/>
       <c r="P14" s="33"/>
       <c r="Q14" s="33" t="s">
@@ -3163,84 +3181,86 @@
       <c r="T14" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="U14" s="34"/>
+      <c r="U14" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="V14" s="33"/>
       <c r="W14" s="33"/>
       <c r="X14" s="33"/>
       <c r="Y14" s="33"/>
       <c r="Z14" s="33"/>
-      <c r="AA14" s="35"/>
-      <c r="AB14" s="34"/>
+      <c r="AA14" s="34"/>
+      <c r="AB14" s="35"/>
       <c r="AC14" s="33"/>
       <c r="AD14" s="33"/>
       <c r="AE14" s="33"/>
       <c r="AF14" s="33"/>
       <c r="AG14" s="33"/>
-      <c r="AH14" s="35"/>
-      <c r="AI14" s="34"/>
+      <c r="AH14" s="34"/>
+      <c r="AI14" s="35"/>
       <c r="AJ14" s="33"/>
       <c r="AK14" s="33"/>
       <c r="AL14" s="33"/>
       <c r="AM14" s="33"/>
       <c r="AN14" s="33"/>
-      <c r="AO14" s="35"/>
-      <c r="AP14" s="34"/>
+      <c r="AO14" s="34"/>
+      <c r="AP14" s="35"/>
       <c r="AQ14" s="33"/>
       <c r="AR14" s="33"/>
       <c r="AS14" s="33"/>
       <c r="AT14" s="33"/>
       <c r="AU14" s="33"/>
-      <c r="AV14" s="35"/>
-      <c r="AW14" s="34"/>
+      <c r="AV14" s="34"/>
+      <c r="AW14" s="35"/>
       <c r="AX14" s="33"/>
       <c r="AY14" s="33"/>
       <c r="AZ14" s="33"/>
       <c r="BA14" s="33"/>
       <c r="BB14" s="33"/>
-      <c r="BC14" s="35"/>
-      <c r="BD14" s="34"/>
+      <c r="BC14" s="34"/>
+      <c r="BD14" s="35"/>
       <c r="BE14" s="33"/>
       <c r="BF14" s="33"/>
       <c r="BG14" s="33"/>
       <c r="BH14" s="33"/>
       <c r="BI14" s="33"/>
-      <c r="BJ14" s="35"/>
-      <c r="BK14" s="34"/>
+      <c r="BJ14" s="34"/>
+      <c r="BK14" s="35"/>
       <c r="BL14" s="33"/>
       <c r="BM14" s="33"/>
       <c r="BN14" s="33"/>
       <c r="BO14" s="33"/>
       <c r="BP14" s="33"/>
-      <c r="BQ14" s="35"/>
-      <c r="BR14" s="34"/>
+      <c r="BQ14" s="34"/>
+      <c r="BR14" s="35"/>
       <c r="BS14" s="33"/>
       <c r="BT14" s="33"/>
       <c r="BU14" s="33"/>
       <c r="BV14" s="33"/>
       <c r="BW14" s="33"/>
-      <c r="BX14" s="35"/>
-      <c r="BY14" s="34"/>
+      <c r="BX14" s="34"/>
+      <c r="BY14" s="35"/>
       <c r="BZ14" s="33"/>
       <c r="CA14" s="33"/>
       <c r="CB14" s="33"/>
       <c r="CC14" s="33"/>
       <c r="CD14" s="33"/>
-      <c r="CE14" s="35"/>
-      <c r="CF14" s="34"/>
+      <c r="CE14" s="34"/>
+      <c r="CF14" s="35"/>
       <c r="CG14" s="33"/>
       <c r="CH14" s="33"/>
       <c r="CI14" s="33"/>
       <c r="CJ14" s="33"/>
       <c r="CK14" s="33"/>
-      <c r="CL14" s="35"/>
-      <c r="CM14" s="34"/>
+      <c r="CL14" s="34"/>
+      <c r="CM14" s="35"/>
       <c r="CN14" s="33"/>
       <c r="CO14" s="33"/>
       <c r="CP14" s="33"/>
       <c r="CQ14" s="33"/>
       <c r="CR14" s="33"/>
-      <c r="CS14" s="35"/>
-      <c r="CT14" s="34"/>
+      <c r="CS14" s="34"/>
+      <c r="CT14" s="35"/>
       <c r="CU14" s="33"/>
       <c r="CV14" s="33"/>
     </row>
@@ -3263,14 +3283,14 @@
       <c r="F15" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G15" s="34"/>
+      <c r="G15" s="35"/>
       <c r="H15" s="33"/>
       <c r="I15" s="33"/>
       <c r="J15" s="33"/>
       <c r="K15" s="33"/>
       <c r="L15" s="33"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="35"/>
       <c r="O15" s="33"/>
       <c r="P15" s="33"/>
       <c r="Q15" s="33"/>
@@ -3283,84 +3303,86 @@
       <c r="T15" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="U15" s="34"/>
+      <c r="U15" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="V15" s="33"/>
       <c r="W15" s="33"/>
       <c r="X15" s="33"/>
       <c r="Y15" s="33"/>
       <c r="Z15" s="33"/>
-      <c r="AA15" s="35"/>
-      <c r="AB15" s="34"/>
+      <c r="AA15" s="34"/>
+      <c r="AB15" s="35"/>
       <c r="AC15" s="33"/>
       <c r="AD15" s="33"/>
       <c r="AE15" s="33"/>
       <c r="AF15" s="33"/>
       <c r="AG15" s="33"/>
-      <c r="AH15" s="35"/>
-      <c r="AI15" s="34"/>
+      <c r="AH15" s="34"/>
+      <c r="AI15" s="35"/>
       <c r="AJ15" s="33"/>
       <c r="AK15" s="33"/>
       <c r="AL15" s="33"/>
       <c r="AM15" s="33"/>
       <c r="AN15" s="33"/>
-      <c r="AO15" s="35"/>
-      <c r="AP15" s="34"/>
+      <c r="AO15" s="34"/>
+      <c r="AP15" s="35"/>
       <c r="AQ15" s="33"/>
       <c r="AR15" s="33"/>
       <c r="AS15" s="33"/>
       <c r="AT15" s="33"/>
       <c r="AU15" s="33"/>
-      <c r="AV15" s="35"/>
-      <c r="AW15" s="34"/>
+      <c r="AV15" s="34"/>
+      <c r="AW15" s="35"/>
       <c r="AX15" s="33"/>
       <c r="AY15" s="33"/>
       <c r="AZ15" s="33"/>
       <c r="BA15" s="33"/>
       <c r="BB15" s="33"/>
-      <c r="BC15" s="35"/>
-      <c r="BD15" s="34"/>
+      <c r="BC15" s="34"/>
+      <c r="BD15" s="35"/>
       <c r="BE15" s="33"/>
       <c r="BF15" s="33"/>
       <c r="BG15" s="33"/>
       <c r="BH15" s="33"/>
       <c r="BI15" s="33"/>
-      <c r="BJ15" s="35"/>
-      <c r="BK15" s="34"/>
+      <c r="BJ15" s="34"/>
+      <c r="BK15" s="35"/>
       <c r="BL15" s="33"/>
       <c r="BM15" s="33"/>
       <c r="BN15" s="33"/>
       <c r="BO15" s="33"/>
       <c r="BP15" s="33"/>
-      <c r="BQ15" s="35"/>
-      <c r="BR15" s="34"/>
+      <c r="BQ15" s="34"/>
+      <c r="BR15" s="35"/>
       <c r="BS15" s="33"/>
       <c r="BT15" s="33"/>
       <c r="BU15" s="33"/>
       <c r="BV15" s="33"/>
       <c r="BW15" s="33"/>
-      <c r="BX15" s="35"/>
-      <c r="BY15" s="34"/>
+      <c r="BX15" s="34"/>
+      <c r="BY15" s="35"/>
       <c r="BZ15" s="33"/>
       <c r="CA15" s="33"/>
       <c r="CB15" s="33"/>
       <c r="CC15" s="33"/>
       <c r="CD15" s="33"/>
-      <c r="CE15" s="35"/>
-      <c r="CF15" s="34"/>
+      <c r="CE15" s="34"/>
+      <c r="CF15" s="35"/>
       <c r="CG15" s="33"/>
       <c r="CH15" s="33"/>
       <c r="CI15" s="33"/>
       <c r="CJ15" s="33"/>
       <c r="CK15" s="33"/>
-      <c r="CL15" s="35"/>
-      <c r="CM15" s="34"/>
+      <c r="CL15" s="34"/>
+      <c r="CM15" s="35"/>
       <c r="CN15" s="33"/>
       <c r="CO15" s="33"/>
       <c r="CP15" s="33"/>
       <c r="CQ15" s="33"/>
       <c r="CR15" s="33"/>
-      <c r="CS15" s="35"/>
-      <c r="CT15" s="34"/>
+      <c r="CS15" s="34"/>
+      <c r="CT15" s="35"/>
       <c r="CU15" s="33"/>
       <c r="CV15" s="33"/>
     </row>
@@ -3383,14 +3405,14 @@
       <c r="F16" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G16" s="34"/>
+      <c r="G16" s="35"/>
       <c r="H16" s="33"/>
       <c r="I16" s="33"/>
       <c r="J16" s="33"/>
       <c r="K16" s="33"/>
       <c r="L16" s="33"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="35"/>
       <c r="O16" s="33"/>
       <c r="P16" s="33"/>
       <c r="Q16" s="33"/>
@@ -3401,84 +3423,86 @@
       <c r="T16" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="U16" s="34"/>
+      <c r="U16" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="V16" s="33"/>
       <c r="W16" s="33"/>
       <c r="X16" s="33"/>
       <c r="Y16" s="33"/>
       <c r="Z16" s="33"/>
-      <c r="AA16" s="35"/>
-      <c r="AB16" s="34"/>
+      <c r="AA16" s="34"/>
+      <c r="AB16" s="35"/>
       <c r="AC16" s="33"/>
       <c r="AD16" s="33"/>
       <c r="AE16" s="33"/>
       <c r="AF16" s="33"/>
       <c r="AG16" s="33"/>
-      <c r="AH16" s="35"/>
-      <c r="AI16" s="34"/>
+      <c r="AH16" s="34"/>
+      <c r="AI16" s="35"/>
       <c r="AJ16" s="33"/>
       <c r="AK16" s="33"/>
       <c r="AL16" s="33"/>
       <c r="AM16" s="33"/>
       <c r="AN16" s="33"/>
-      <c r="AO16" s="35"/>
-      <c r="AP16" s="34"/>
+      <c r="AO16" s="34"/>
+      <c r="AP16" s="35"/>
       <c r="AQ16" s="33"/>
       <c r="AR16" s="33"/>
       <c r="AS16" s="33"/>
       <c r="AT16" s="33"/>
       <c r="AU16" s="33"/>
-      <c r="AV16" s="35"/>
-      <c r="AW16" s="34"/>
+      <c r="AV16" s="34"/>
+      <c r="AW16" s="35"/>
       <c r="AX16" s="33"/>
       <c r="AY16" s="33"/>
       <c r="AZ16" s="33"/>
       <c r="BA16" s="33"/>
       <c r="BB16" s="33"/>
-      <c r="BC16" s="35"/>
-      <c r="BD16" s="34"/>
+      <c r="BC16" s="34"/>
+      <c r="BD16" s="35"/>
       <c r="BE16" s="33"/>
       <c r="BF16" s="33"/>
       <c r="BG16" s="33"/>
       <c r="BH16" s="33"/>
       <c r="BI16" s="33"/>
-      <c r="BJ16" s="35"/>
-      <c r="BK16" s="34"/>
+      <c r="BJ16" s="34"/>
+      <c r="BK16" s="35"/>
       <c r="BL16" s="33"/>
       <c r="BM16" s="33"/>
       <c r="BN16" s="33"/>
       <c r="BO16" s="33"/>
       <c r="BP16" s="33"/>
-      <c r="BQ16" s="35"/>
-      <c r="BR16" s="34"/>
+      <c r="BQ16" s="34"/>
+      <c r="BR16" s="35"/>
       <c r="BS16" s="33"/>
       <c r="BT16" s="33"/>
       <c r="BU16" s="33"/>
       <c r="BV16" s="33"/>
       <c r="BW16" s="33"/>
-      <c r="BX16" s="35"/>
-      <c r="BY16" s="34"/>
+      <c r="BX16" s="34"/>
+      <c r="BY16" s="35"/>
       <c r="BZ16" s="33"/>
       <c r="CA16" s="33"/>
       <c r="CB16" s="33"/>
       <c r="CC16" s="33"/>
       <c r="CD16" s="33"/>
-      <c r="CE16" s="35"/>
-      <c r="CF16" s="34"/>
+      <c r="CE16" s="34"/>
+      <c r="CF16" s="35"/>
       <c r="CG16" s="33"/>
       <c r="CH16" s="33"/>
       <c r="CI16" s="33"/>
       <c r="CJ16" s="33"/>
       <c r="CK16" s="33"/>
-      <c r="CL16" s="35"/>
-      <c r="CM16" s="34"/>
+      <c r="CL16" s="34"/>
+      <c r="CM16" s="35"/>
       <c r="CN16" s="33"/>
       <c r="CO16" s="33"/>
       <c r="CP16" s="33"/>
       <c r="CQ16" s="33"/>
       <c r="CR16" s="33"/>
-      <c r="CS16" s="35"/>
-      <c r="CT16" s="34"/>
+      <c r="CS16" s="34"/>
+      <c r="CT16" s="35"/>
       <c r="CU16" s="33"/>
       <c r="CV16" s="33"/>
     </row>
@@ -3501,14 +3525,14 @@
       <c r="F17" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G17" s="34"/>
+      <c r="G17" s="35"/>
       <c r="H17" s="33"/>
       <c r="I17" s="33"/>
       <c r="J17" s="33"/>
       <c r="K17" s="33"/>
       <c r="L17" s="33"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="35"/>
       <c r="O17" s="33"/>
       <c r="P17" s="33"/>
       <c r="Q17" s="33"/>
@@ -3517,84 +3541,86 @@
       <c r="T17" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="U17" s="34"/>
+      <c r="U17" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="V17" s="33"/>
       <c r="W17" s="33"/>
       <c r="X17" s="33"/>
       <c r="Y17" s="33"/>
       <c r="Z17" s="33"/>
-      <c r="AA17" s="35"/>
-      <c r="AB17" s="34"/>
+      <c r="AA17" s="34"/>
+      <c r="AB17" s="35"/>
       <c r="AC17" s="33"/>
       <c r="AD17" s="33"/>
       <c r="AE17" s="33"/>
       <c r="AF17" s="33"/>
       <c r="AG17" s="33"/>
-      <c r="AH17" s="35"/>
-      <c r="AI17" s="34"/>
+      <c r="AH17" s="34"/>
+      <c r="AI17" s="35"/>
       <c r="AJ17" s="33"/>
       <c r="AK17" s="33"/>
       <c r="AL17" s="33"/>
       <c r="AM17" s="33"/>
       <c r="AN17" s="33"/>
-      <c r="AO17" s="35"/>
-      <c r="AP17" s="34"/>
+      <c r="AO17" s="34"/>
+      <c r="AP17" s="35"/>
       <c r="AQ17" s="33"/>
       <c r="AR17" s="33"/>
       <c r="AS17" s="33"/>
       <c r="AT17" s="33"/>
       <c r="AU17" s="33"/>
-      <c r="AV17" s="35"/>
-      <c r="AW17" s="34"/>
+      <c r="AV17" s="34"/>
+      <c r="AW17" s="35"/>
       <c r="AX17" s="33"/>
       <c r="AY17" s="33"/>
       <c r="AZ17" s="33"/>
       <c r="BA17" s="33"/>
       <c r="BB17" s="33"/>
-      <c r="BC17" s="35"/>
-      <c r="BD17" s="34"/>
+      <c r="BC17" s="34"/>
+      <c r="BD17" s="35"/>
       <c r="BE17" s="33"/>
       <c r="BF17" s="33"/>
       <c r="BG17" s="33"/>
       <c r="BH17" s="33"/>
       <c r="BI17" s="33"/>
-      <c r="BJ17" s="35"/>
-      <c r="BK17" s="34"/>
+      <c r="BJ17" s="34"/>
+      <c r="BK17" s="35"/>
       <c r="BL17" s="33"/>
       <c r="BM17" s="33"/>
       <c r="BN17" s="33"/>
       <c r="BO17" s="33"/>
       <c r="BP17" s="33"/>
-      <c r="BQ17" s="35"/>
-      <c r="BR17" s="34"/>
+      <c r="BQ17" s="34"/>
+      <c r="BR17" s="35"/>
       <c r="BS17" s="33"/>
       <c r="BT17" s="33"/>
       <c r="BU17" s="33"/>
       <c r="BV17" s="33"/>
       <c r="BW17" s="33"/>
-      <c r="BX17" s="35"/>
-      <c r="BY17" s="34"/>
+      <c r="BX17" s="34"/>
+      <c r="BY17" s="35"/>
       <c r="BZ17" s="33"/>
       <c r="CA17" s="33"/>
       <c r="CB17" s="33"/>
       <c r="CC17" s="33"/>
       <c r="CD17" s="33"/>
-      <c r="CE17" s="35"/>
-      <c r="CF17" s="34"/>
+      <c r="CE17" s="34"/>
+      <c r="CF17" s="35"/>
       <c r="CG17" s="33"/>
       <c r="CH17" s="33"/>
       <c r="CI17" s="33"/>
       <c r="CJ17" s="33"/>
       <c r="CK17" s="33"/>
-      <c r="CL17" s="35"/>
-      <c r="CM17" s="34"/>
+      <c r="CL17" s="34"/>
+      <c r="CM17" s="35"/>
       <c r="CN17" s="33"/>
       <c r="CO17" s="33"/>
       <c r="CP17" s="33"/>
       <c r="CQ17" s="33"/>
       <c r="CR17" s="33"/>
-      <c r="CS17" s="35"/>
-      <c r="CT17" s="34"/>
+      <c r="CS17" s="34"/>
+      <c r="CT17" s="35"/>
       <c r="CU17" s="33"/>
       <c r="CV17" s="33"/>
     </row>
@@ -3617,98 +3643,100 @@
       <c r="F18" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G18" s="34"/>
+      <c r="G18" s="35"/>
       <c r="H18" s="33"/>
       <c r="I18" s="33"/>
       <c r="J18" s="33"/>
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="34"/>
+      <c r="M18" s="34"/>
+      <c r="N18" s="35"/>
       <c r="O18" s="33"/>
       <c r="P18" s="33"/>
       <c r="Q18" s="33"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
-      <c r="T18" s="35"/>
-      <c r="U18" s="34"/>
+      <c r="T18" s="34"/>
+      <c r="U18" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="V18" s="33"/>
       <c r="W18" s="33"/>
       <c r="X18" s="33"/>
       <c r="Y18" s="33"/>
       <c r="Z18" s="33"/>
-      <c r="AA18" s="35"/>
-      <c r="AB18" s="34"/>
+      <c r="AA18" s="34"/>
+      <c r="AB18" s="35"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
       <c r="AF18" s="33"/>
       <c r="AG18" s="33"/>
-      <c r="AH18" s="35"/>
-      <c r="AI18" s="34"/>
+      <c r="AH18" s="34"/>
+      <c r="AI18" s="35"/>
       <c r="AJ18" s="33"/>
       <c r="AK18" s="33"/>
       <c r="AL18" s="33"/>
       <c r="AM18" s="33"/>
       <c r="AN18" s="33"/>
-      <c r="AO18" s="35"/>
-      <c r="AP18" s="34"/>
+      <c r="AO18" s="34"/>
+      <c r="AP18" s="35"/>
       <c r="AQ18" s="33"/>
       <c r="AR18" s="33"/>
       <c r="AS18" s="33"/>
       <c r="AT18" s="33"/>
       <c r="AU18" s="33"/>
-      <c r="AV18" s="35"/>
-      <c r="AW18" s="34"/>
+      <c r="AV18" s="34"/>
+      <c r="AW18" s="35"/>
       <c r="AX18" s="33"/>
       <c r="AY18" s="33"/>
       <c r="AZ18" s="33"/>
       <c r="BA18" s="33"/>
       <c r="BB18" s="33"/>
-      <c r="BC18" s="35"/>
-      <c r="BD18" s="34"/>
+      <c r="BC18" s="34"/>
+      <c r="BD18" s="35"/>
       <c r="BE18" s="33"/>
       <c r="BF18" s="33"/>
       <c r="BG18" s="33"/>
       <c r="BH18" s="33"/>
       <c r="BI18" s="33"/>
-      <c r="BJ18" s="35"/>
-      <c r="BK18" s="34"/>
+      <c r="BJ18" s="34"/>
+      <c r="BK18" s="35"/>
       <c r="BL18" s="33"/>
       <c r="BM18" s="33"/>
       <c r="BN18" s="33"/>
       <c r="BO18" s="33"/>
       <c r="BP18" s="33"/>
-      <c r="BQ18" s="35"/>
-      <c r="BR18" s="34"/>
+      <c r="BQ18" s="34"/>
+      <c r="BR18" s="35"/>
       <c r="BS18" s="33"/>
       <c r="BT18" s="33"/>
       <c r="BU18" s="33"/>
       <c r="BV18" s="33"/>
       <c r="BW18" s="33"/>
-      <c r="BX18" s="35"/>
-      <c r="BY18" s="34"/>
+      <c r="BX18" s="34"/>
+      <c r="BY18" s="35"/>
       <c r="BZ18" s="33"/>
       <c r="CA18" s="33"/>
       <c r="CB18" s="33"/>
       <c r="CC18" s="33"/>
       <c r="CD18" s="33"/>
-      <c r="CE18" s="35"/>
-      <c r="CF18" s="34"/>
+      <c r="CE18" s="34"/>
+      <c r="CF18" s="35"/>
       <c r="CG18" s="33"/>
       <c r="CH18" s="33"/>
       <c r="CI18" s="33"/>
       <c r="CJ18" s="33"/>
       <c r="CK18" s="33"/>
-      <c r="CL18" s="35"/>
-      <c r="CM18" s="34"/>
+      <c r="CL18" s="34"/>
+      <c r="CM18" s="35"/>
       <c r="CN18" s="33"/>
       <c r="CO18" s="33"/>
       <c r="CP18" s="33"/>
       <c r="CQ18" s="33"/>
       <c r="CR18" s="33"/>
-      <c r="CS18" s="35"/>
-      <c r="CT18" s="34"/>
+      <c r="CS18" s="34"/>
+      <c r="CT18" s="35"/>
       <c r="CU18" s="33"/>
       <c r="CV18" s="33"/>
     </row>
@@ -3731,98 +3759,98 @@
       <c r="F19" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G19" s="34"/>
+      <c r="G19" s="35"/>
       <c r="H19" s="33"/>
       <c r="I19" s="33"/>
       <c r="J19" s="33"/>
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
-      <c r="M19" s="35"/>
-      <c r="N19" s="34"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="35"/>
       <c r="O19" s="33"/>
       <c r="P19" s="33"/>
       <c r="Q19" s="33"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
-      <c r="T19" s="35"/>
-      <c r="U19" s="34"/>
+      <c r="T19" s="34"/>
+      <c r="U19" s="35"/>
       <c r="V19" s="33"/>
       <c r="W19" s="33"/>
       <c r="X19" s="33"/>
       <c r="Y19" s="33"/>
       <c r="Z19" s="33"/>
-      <c r="AA19" s="35"/>
-      <c r="AB19" s="34"/>
+      <c r="AA19" s="34"/>
+      <c r="AB19" s="35"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
       <c r="AF19" s="33"/>
       <c r="AG19" s="33"/>
-      <c r="AH19" s="35"/>
-      <c r="AI19" s="34"/>
+      <c r="AH19" s="34"/>
+      <c r="AI19" s="35"/>
       <c r="AJ19" s="33"/>
       <c r="AK19" s="33"/>
       <c r="AL19" s="33"/>
       <c r="AM19" s="33"/>
       <c r="AN19" s="33"/>
-      <c r="AO19" s="35"/>
-      <c r="AP19" s="34"/>
+      <c r="AO19" s="34"/>
+      <c r="AP19" s="35"/>
       <c r="AQ19" s="33"/>
       <c r="AR19" s="33"/>
       <c r="AS19" s="33"/>
       <c r="AT19" s="33"/>
       <c r="AU19" s="33"/>
-      <c r="AV19" s="35"/>
-      <c r="AW19" s="34"/>
+      <c r="AV19" s="34"/>
+      <c r="AW19" s="35"/>
       <c r="AX19" s="33"/>
       <c r="AY19" s="33"/>
       <c r="AZ19" s="33"/>
       <c r="BA19" s="33"/>
       <c r="BB19" s="33"/>
-      <c r="BC19" s="35"/>
-      <c r="BD19" s="34"/>
+      <c r="BC19" s="34"/>
+      <c r="BD19" s="35"/>
       <c r="BE19" s="33"/>
       <c r="BF19" s="33"/>
       <c r="BG19" s="33"/>
       <c r="BH19" s="33"/>
       <c r="BI19" s="33"/>
-      <c r="BJ19" s="35"/>
-      <c r="BK19" s="34"/>
+      <c r="BJ19" s="34"/>
+      <c r="BK19" s="35"/>
       <c r="BL19" s="33"/>
       <c r="BM19" s="33"/>
       <c r="BN19" s="33"/>
       <c r="BO19" s="33"/>
       <c r="BP19" s="33"/>
-      <c r="BQ19" s="35"/>
-      <c r="BR19" s="34"/>
+      <c r="BQ19" s="34"/>
+      <c r="BR19" s="35"/>
       <c r="BS19" s="33"/>
       <c r="BT19" s="33"/>
       <c r="BU19" s="33"/>
       <c r="BV19" s="33"/>
       <c r="BW19" s="33"/>
-      <c r="BX19" s="35"/>
-      <c r="BY19" s="34"/>
+      <c r="BX19" s="34"/>
+      <c r="BY19" s="35"/>
       <c r="BZ19" s="33"/>
       <c r="CA19" s="33"/>
       <c r="CB19" s="33"/>
       <c r="CC19" s="33"/>
       <c r="CD19" s="33"/>
-      <c r="CE19" s="35"/>
-      <c r="CF19" s="34"/>
+      <c r="CE19" s="34"/>
+      <c r="CF19" s="35"/>
       <c r="CG19" s="33"/>
       <c r="CH19" s="33"/>
       <c r="CI19" s="33"/>
       <c r="CJ19" s="33"/>
       <c r="CK19" s="33"/>
-      <c r="CL19" s="35"/>
-      <c r="CM19" s="34"/>
+      <c r="CL19" s="34"/>
+      <c r="CM19" s="35"/>
       <c r="CN19" s="33"/>
       <c r="CO19" s="33"/>
       <c r="CP19" s="33"/>
       <c r="CQ19" s="33"/>
       <c r="CR19" s="33"/>
-      <c r="CS19" s="35"/>
-      <c r="CT19" s="34"/>
+      <c r="CS19" s="34"/>
+      <c r="CT19" s="35"/>
       <c r="CU19" s="33"/>
       <c r="CV19" s="33"/>
     </row>
@@ -3845,98 +3873,98 @@
       <c r="F20" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G20" s="34"/>
+      <c r="G20" s="35"/>
       <c r="H20" s="33"/>
       <c r="I20" s="33"/>
       <c r="J20" s="33"/>
       <c r="K20" s="33"/>
       <c r="L20" s="33"/>
-      <c r="M20" s="35"/>
-      <c r="N20" s="34"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="35"/>
       <c r="O20" s="33"/>
       <c r="P20" s="33"/>
       <c r="Q20" s="33"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
-      <c r="T20" s="35"/>
-      <c r="U20" s="34"/>
+      <c r="T20" s="34"/>
+      <c r="U20" s="35"/>
       <c r="V20" s="33"/>
       <c r="W20" s="33"/>
       <c r="X20" s="33"/>
       <c r="Y20" s="33"/>
       <c r="Z20" s="33"/>
-      <c r="AA20" s="35"/>
-      <c r="AB20" s="34"/>
+      <c r="AA20" s="34"/>
+      <c r="AB20" s="35"/>
       <c r="AC20" s="33"/>
       <c r="AD20" s="33"/>
       <c r="AE20" s="33"/>
       <c r="AF20" s="33"/>
       <c r="AG20" s="33"/>
-      <c r="AH20" s="35"/>
-      <c r="AI20" s="34"/>
+      <c r="AH20" s="34"/>
+      <c r="AI20" s="35"/>
       <c r="AJ20" s="33"/>
       <c r="AK20" s="33"/>
       <c r="AL20" s="33"/>
       <c r="AM20" s="33"/>
       <c r="AN20" s="33"/>
-      <c r="AO20" s="35"/>
-      <c r="AP20" s="34"/>
+      <c r="AO20" s="34"/>
+      <c r="AP20" s="35"/>
       <c r="AQ20" s="33"/>
       <c r="AR20" s="33"/>
       <c r="AS20" s="33"/>
       <c r="AT20" s="33"/>
       <c r="AU20" s="33"/>
-      <c r="AV20" s="35"/>
-      <c r="AW20" s="34"/>
+      <c r="AV20" s="34"/>
+      <c r="AW20" s="35"/>
       <c r="AX20" s="33"/>
       <c r="AY20" s="33"/>
       <c r="AZ20" s="33"/>
       <c r="BA20" s="33"/>
       <c r="BB20" s="33"/>
-      <c r="BC20" s="35"/>
-      <c r="BD20" s="34"/>
+      <c r="BC20" s="34"/>
+      <c r="BD20" s="35"/>
       <c r="BE20" s="33"/>
       <c r="BF20" s="33"/>
       <c r="BG20" s="33"/>
       <c r="BH20" s="33"/>
       <c r="BI20" s="33"/>
-      <c r="BJ20" s="35"/>
-      <c r="BK20" s="34"/>
+      <c r="BJ20" s="34"/>
+      <c r="BK20" s="35"/>
       <c r="BL20" s="33"/>
       <c r="BM20" s="33"/>
       <c r="BN20" s="33"/>
       <c r="BO20" s="33"/>
       <c r="BP20" s="33"/>
-      <c r="BQ20" s="35"/>
-      <c r="BR20" s="34"/>
+      <c r="BQ20" s="34"/>
+      <c r="BR20" s="35"/>
       <c r="BS20" s="33"/>
       <c r="BT20" s="33"/>
       <c r="BU20" s="33"/>
       <c r="BV20" s="33"/>
       <c r="BW20" s="33"/>
-      <c r="BX20" s="35"/>
-      <c r="BY20" s="34"/>
+      <c r="BX20" s="34"/>
+      <c r="BY20" s="35"/>
       <c r="BZ20" s="33"/>
       <c r="CA20" s="33"/>
       <c r="CB20" s="33"/>
       <c r="CC20" s="33"/>
       <c r="CD20" s="33"/>
-      <c r="CE20" s="35"/>
-      <c r="CF20" s="34"/>
+      <c r="CE20" s="34"/>
+      <c r="CF20" s="35"/>
       <c r="CG20" s="33"/>
       <c r="CH20" s="33"/>
       <c r="CI20" s="33"/>
       <c r="CJ20" s="33"/>
       <c r="CK20" s="33"/>
-      <c r="CL20" s="35"/>
-      <c r="CM20" s="34"/>
+      <c r="CL20" s="34"/>
+      <c r="CM20" s="35"/>
       <c r="CN20" s="33"/>
       <c r="CO20" s="33"/>
       <c r="CP20" s="33"/>
       <c r="CQ20" s="33"/>
       <c r="CR20" s="33"/>
-      <c r="CS20" s="35"/>
-      <c r="CT20" s="34"/>
+      <c r="CS20" s="34"/>
+      <c r="CT20" s="35"/>
       <c r="CU20" s="33"/>
       <c r="CV20" s="33"/>
     </row>
@@ -3959,98 +3987,98 @@
       <c r="F21" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G21" s="34"/>
+      <c r="G21" s="35"/>
       <c r="H21" s="33"/>
       <c r="I21" s="33"/>
       <c r="J21" s="33"/>
       <c r="K21" s="33"/>
       <c r="L21" s="33"/>
-      <c r="M21" s="35"/>
-      <c r="N21" s="34"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="35"/>
       <c r="O21" s="33"/>
       <c r="P21" s="33"/>
       <c r="Q21" s="33"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
-      <c r="T21" s="35"/>
-      <c r="U21" s="34"/>
+      <c r="T21" s="34"/>
+      <c r="U21" s="35"/>
       <c r="V21" s="33"/>
       <c r="W21" s="33"/>
       <c r="X21" s="33"/>
       <c r="Y21" s="33"/>
       <c r="Z21" s="33"/>
-      <c r="AA21" s="35"/>
-      <c r="AB21" s="34"/>
+      <c r="AA21" s="34"/>
+      <c r="AB21" s="35"/>
       <c r="AC21" s="33"/>
       <c r="AD21" s="33"/>
       <c r="AE21" s="33"/>
       <c r="AF21" s="33"/>
       <c r="AG21" s="33"/>
-      <c r="AH21" s="35"/>
-      <c r="AI21" s="34"/>
+      <c r="AH21" s="34"/>
+      <c r="AI21" s="35"/>
       <c r="AJ21" s="33"/>
       <c r="AK21" s="33"/>
       <c r="AL21" s="33"/>
       <c r="AM21" s="33"/>
       <c r="AN21" s="33"/>
-      <c r="AO21" s="35"/>
-      <c r="AP21" s="34"/>
+      <c r="AO21" s="34"/>
+      <c r="AP21" s="35"/>
       <c r="AQ21" s="33"/>
       <c r="AR21" s="33"/>
       <c r="AS21" s="33"/>
       <c r="AT21" s="33"/>
       <c r="AU21" s="33"/>
-      <c r="AV21" s="35"/>
-      <c r="AW21" s="34"/>
+      <c r="AV21" s="34"/>
+      <c r="AW21" s="35"/>
       <c r="AX21" s="33"/>
       <c r="AY21" s="33"/>
       <c r="AZ21" s="33"/>
       <c r="BA21" s="33"/>
       <c r="BB21" s="33"/>
-      <c r="BC21" s="35"/>
-      <c r="BD21" s="34"/>
+      <c r="BC21" s="34"/>
+      <c r="BD21" s="35"/>
       <c r="BE21" s="33"/>
       <c r="BF21" s="33"/>
       <c r="BG21" s="33"/>
       <c r="BH21" s="33"/>
       <c r="BI21" s="33"/>
-      <c r="BJ21" s="35"/>
-      <c r="BK21" s="34"/>
+      <c r="BJ21" s="34"/>
+      <c r="BK21" s="35"/>
       <c r="BL21" s="33"/>
       <c r="BM21" s="33"/>
       <c r="BN21" s="33"/>
       <c r="BO21" s="33"/>
       <c r="BP21" s="33"/>
-      <c r="BQ21" s="35"/>
-      <c r="BR21" s="34"/>
+      <c r="BQ21" s="34"/>
+      <c r="BR21" s="35"/>
       <c r="BS21" s="33"/>
       <c r="BT21" s="33"/>
       <c r="BU21" s="33"/>
       <c r="BV21" s="33"/>
       <c r="BW21" s="33"/>
-      <c r="BX21" s="35"/>
-      <c r="BY21" s="34"/>
+      <c r="BX21" s="34"/>
+      <c r="BY21" s="35"/>
       <c r="BZ21" s="33"/>
       <c r="CA21" s="33"/>
       <c r="CB21" s="33"/>
       <c r="CC21" s="33"/>
       <c r="CD21" s="33"/>
-      <c r="CE21" s="35"/>
-      <c r="CF21" s="34"/>
+      <c r="CE21" s="34"/>
+      <c r="CF21" s="35"/>
       <c r="CG21" s="33"/>
       <c r="CH21" s="33"/>
       <c r="CI21" s="33"/>
       <c r="CJ21" s="33"/>
       <c r="CK21" s="33"/>
-      <c r="CL21" s="35"/>
-      <c r="CM21" s="34"/>
+      <c r="CL21" s="34"/>
+      <c r="CM21" s="35"/>
       <c r="CN21" s="33"/>
       <c r="CO21" s="33"/>
       <c r="CP21" s="33"/>
       <c r="CQ21" s="33"/>
       <c r="CR21" s="33"/>
-      <c r="CS21" s="35"/>
-      <c r="CT21" s="34"/>
+      <c r="CS21" s="34"/>
+      <c r="CT21" s="35"/>
       <c r="CU21" s="33"/>
       <c r="CV21" s="33"/>
     </row>
@@ -4073,98 +4101,98 @@
       <c r="F22" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G22" s="34"/>
+      <c r="G22" s="35"/>
       <c r="H22" s="33"/>
       <c r="I22" s="33"/>
       <c r="J22" s="33"/>
       <c r="K22" s="33"/>
       <c r="L22" s="33"/>
-      <c r="M22" s="35"/>
-      <c r="N22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="35"/>
       <c r="O22" s="33"/>
       <c r="P22" s="33"/>
       <c r="Q22" s="33"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
-      <c r="T22" s="35"/>
-      <c r="U22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="35"/>
       <c r="V22" s="33"/>
       <c r="W22" s="33"/>
       <c r="X22" s="33"/>
       <c r="Y22" s="33"/>
       <c r="Z22" s="33"/>
-      <c r="AA22" s="35"/>
-      <c r="AB22" s="34"/>
+      <c r="AA22" s="34"/>
+      <c r="AB22" s="35"/>
       <c r="AC22" s="33"/>
       <c r="AD22" s="33"/>
       <c r="AE22" s="33"/>
       <c r="AF22" s="33"/>
       <c r="AG22" s="33"/>
-      <c r="AH22" s="35"/>
-      <c r="AI22" s="34"/>
+      <c r="AH22" s="34"/>
+      <c r="AI22" s="35"/>
       <c r="AJ22" s="33"/>
       <c r="AK22" s="33"/>
       <c r="AL22" s="33"/>
       <c r="AM22" s="33"/>
       <c r="AN22" s="33"/>
-      <c r="AO22" s="35"/>
-      <c r="AP22" s="34"/>
+      <c r="AO22" s="34"/>
+      <c r="AP22" s="35"/>
       <c r="AQ22" s="33"/>
       <c r="AR22" s="33"/>
       <c r="AS22" s="33"/>
       <c r="AT22" s="33"/>
       <c r="AU22" s="33"/>
-      <c r="AV22" s="35"/>
-      <c r="AW22" s="34"/>
+      <c r="AV22" s="34"/>
+      <c r="AW22" s="35"/>
       <c r="AX22" s="33"/>
       <c r="AY22" s="33"/>
       <c r="AZ22" s="33"/>
       <c r="BA22" s="33"/>
       <c r="BB22" s="33"/>
-      <c r="BC22" s="35"/>
-      <c r="BD22" s="34"/>
+      <c r="BC22" s="34"/>
+      <c r="BD22" s="35"/>
       <c r="BE22" s="33"/>
       <c r="BF22" s="33"/>
       <c r="BG22" s="33"/>
       <c r="BH22" s="33"/>
       <c r="BI22" s="33"/>
-      <c r="BJ22" s="35"/>
-      <c r="BK22" s="34"/>
+      <c r="BJ22" s="34"/>
+      <c r="BK22" s="35"/>
       <c r="BL22" s="33"/>
       <c r="BM22" s="33"/>
       <c r="BN22" s="33"/>
       <c r="BO22" s="33"/>
       <c r="BP22" s="33"/>
-      <c r="BQ22" s="35"/>
-      <c r="BR22" s="34"/>
+      <c r="BQ22" s="34"/>
+      <c r="BR22" s="35"/>
       <c r="BS22" s="33"/>
       <c r="BT22" s="33"/>
       <c r="BU22" s="33"/>
       <c r="BV22" s="33"/>
       <c r="BW22" s="33"/>
-      <c r="BX22" s="35"/>
-      <c r="BY22" s="34"/>
+      <c r="BX22" s="34"/>
+      <c r="BY22" s="35"/>
       <c r="BZ22" s="33"/>
       <c r="CA22" s="33"/>
       <c r="CB22" s="33"/>
       <c r="CC22" s="33"/>
       <c r="CD22" s="33"/>
-      <c r="CE22" s="35"/>
-      <c r="CF22" s="34"/>
+      <c r="CE22" s="34"/>
+      <c r="CF22" s="35"/>
       <c r="CG22" s="33"/>
       <c r="CH22" s="33"/>
       <c r="CI22" s="33"/>
       <c r="CJ22" s="33"/>
       <c r="CK22" s="33"/>
-      <c r="CL22" s="35"/>
-      <c r="CM22" s="34"/>
+      <c r="CL22" s="34"/>
+      <c r="CM22" s="35"/>
       <c r="CN22" s="33"/>
       <c r="CO22" s="33"/>
       <c r="CP22" s="33"/>
       <c r="CQ22" s="33"/>
       <c r="CR22" s="33"/>
-      <c r="CS22" s="35"/>
-      <c r="CT22" s="34"/>
+      <c r="CS22" s="34"/>
+      <c r="CT22" s="35"/>
       <c r="CU22" s="33"/>
       <c r="CV22" s="33"/>
     </row>
@@ -4187,98 +4215,98 @@
       <c r="F23" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G23" s="34"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="33"/>
       <c r="I23" s="33"/>
       <c r="J23" s="33"/>
       <c r="K23" s="33"/>
       <c r="L23" s="33"/>
-      <c r="M23" s="35"/>
-      <c r="N23" s="34"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="35"/>
       <c r="O23" s="33"/>
       <c r="P23" s="33"/>
       <c r="Q23" s="33"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
-      <c r="T23" s="35"/>
-      <c r="U23" s="34"/>
+      <c r="T23" s="34"/>
+      <c r="U23" s="35"/>
       <c r="V23" s="33"/>
       <c r="W23" s="33"/>
       <c r="X23" s="33"/>
       <c r="Y23" s="33"/>
       <c r="Z23" s="33"/>
-      <c r="AA23" s="35"/>
-      <c r="AB23" s="34"/>
+      <c r="AA23" s="34"/>
+      <c r="AB23" s="35"/>
       <c r="AC23" s="33"/>
       <c r="AD23" s="33"/>
       <c r="AE23" s="33"/>
       <c r="AF23" s="33"/>
       <c r="AG23" s="33"/>
-      <c r="AH23" s="35"/>
-      <c r="AI23" s="34"/>
+      <c r="AH23" s="34"/>
+      <c r="AI23" s="35"/>
       <c r="AJ23" s="33"/>
       <c r="AK23" s="33"/>
       <c r="AL23" s="33"/>
       <c r="AM23" s="33"/>
       <c r="AN23" s="33"/>
-      <c r="AO23" s="35"/>
-      <c r="AP23" s="34"/>
+      <c r="AO23" s="34"/>
+      <c r="AP23" s="35"/>
       <c r="AQ23" s="33"/>
       <c r="AR23" s="33"/>
       <c r="AS23" s="33"/>
       <c r="AT23" s="33"/>
       <c r="AU23" s="33"/>
-      <c r="AV23" s="35"/>
-      <c r="AW23" s="34"/>
+      <c r="AV23" s="34"/>
+      <c r="AW23" s="35"/>
       <c r="AX23" s="33"/>
       <c r="AY23" s="33"/>
       <c r="AZ23" s="33"/>
       <c r="BA23" s="33"/>
       <c r="BB23" s="33"/>
-      <c r="BC23" s="35"/>
-      <c r="BD23" s="34"/>
+      <c r="BC23" s="34"/>
+      <c r="BD23" s="35"/>
       <c r="BE23" s="33"/>
       <c r="BF23" s="33"/>
       <c r="BG23" s="33"/>
       <c r="BH23" s="33"/>
       <c r="BI23" s="33"/>
-      <c r="BJ23" s="35"/>
-      <c r="BK23" s="34"/>
+      <c r="BJ23" s="34"/>
+      <c r="BK23" s="35"/>
       <c r="BL23" s="33"/>
       <c r="BM23" s="33"/>
       <c r="BN23" s="33"/>
       <c r="BO23" s="33"/>
       <c r="BP23" s="33"/>
-      <c r="BQ23" s="35"/>
-      <c r="BR23" s="34"/>
+      <c r="BQ23" s="34"/>
+      <c r="BR23" s="35"/>
       <c r="BS23" s="33"/>
       <c r="BT23" s="33"/>
       <c r="BU23" s="33"/>
       <c r="BV23" s="33"/>
       <c r="BW23" s="33"/>
-      <c r="BX23" s="35"/>
-      <c r="BY23" s="34"/>
+      <c r="BX23" s="34"/>
+      <c r="BY23" s="35"/>
       <c r="BZ23" s="33"/>
       <c r="CA23" s="33"/>
       <c r="CB23" s="33"/>
       <c r="CC23" s="33"/>
       <c r="CD23" s="33"/>
-      <c r="CE23" s="35"/>
-      <c r="CF23" s="34"/>
+      <c r="CE23" s="34"/>
+      <c r="CF23" s="35"/>
       <c r="CG23" s="33"/>
       <c r="CH23" s="33"/>
       <c r="CI23" s="33"/>
       <c r="CJ23" s="33"/>
       <c r="CK23" s="33"/>
-      <c r="CL23" s="35"/>
-      <c r="CM23" s="34"/>
+      <c r="CL23" s="34"/>
+      <c r="CM23" s="35"/>
       <c r="CN23" s="33"/>
       <c r="CO23" s="33"/>
       <c r="CP23" s="33"/>
       <c r="CQ23" s="33"/>
       <c r="CR23" s="33"/>
-      <c r="CS23" s="35"/>
-      <c r="CT23" s="34"/>
+      <c r="CS23" s="34"/>
+      <c r="CT23" s="35"/>
       <c r="CU23" s="33"/>
       <c r="CV23" s="33"/>
     </row>
@@ -4301,98 +4329,98 @@
       <c r="F24" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G24" s="34"/>
+      <c r="G24" s="35"/>
       <c r="H24" s="33"/>
       <c r="I24" s="33"/>
       <c r="J24" s="33"/>
       <c r="K24" s="33"/>
       <c r="L24" s="33"/>
-      <c r="M24" s="35"/>
-      <c r="N24" s="34"/>
+      <c r="M24" s="34"/>
+      <c r="N24" s="35"/>
       <c r="O24" s="33"/>
       <c r="P24" s="33"/>
       <c r="Q24" s="33"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
-      <c r="T24" s="35"/>
-      <c r="U24" s="34"/>
+      <c r="T24" s="34"/>
+      <c r="U24" s="35"/>
       <c r="V24" s="33"/>
       <c r="W24" s="33"/>
       <c r="X24" s="33"/>
       <c r="Y24" s="33"/>
       <c r="Z24" s="33"/>
-      <c r="AA24" s="35"/>
-      <c r="AB24" s="34"/>
+      <c r="AA24" s="34"/>
+      <c r="AB24" s="35"/>
       <c r="AC24" s="33"/>
       <c r="AD24" s="33"/>
       <c r="AE24" s="33"/>
       <c r="AF24" s="33"/>
       <c r="AG24" s="33"/>
-      <c r="AH24" s="35"/>
-      <c r="AI24" s="34"/>
+      <c r="AH24" s="34"/>
+      <c r="AI24" s="35"/>
       <c r="AJ24" s="33"/>
       <c r="AK24" s="33"/>
       <c r="AL24" s="33"/>
       <c r="AM24" s="33"/>
       <c r="AN24" s="33"/>
-      <c r="AO24" s="35"/>
-      <c r="AP24" s="34"/>
+      <c r="AO24" s="34"/>
+      <c r="AP24" s="35"/>
       <c r="AQ24" s="33"/>
       <c r="AR24" s="33"/>
       <c r="AS24" s="33"/>
       <c r="AT24" s="33"/>
       <c r="AU24" s="33"/>
-      <c r="AV24" s="35"/>
-      <c r="AW24" s="34"/>
+      <c r="AV24" s="34"/>
+      <c r="AW24" s="35"/>
       <c r="AX24" s="33"/>
       <c r="AY24" s="33"/>
       <c r="AZ24" s="33"/>
       <c r="BA24" s="33"/>
       <c r="BB24" s="33"/>
-      <c r="BC24" s="35"/>
-      <c r="BD24" s="34"/>
+      <c r="BC24" s="34"/>
+      <c r="BD24" s="35"/>
       <c r="BE24" s="33"/>
       <c r="BF24" s="33"/>
       <c r="BG24" s="33"/>
       <c r="BH24" s="33"/>
       <c r="BI24" s="33"/>
-      <c r="BJ24" s="35"/>
-      <c r="BK24" s="34"/>
+      <c r="BJ24" s="34"/>
+      <c r="BK24" s="35"/>
       <c r="BL24" s="33"/>
       <c r="BM24" s="33"/>
       <c r="BN24" s="33"/>
       <c r="BO24" s="33"/>
       <c r="BP24" s="33"/>
-      <c r="BQ24" s="35"/>
-      <c r="BR24" s="34"/>
+      <c r="BQ24" s="34"/>
+      <c r="BR24" s="35"/>
       <c r="BS24" s="33"/>
       <c r="BT24" s="33"/>
       <c r="BU24" s="33"/>
       <c r="BV24" s="33"/>
       <c r="BW24" s="33"/>
-      <c r="BX24" s="35"/>
-      <c r="BY24" s="34"/>
+      <c r="BX24" s="34"/>
+      <c r="BY24" s="35"/>
       <c r="BZ24" s="33"/>
       <c r="CA24" s="33"/>
       <c r="CB24" s="33"/>
       <c r="CC24" s="33"/>
       <c r="CD24" s="33"/>
-      <c r="CE24" s="35"/>
-      <c r="CF24" s="34"/>
+      <c r="CE24" s="34"/>
+      <c r="CF24" s="35"/>
       <c r="CG24" s="33"/>
       <c r="CH24" s="33"/>
       <c r="CI24" s="33"/>
       <c r="CJ24" s="33"/>
       <c r="CK24" s="33"/>
-      <c r="CL24" s="35"/>
-      <c r="CM24" s="34"/>
+      <c r="CL24" s="34"/>
+      <c r="CM24" s="35"/>
       <c r="CN24" s="33"/>
       <c r="CO24" s="33"/>
       <c r="CP24" s="33"/>
       <c r="CQ24" s="33"/>
       <c r="CR24" s="33"/>
-      <c r="CS24" s="35"/>
-      <c r="CT24" s="34"/>
+      <c r="CS24" s="34"/>
+      <c r="CT24" s="35"/>
       <c r="CU24" s="33"/>
       <c r="CV24" s="33"/>
     </row>

--- a/STL_Study_Tracker.xlsx
+++ b/STL_Study_Tracker.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="174">
   <si>
     <t>STL Topics — Detailed Breakdown</t>
   </si>
@@ -1996,7 +1996,9 @@
       <c r="U5" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="V5" s="33"/>
+      <c r="V5" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="W5" s="33"/>
       <c r="X5" s="33"/>
       <c r="Y5" s="33"/>
@@ -2136,7 +2138,9 @@
       <c r="U6" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="V6" s="33"/>
+      <c r="V6" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="W6" s="33"/>
       <c r="X6" s="33"/>
       <c r="Y6" s="33"/>
@@ -2274,7 +2278,9 @@
       <c r="U7" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="V7" s="33"/>
+      <c r="V7" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="W7" s="33"/>
       <c r="X7" s="33"/>
       <c r="Y7" s="33"/>
@@ -2410,7 +2416,9 @@
       <c r="U8" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="V8" s="33"/>
+      <c r="V8" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="W8" s="33"/>
       <c r="X8" s="33"/>
       <c r="Y8" s="33"/>
@@ -2544,7 +2552,9 @@
       <c r="U9" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="V9" s="33"/>
+      <c r="V9" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="W9" s="33"/>
       <c r="X9" s="33"/>
       <c r="Y9" s="33"/>
@@ -2676,7 +2686,9 @@
       <c r="U10" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="V10" s="33"/>
+      <c r="V10" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="W10" s="33"/>
       <c r="X10" s="33"/>
       <c r="Y10" s="33"/>
@@ -2806,7 +2818,9 @@
       <c r="U11" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="V11" s="33"/>
+      <c r="V11" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="W11" s="33"/>
       <c r="X11" s="33"/>
       <c r="Y11" s="33"/>
@@ -2934,7 +2948,9 @@
       <c r="U12" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="V12" s="33"/>
+      <c r="V12" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="W12" s="33"/>
       <c r="X12" s="33"/>
       <c r="Y12" s="33"/>
@@ -3060,7 +3076,9 @@
       <c r="U13" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="V13" s="33"/>
+      <c r="V13" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="W13" s="33"/>
       <c r="X13" s="33"/>
       <c r="Y13" s="33"/>
@@ -3184,7 +3202,9 @@
       <c r="U14" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="V14" s="33"/>
+      <c r="V14" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="W14" s="33"/>
       <c r="X14" s="33"/>
       <c r="Y14" s="33"/>
@@ -3306,7 +3326,9 @@
       <c r="U15" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="V15" s="33"/>
+      <c r="V15" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="W15" s="33"/>
       <c r="X15" s="33"/>
       <c r="Y15" s="33"/>
@@ -3426,7 +3448,9 @@
       <c r="U16" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="V16" s="33"/>
+      <c r="V16" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="W16" s="33"/>
       <c r="X16" s="33"/>
       <c r="Y16" s="33"/>
@@ -3544,7 +3568,9 @@
       <c r="U17" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="V17" s="33"/>
+      <c r="V17" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="W17" s="33"/>
       <c r="X17" s="33"/>
       <c r="Y17" s="33"/>
@@ -3660,7 +3686,9 @@
       <c r="U18" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="V18" s="33"/>
+      <c r="V18" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="W18" s="33"/>
       <c r="X18" s="33"/>
       <c r="Y18" s="33"/>
@@ -3774,7 +3802,9 @@
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
       <c r="U19" s="35"/>
-      <c r="V19" s="33"/>
+      <c r="V19" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="W19" s="33"/>
       <c r="X19" s="33"/>
       <c r="Y19" s="33"/>

--- a/STL_Study_Tracker.xlsx
+++ b/STL_Study_Tracker.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="174">
   <si>
     <t>STL Topics — Detailed Breakdown</t>
   </si>
@@ -1999,7 +1999,9 @@
       <c r="V5" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="W5" s="33"/>
+      <c r="W5" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="X5" s="33"/>
       <c r="Y5" s="33"/>
       <c r="Z5" s="33"/>
@@ -2141,7 +2143,9 @@
       <c r="V6" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="W6" s="33"/>
+      <c r="W6" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="X6" s="33"/>
       <c r="Y6" s="33"/>
       <c r="Z6" s="33"/>
@@ -2281,7 +2285,9 @@
       <c r="V7" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="W7" s="33"/>
+      <c r="W7" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="X7" s="33"/>
       <c r="Y7" s="33"/>
       <c r="Z7" s="33"/>
@@ -2419,7 +2425,9 @@
       <c r="V8" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="W8" s="33"/>
+      <c r="W8" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="X8" s="33"/>
       <c r="Y8" s="33"/>
       <c r="Z8" s="33"/>
@@ -2555,7 +2563,9 @@
       <c r="V9" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="W9" s="33"/>
+      <c r="W9" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="X9" s="33"/>
       <c r="Y9" s="33"/>
       <c r="Z9" s="33"/>
@@ -2689,7 +2699,9 @@
       <c r="V10" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="W10" s="33"/>
+      <c r="W10" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="X10" s="33"/>
       <c r="Y10" s="33"/>
       <c r="Z10" s="33"/>
@@ -2821,7 +2833,9 @@
       <c r="V11" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="W11" s="33"/>
+      <c r="W11" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="X11" s="33"/>
       <c r="Y11" s="33"/>
       <c r="Z11" s="33"/>
@@ -2951,7 +2965,9 @@
       <c r="V12" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="W12" s="33"/>
+      <c r="W12" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="X12" s="33"/>
       <c r="Y12" s="33"/>
       <c r="Z12" s="33"/>
@@ -3079,7 +3095,9 @@
       <c r="V13" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="W13" s="33"/>
+      <c r="W13" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="X13" s="33"/>
       <c r="Y13" s="33"/>
       <c r="Z13" s="33"/>
@@ -3205,7 +3223,9 @@
       <c r="V14" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="W14" s="33"/>
+      <c r="W14" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="X14" s="33"/>
       <c r="Y14" s="33"/>
       <c r="Z14" s="33"/>
@@ -3329,7 +3349,9 @@
       <c r="V15" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="W15" s="33"/>
+      <c r="W15" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="X15" s="33"/>
       <c r="Y15" s="33"/>
       <c r="Z15" s="33"/>
@@ -3451,7 +3473,9 @@
       <c r="V16" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="W16" s="33"/>
+      <c r="W16" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="X16" s="33"/>
       <c r="Y16" s="33"/>
       <c r="Z16" s="33"/>
@@ -3571,7 +3595,9 @@
       <c r="V17" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="W17" s="33"/>
+      <c r="W17" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="X17" s="33"/>
       <c r="Y17" s="33"/>
       <c r="Z17" s="33"/>
@@ -3689,7 +3715,9 @@
       <c r="V18" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="W18" s="33"/>
+      <c r="W18" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="X18" s="33"/>
       <c r="Y18" s="33"/>
       <c r="Z18" s="33"/>
@@ -3805,7 +3833,9 @@
       <c r="V19" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="W19" s="33"/>
+      <c r="W19" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="X19" s="33"/>
       <c r="Y19" s="33"/>
       <c r="Z19" s="33"/>
@@ -3919,7 +3949,9 @@
       <c r="T20" s="34"/>
       <c r="U20" s="35"/>
       <c r="V20" s="33"/>
-      <c r="W20" s="33"/>
+      <c r="W20" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="X20" s="33"/>
       <c r="Y20" s="33"/>
       <c r="Z20" s="33"/>

--- a/STL_Study_Tracker.xlsx
+++ b/STL_Study_Tracker.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="174">
   <si>
     <t>STL Topics — Detailed Breakdown</t>
   </si>
@@ -2002,7 +2002,9 @@
       <c r="W5" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="X5" s="33"/>
+      <c r="X5" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Y5" s="33"/>
       <c r="Z5" s="33"/>
       <c r="AA5" s="34"/>
@@ -2146,7 +2148,9 @@
       <c r="W6" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="X6" s="33"/>
+      <c r="X6" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Y6" s="33"/>
       <c r="Z6" s="33"/>
       <c r="AA6" s="34"/>
@@ -2288,7 +2292,9 @@
       <c r="W7" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="X7" s="33"/>
+      <c r="X7" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Y7" s="33"/>
       <c r="Z7" s="33"/>
       <c r="AA7" s="34"/>
@@ -2428,7 +2434,9 @@
       <c r="W8" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="X8" s="33"/>
+      <c r="X8" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Y8" s="33"/>
       <c r="Z8" s="33"/>
       <c r="AA8" s="34"/>
@@ -2566,7 +2574,9 @@
       <c r="W9" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="X9" s="33"/>
+      <c r="X9" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Y9" s="33"/>
       <c r="Z9" s="33"/>
       <c r="AA9" s="34"/>
@@ -2702,7 +2712,9 @@
       <c r="W10" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="X10" s="33"/>
+      <c r="X10" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Y10" s="33"/>
       <c r="Z10" s="33"/>
       <c r="AA10" s="34"/>
@@ -2836,7 +2848,9 @@
       <c r="W11" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="X11" s="33"/>
+      <c r="X11" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Y11" s="33"/>
       <c r="Z11" s="33"/>
       <c r="AA11" s="34"/>
@@ -2968,7 +2982,9 @@
       <c r="W12" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="X12" s="33"/>
+      <c r="X12" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Y12" s="33"/>
       <c r="Z12" s="33"/>
       <c r="AA12" s="34"/>
@@ -3098,7 +3114,9 @@
       <c r="W13" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="X13" s="33"/>
+      <c r="X13" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Y13" s="33"/>
       <c r="Z13" s="33"/>
       <c r="AA13" s="34"/>
@@ -3226,7 +3244,9 @@
       <c r="W14" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="X14" s="33"/>
+      <c r="X14" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Y14" s="33"/>
       <c r="Z14" s="33"/>
       <c r="AA14" s="34"/>
@@ -3352,7 +3372,9 @@
       <c r="W15" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="X15" s="33"/>
+      <c r="X15" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Y15" s="33"/>
       <c r="Z15" s="33"/>
       <c r="AA15" s="34"/>
@@ -3476,7 +3498,9 @@
       <c r="W16" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="X16" s="33"/>
+      <c r="X16" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Y16" s="33"/>
       <c r="Z16" s="33"/>
       <c r="AA16" s="34"/>
@@ -3598,7 +3622,9 @@
       <c r="W17" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="X17" s="33"/>
+      <c r="X17" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Y17" s="33"/>
       <c r="Z17" s="33"/>
       <c r="AA17" s="34"/>
@@ -3718,7 +3744,9 @@
       <c r="W18" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="X18" s="33"/>
+      <c r="X18" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Y18" s="33"/>
       <c r="Z18" s="33"/>
       <c r="AA18" s="34"/>
@@ -3836,7 +3864,9 @@
       <c r="W19" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="X19" s="33"/>
+      <c r="X19" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Y19" s="33"/>
       <c r="Z19" s="33"/>
       <c r="AA19" s="34"/>
@@ -3952,7 +3982,9 @@
       <c r="W20" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="X20" s="33"/>
+      <c r="X20" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Y20" s="33"/>
       <c r="Z20" s="33"/>
       <c r="AA20" s="34"/>
@@ -4066,7 +4098,9 @@
       <c r="U21" s="35"/>
       <c r="V21" s="33"/>
       <c r="W21" s="33"/>
-      <c r="X21" s="33"/>
+      <c r="X21" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Y21" s="33"/>
       <c r="Z21" s="33"/>
       <c r="AA21" s="34"/>

--- a/STL_Study_Tracker.xlsx
+++ b/STL_Study_Tracker.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="174">
   <si>
     <t>STL Topics — Detailed Breakdown</t>
   </si>
@@ -2005,7 +2005,9 @@
       <c r="X5" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Y5" s="33"/>
+      <c r="Y5" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Z5" s="33"/>
       <c r="AA5" s="34"/>
       <c r="AB5" s="35"/>
@@ -2151,7 +2153,9 @@
       <c r="X6" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Y6" s="33"/>
+      <c r="Y6" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Z6" s="33"/>
       <c r="AA6" s="34"/>
       <c r="AB6" s="35"/>
@@ -2295,7 +2299,9 @@
       <c r="X7" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Y7" s="33"/>
+      <c r="Y7" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Z7" s="33"/>
       <c r="AA7" s="34"/>
       <c r="AB7" s="35"/>
@@ -2437,7 +2443,9 @@
       <c r="X8" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Y8" s="33"/>
+      <c r="Y8" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Z8" s="33"/>
       <c r="AA8" s="34"/>
       <c r="AB8" s="35"/>
@@ -2577,7 +2585,9 @@
       <c r="X9" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Y9" s="33"/>
+      <c r="Y9" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Z9" s="33"/>
       <c r="AA9" s="34"/>
       <c r="AB9" s="35"/>
@@ -2715,7 +2725,9 @@
       <c r="X10" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Y10" s="33"/>
+      <c r="Y10" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Z10" s="33"/>
       <c r="AA10" s="34"/>
       <c r="AB10" s="35"/>
@@ -2851,7 +2863,9 @@
       <c r="X11" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Y11" s="33"/>
+      <c r="Y11" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Z11" s="33"/>
       <c r="AA11" s="34"/>
       <c r="AB11" s="35"/>
@@ -2985,7 +2999,9 @@
       <c r="X12" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Y12" s="33"/>
+      <c r="Y12" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Z12" s="33"/>
       <c r="AA12" s="34"/>
       <c r="AB12" s="35"/>
@@ -3117,7 +3133,9 @@
       <c r="X13" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Y13" s="33"/>
+      <c r="Y13" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Z13" s="33"/>
       <c r="AA13" s="34"/>
       <c r="AB13" s="35"/>
@@ -3247,7 +3265,9 @@
       <c r="X14" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Y14" s="33"/>
+      <c r="Y14" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Z14" s="33"/>
       <c r="AA14" s="34"/>
       <c r="AB14" s="35"/>
@@ -3375,7 +3395,9 @@
       <c r="X15" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Y15" s="33"/>
+      <c r="Y15" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Z15" s="33"/>
       <c r="AA15" s="34"/>
       <c r="AB15" s="35"/>
@@ -3501,7 +3523,9 @@
       <c r="X16" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Y16" s="33"/>
+      <c r="Y16" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Z16" s="33"/>
       <c r="AA16" s="34"/>
       <c r="AB16" s="35"/>
@@ -3625,7 +3649,9 @@
       <c r="X17" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Y17" s="33"/>
+      <c r="Y17" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Z17" s="33"/>
       <c r="AA17" s="34"/>
       <c r="AB17" s="35"/>
@@ -3747,7 +3773,9 @@
       <c r="X18" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Y18" s="33"/>
+      <c r="Y18" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Z18" s="33"/>
       <c r="AA18" s="34"/>
       <c r="AB18" s="35"/>
@@ -3867,7 +3895,9 @@
       <c r="X19" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Y19" s="33"/>
+      <c r="Y19" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Z19" s="33"/>
       <c r="AA19" s="34"/>
       <c r="AB19" s="35"/>
@@ -3985,7 +4015,9 @@
       <c r="X20" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Y20" s="33"/>
+      <c r="Y20" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Z20" s="33"/>
       <c r="AA20" s="34"/>
       <c r="AB20" s="35"/>
@@ -4101,7 +4133,9 @@
       <c r="X21" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Y21" s="33"/>
+      <c r="Y21" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Z21" s="33"/>
       <c r="AA21" s="34"/>
       <c r="AB21" s="35"/>
@@ -4215,7 +4249,9 @@
       <c r="V22" s="33"/>
       <c r="W22" s="33"/>
       <c r="X22" s="33"/>
-      <c r="Y22" s="33"/>
+      <c r="Y22" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="Z22" s="33"/>
       <c r="AA22" s="34"/>
       <c r="AB22" s="35"/>

--- a/STL_Study_Tracker.xlsx
+++ b/STL_Study_Tracker.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="174">
   <si>
     <t>STL Topics — Detailed Breakdown</t>
   </si>
@@ -2008,7 +2008,9 @@
       <c r="Y5" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Z5" s="33"/>
+      <c r="Z5" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="AA5" s="34"/>
       <c r="AB5" s="35"/>
       <c r="AC5" s="33"/>
@@ -2156,7 +2158,9 @@
       <c r="Y6" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Z6" s="33"/>
+      <c r="Z6" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="AA6" s="34"/>
       <c r="AB6" s="35"/>
       <c r="AC6" s="33"/>
@@ -2302,7 +2306,9 @@
       <c r="Y7" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Z7" s="33"/>
+      <c r="Z7" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="AA7" s="34"/>
       <c r="AB7" s="35"/>
       <c r="AC7" s="33"/>
@@ -2446,7 +2452,9 @@
       <c r="Y8" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Z8" s="33"/>
+      <c r="Z8" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="AA8" s="34"/>
       <c r="AB8" s="35"/>
       <c r="AC8" s="33"/>
@@ -2588,7 +2596,9 @@
       <c r="Y9" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Z9" s="33"/>
+      <c r="Z9" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="AA9" s="34"/>
       <c r="AB9" s="35"/>
       <c r="AC9" s="33"/>
@@ -2728,7 +2738,9 @@
       <c r="Y10" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Z10" s="33"/>
+      <c r="Z10" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="AA10" s="34"/>
       <c r="AB10" s="35"/>
       <c r="AC10" s="33"/>
@@ -2866,7 +2878,9 @@
       <c r="Y11" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Z11" s="33"/>
+      <c r="Z11" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="AA11" s="34"/>
       <c r="AB11" s="35"/>
       <c r="AC11" s="33"/>
@@ -3002,7 +3016,9 @@
       <c r="Y12" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Z12" s="33"/>
+      <c r="Z12" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="AA12" s="34"/>
       <c r="AB12" s="35"/>
       <c r="AC12" s="33"/>
@@ -3136,7 +3152,9 @@
       <c r="Y13" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Z13" s="33"/>
+      <c r="Z13" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="AA13" s="34"/>
       <c r="AB13" s="35"/>
       <c r="AC13" s="33"/>
@@ -3268,7 +3286,9 @@
       <c r="Y14" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Z14" s="33"/>
+      <c r="Z14" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="AA14" s="34"/>
       <c r="AB14" s="35"/>
       <c r="AC14" s="33"/>
@@ -3398,7 +3418,9 @@
       <c r="Y15" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Z15" s="33"/>
+      <c r="Z15" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="AA15" s="34"/>
       <c r="AB15" s="35"/>
       <c r="AC15" s="33"/>
@@ -3526,7 +3548,9 @@
       <c r="Y16" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Z16" s="33"/>
+      <c r="Z16" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="AA16" s="34"/>
       <c r="AB16" s="35"/>
       <c r="AC16" s="33"/>
@@ -3652,7 +3676,9 @@
       <c r="Y17" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Z17" s="33"/>
+      <c r="Z17" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="AA17" s="34"/>
       <c r="AB17" s="35"/>
       <c r="AC17" s="33"/>
@@ -3776,7 +3802,9 @@
       <c r="Y18" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Z18" s="33"/>
+      <c r="Z18" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="AA18" s="34"/>
       <c r="AB18" s="35"/>
       <c r="AC18" s="33"/>
@@ -3898,7 +3926,9 @@
       <c r="Y19" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Z19" s="33"/>
+      <c r="Z19" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="AA19" s="34"/>
       <c r="AB19" s="35"/>
       <c r="AC19" s="33"/>
@@ -4018,7 +4048,9 @@
       <c r="Y20" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Z20" s="33"/>
+      <c r="Z20" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="AA20" s="34"/>
       <c r="AB20" s="35"/>
       <c r="AC20" s="33"/>
@@ -4136,7 +4168,9 @@
       <c r="Y21" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Z21" s="33"/>
+      <c r="Z21" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="AA21" s="34"/>
       <c r="AB21" s="35"/>
       <c r="AC21" s="33"/>
@@ -4252,7 +4286,9 @@
       <c r="Y22" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="Z22" s="33"/>
+      <c r="Z22" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="AA22" s="34"/>
       <c r="AB22" s="35"/>
       <c r="AC22" s="33"/>
@@ -4366,7 +4402,9 @@
       <c r="W23" s="33"/>
       <c r="X23" s="33"/>
       <c r="Y23" s="33"/>
-      <c r="Z23" s="33"/>
+      <c r="Z23" s="33" t="s">
+        <v>173</v>
+      </c>
       <c r="AA23" s="34"/>
       <c r="AB23" s="35"/>
       <c r="AC23" s="33"/>

--- a/STL_Study_Tracker.xlsx
+++ b/STL_Study_Tracker.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="174">
   <si>
     <t>STL Topics — Detailed Breakdown</t>
   </si>
@@ -677,12 +677,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFf2f2f2"/>
+        <fgColor rgb="FFe8e8e8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8e8e8"/>
+        <fgColor rgb="FFf2f2f2"/>
       </patternFill>
     </fill>
   </fills>
@@ -2011,78 +2011,80 @@
       <c r="Z5" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AA5" s="34"/>
-      <c r="AB5" s="35"/>
+      <c r="AA5" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB5" s="34"/>
       <c r="AC5" s="33"/>
       <c r="AD5" s="33"/>
       <c r="AE5" s="33"/>
       <c r="AF5" s="33"/>
       <c r="AG5" s="33"/>
-      <c r="AH5" s="34"/>
-      <c r="AI5" s="35"/>
+      <c r="AH5" s="35"/>
+      <c r="AI5" s="34"/>
       <c r="AJ5" s="33"/>
       <c r="AK5" s="33"/>
       <c r="AL5" s="33"/>
       <c r="AM5" s="33"/>
       <c r="AN5" s="33"/>
-      <c r="AO5" s="34"/>
-      <c r="AP5" s="35"/>
+      <c r="AO5" s="35"/>
+      <c r="AP5" s="34"/>
       <c r="AQ5" s="33"/>
       <c r="AR5" s="33"/>
       <c r="AS5" s="33"/>
       <c r="AT5" s="33"/>
       <c r="AU5" s="33"/>
-      <c r="AV5" s="34"/>
-      <c r="AW5" s="35"/>
+      <c r="AV5" s="35"/>
+      <c r="AW5" s="34"/>
       <c r="AX5" s="33"/>
       <c r="AY5" s="33"/>
       <c r="AZ5" s="33"/>
       <c r="BA5" s="33"/>
       <c r="BB5" s="33"/>
-      <c r="BC5" s="34"/>
-      <c r="BD5" s="35"/>
+      <c r="BC5" s="35"/>
+      <c r="BD5" s="34"/>
       <c r="BE5" s="33"/>
       <c r="BF5" s="33"/>
       <c r="BG5" s="33"/>
       <c r="BH5" s="33"/>
       <c r="BI5" s="33"/>
-      <c r="BJ5" s="34"/>
-      <c r="BK5" s="35"/>
+      <c r="BJ5" s="35"/>
+      <c r="BK5" s="34"/>
       <c r="BL5" s="33"/>
       <c r="BM5" s="33"/>
       <c r="BN5" s="33"/>
       <c r="BO5" s="33"/>
       <c r="BP5" s="33"/>
-      <c r="BQ5" s="34"/>
-      <c r="BR5" s="35"/>
+      <c r="BQ5" s="35"/>
+      <c r="BR5" s="34"/>
       <c r="BS5" s="33"/>
       <c r="BT5" s="33"/>
       <c r="BU5" s="33"/>
       <c r="BV5" s="33"/>
       <c r="BW5" s="33"/>
-      <c r="BX5" s="34"/>
-      <c r="BY5" s="35"/>
+      <c r="BX5" s="35"/>
+      <c r="BY5" s="34"/>
       <c r="BZ5" s="33"/>
       <c r="CA5" s="33"/>
       <c r="CB5" s="33"/>
       <c r="CC5" s="33"/>
       <c r="CD5" s="33"/>
-      <c r="CE5" s="34"/>
-      <c r="CF5" s="35"/>
+      <c r="CE5" s="35"/>
+      <c r="CF5" s="34"/>
       <c r="CG5" s="33"/>
       <c r="CH5" s="33"/>
       <c r="CI5" s="33"/>
       <c r="CJ5" s="33"/>
       <c r="CK5" s="33"/>
-      <c r="CL5" s="34"/>
-      <c r="CM5" s="35"/>
+      <c r="CL5" s="35"/>
+      <c r="CM5" s="34"/>
       <c r="CN5" s="33"/>
       <c r="CO5" s="33"/>
       <c r="CP5" s="33"/>
       <c r="CQ5" s="33"/>
       <c r="CR5" s="33"/>
-      <c r="CS5" s="34"/>
-      <c r="CT5" s="35"/>
+      <c r="CS5" s="35"/>
+      <c r="CT5" s="34"/>
       <c r="CU5" s="33"/>
       <c r="CV5" s="33"/>
     </row>
@@ -2105,7 +2107,7 @@
       <c r="F6" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G6" s="35"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="33"/>
       <c r="I6" s="33" t="s">
         <v>173</v>
@@ -2161,78 +2163,80 @@
       <c r="Z6" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AA6" s="34"/>
-      <c r="AB6" s="35"/>
+      <c r="AA6" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB6" s="34"/>
       <c r="AC6" s="33"/>
       <c r="AD6" s="33"/>
       <c r="AE6" s="33"/>
       <c r="AF6" s="33"/>
       <c r="AG6" s="33"/>
-      <c r="AH6" s="34"/>
-      <c r="AI6" s="35"/>
+      <c r="AH6" s="35"/>
+      <c r="AI6" s="34"/>
       <c r="AJ6" s="33"/>
       <c r="AK6" s="33"/>
       <c r="AL6" s="33"/>
       <c r="AM6" s="33"/>
       <c r="AN6" s="33"/>
-      <c r="AO6" s="34"/>
-      <c r="AP6" s="35"/>
+      <c r="AO6" s="35"/>
+      <c r="AP6" s="34"/>
       <c r="AQ6" s="33"/>
       <c r="AR6" s="33"/>
       <c r="AS6" s="33"/>
       <c r="AT6" s="33"/>
       <c r="AU6" s="33"/>
-      <c r="AV6" s="34"/>
-      <c r="AW6" s="35"/>
+      <c r="AV6" s="35"/>
+      <c r="AW6" s="34"/>
       <c r="AX6" s="33"/>
       <c r="AY6" s="33"/>
       <c r="AZ6" s="33"/>
       <c r="BA6" s="33"/>
       <c r="BB6" s="33"/>
-      <c r="BC6" s="34"/>
-      <c r="BD6" s="35"/>
+      <c r="BC6" s="35"/>
+      <c r="BD6" s="34"/>
       <c r="BE6" s="33"/>
       <c r="BF6" s="33"/>
       <c r="BG6" s="33"/>
       <c r="BH6" s="33"/>
       <c r="BI6" s="33"/>
-      <c r="BJ6" s="34"/>
-      <c r="BK6" s="35"/>
+      <c r="BJ6" s="35"/>
+      <c r="BK6" s="34"/>
       <c r="BL6" s="33"/>
       <c r="BM6" s="33"/>
       <c r="BN6" s="33"/>
       <c r="BO6" s="33"/>
       <c r="BP6" s="33"/>
-      <c r="BQ6" s="34"/>
-      <c r="BR6" s="35"/>
+      <c r="BQ6" s="35"/>
+      <c r="BR6" s="34"/>
       <c r="BS6" s="33"/>
       <c r="BT6" s="33"/>
       <c r="BU6" s="33"/>
       <c r="BV6" s="33"/>
       <c r="BW6" s="33"/>
-      <c r="BX6" s="34"/>
-      <c r="BY6" s="35"/>
+      <c r="BX6" s="35"/>
+      <c r="BY6" s="34"/>
       <c r="BZ6" s="33"/>
       <c r="CA6" s="33"/>
       <c r="CB6" s="33"/>
       <c r="CC6" s="33"/>
       <c r="CD6" s="33"/>
-      <c r="CE6" s="34"/>
-      <c r="CF6" s="35"/>
+      <c r="CE6" s="35"/>
+      <c r="CF6" s="34"/>
       <c r="CG6" s="33"/>
       <c r="CH6" s="33"/>
       <c r="CI6" s="33"/>
       <c r="CJ6" s="33"/>
       <c r="CK6" s="33"/>
-      <c r="CL6" s="34"/>
-      <c r="CM6" s="35"/>
+      <c r="CL6" s="35"/>
+      <c r="CM6" s="34"/>
       <c r="CN6" s="33"/>
       <c r="CO6" s="33"/>
       <c r="CP6" s="33"/>
       <c r="CQ6" s="33"/>
       <c r="CR6" s="33"/>
-      <c r="CS6" s="34"/>
-      <c r="CT6" s="35"/>
+      <c r="CS6" s="35"/>
+      <c r="CT6" s="34"/>
       <c r="CU6" s="33"/>
       <c r="CV6" s="33"/>
     </row>
@@ -2255,7 +2259,7 @@
       <c r="F7" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
       <c r="J7" s="33" t="s">
@@ -2309,78 +2313,80 @@
       <c r="Z7" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AA7" s="34"/>
-      <c r="AB7" s="35"/>
+      <c r="AA7" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB7" s="34"/>
       <c r="AC7" s="33"/>
       <c r="AD7" s="33"/>
       <c r="AE7" s="33"/>
       <c r="AF7" s="33"/>
       <c r="AG7" s="33"/>
-      <c r="AH7" s="34"/>
-      <c r="AI7" s="35"/>
+      <c r="AH7" s="35"/>
+      <c r="AI7" s="34"/>
       <c r="AJ7" s="33"/>
       <c r="AK7" s="33"/>
       <c r="AL7" s="33"/>
       <c r="AM7" s="33"/>
       <c r="AN7" s="33"/>
-      <c r="AO7" s="34"/>
-      <c r="AP7" s="35"/>
+      <c r="AO7" s="35"/>
+      <c r="AP7" s="34"/>
       <c r="AQ7" s="33"/>
       <c r="AR7" s="33"/>
       <c r="AS7" s="33"/>
       <c r="AT7" s="33"/>
       <c r="AU7" s="33"/>
-      <c r="AV7" s="34"/>
-      <c r="AW7" s="35"/>
+      <c r="AV7" s="35"/>
+      <c r="AW7" s="34"/>
       <c r="AX7" s="33"/>
       <c r="AY7" s="33"/>
       <c r="AZ7" s="33"/>
       <c r="BA7" s="33"/>
       <c r="BB7" s="33"/>
-      <c r="BC7" s="34"/>
-      <c r="BD7" s="35"/>
+      <c r="BC7" s="35"/>
+      <c r="BD7" s="34"/>
       <c r="BE7" s="33"/>
       <c r="BF7" s="33"/>
       <c r="BG7" s="33"/>
       <c r="BH7" s="33"/>
       <c r="BI7" s="33"/>
-      <c r="BJ7" s="34"/>
-      <c r="BK7" s="35"/>
+      <c r="BJ7" s="35"/>
+      <c r="BK7" s="34"/>
       <c r="BL7" s="33"/>
       <c r="BM7" s="33"/>
       <c r="BN7" s="33"/>
       <c r="BO7" s="33"/>
       <c r="BP7" s="33"/>
-      <c r="BQ7" s="34"/>
-      <c r="BR7" s="35"/>
+      <c r="BQ7" s="35"/>
+      <c r="BR7" s="34"/>
       <c r="BS7" s="33"/>
       <c r="BT7" s="33"/>
       <c r="BU7" s="33"/>
       <c r="BV7" s="33"/>
       <c r="BW7" s="33"/>
-      <c r="BX7" s="34"/>
-      <c r="BY7" s="35"/>
+      <c r="BX7" s="35"/>
+      <c r="BY7" s="34"/>
       <c r="BZ7" s="33"/>
       <c r="CA7" s="33"/>
       <c r="CB7" s="33"/>
       <c r="CC7" s="33"/>
       <c r="CD7" s="33"/>
-      <c r="CE7" s="34"/>
-      <c r="CF7" s="35"/>
+      <c r="CE7" s="35"/>
+      <c r="CF7" s="34"/>
       <c r="CG7" s="33"/>
       <c r="CH7" s="33"/>
       <c r="CI7" s="33"/>
       <c r="CJ7" s="33"/>
       <c r="CK7" s="33"/>
-      <c r="CL7" s="34"/>
-      <c r="CM7" s="35"/>
+      <c r="CL7" s="35"/>
+      <c r="CM7" s="34"/>
       <c r="CN7" s="33"/>
       <c r="CO7" s="33"/>
       <c r="CP7" s="33"/>
       <c r="CQ7" s="33"/>
       <c r="CR7" s="33"/>
-      <c r="CS7" s="34"/>
-      <c r="CT7" s="35"/>
+      <c r="CS7" s="35"/>
+      <c r="CT7" s="34"/>
       <c r="CU7" s="33"/>
       <c r="CV7" s="33"/>
     </row>
@@ -2403,7 +2409,7 @@
       <c r="F8" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G8" s="35"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
       <c r="J8" s="33"/>
@@ -2455,78 +2461,80 @@
       <c r="Z8" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AA8" s="34"/>
-      <c r="AB8" s="35"/>
+      <c r="AA8" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB8" s="34"/>
       <c r="AC8" s="33"/>
       <c r="AD8" s="33"/>
       <c r="AE8" s="33"/>
       <c r="AF8" s="33"/>
       <c r="AG8" s="33"/>
-      <c r="AH8" s="34"/>
-      <c r="AI8" s="35"/>
+      <c r="AH8" s="35"/>
+      <c r="AI8" s="34"/>
       <c r="AJ8" s="33"/>
       <c r="AK8" s="33"/>
       <c r="AL8" s="33"/>
       <c r="AM8" s="33"/>
       <c r="AN8" s="33"/>
-      <c r="AO8" s="34"/>
-      <c r="AP8" s="35"/>
+      <c r="AO8" s="35"/>
+      <c r="AP8" s="34"/>
       <c r="AQ8" s="33"/>
       <c r="AR8" s="33"/>
       <c r="AS8" s="33"/>
       <c r="AT8" s="33"/>
       <c r="AU8" s="33"/>
-      <c r="AV8" s="34"/>
-      <c r="AW8" s="35"/>
+      <c r="AV8" s="35"/>
+      <c r="AW8" s="34"/>
       <c r="AX8" s="33"/>
       <c r="AY8" s="33"/>
       <c r="AZ8" s="33"/>
       <c r="BA8" s="33"/>
       <c r="BB8" s="33"/>
-      <c r="BC8" s="34"/>
-      <c r="BD8" s="35"/>
+      <c r="BC8" s="35"/>
+      <c r="BD8" s="34"/>
       <c r="BE8" s="33"/>
       <c r="BF8" s="33"/>
       <c r="BG8" s="33"/>
       <c r="BH8" s="33"/>
       <c r="BI8" s="33"/>
-      <c r="BJ8" s="34"/>
-      <c r="BK8" s="35"/>
+      <c r="BJ8" s="35"/>
+      <c r="BK8" s="34"/>
       <c r="BL8" s="33"/>
       <c r="BM8" s="33"/>
       <c r="BN8" s="33"/>
       <c r="BO8" s="33"/>
       <c r="BP8" s="33"/>
-      <c r="BQ8" s="34"/>
-      <c r="BR8" s="35"/>
+      <c r="BQ8" s="35"/>
+      <c r="BR8" s="34"/>
       <c r="BS8" s="33"/>
       <c r="BT8" s="33"/>
       <c r="BU8" s="33"/>
       <c r="BV8" s="33"/>
       <c r="BW8" s="33"/>
-      <c r="BX8" s="34"/>
-      <c r="BY8" s="35"/>
+      <c r="BX8" s="35"/>
+      <c r="BY8" s="34"/>
       <c r="BZ8" s="33"/>
       <c r="CA8" s="33"/>
       <c r="CB8" s="33"/>
       <c r="CC8" s="33"/>
       <c r="CD8" s="33"/>
-      <c r="CE8" s="34"/>
-      <c r="CF8" s="35"/>
+      <c r="CE8" s="35"/>
+      <c r="CF8" s="34"/>
       <c r="CG8" s="33"/>
       <c r="CH8" s="33"/>
       <c r="CI8" s="33"/>
       <c r="CJ8" s="33"/>
       <c r="CK8" s="33"/>
-      <c r="CL8" s="34"/>
-      <c r="CM8" s="35"/>
+      <c r="CL8" s="35"/>
+      <c r="CM8" s="34"/>
       <c r="CN8" s="33"/>
       <c r="CO8" s="33"/>
       <c r="CP8" s="33"/>
       <c r="CQ8" s="33"/>
       <c r="CR8" s="33"/>
-      <c r="CS8" s="34"/>
-      <c r="CT8" s="35"/>
+      <c r="CS8" s="35"/>
+      <c r="CT8" s="34"/>
       <c r="CU8" s="33"/>
       <c r="CV8" s="33"/>
     </row>
@@ -2549,7 +2557,7 @@
       <c r="F9" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
       <c r="J9" s="33"/>
@@ -2599,78 +2607,80 @@
       <c r="Z9" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AA9" s="34"/>
-      <c r="AB9" s="35"/>
+      <c r="AA9" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB9" s="34"/>
       <c r="AC9" s="33"/>
       <c r="AD9" s="33"/>
       <c r="AE9" s="33"/>
       <c r="AF9" s="33"/>
       <c r="AG9" s="33"/>
-      <c r="AH9" s="34"/>
-      <c r="AI9" s="35"/>
+      <c r="AH9" s="35"/>
+      <c r="AI9" s="34"/>
       <c r="AJ9" s="33"/>
       <c r="AK9" s="33"/>
       <c r="AL9" s="33"/>
       <c r="AM9" s="33"/>
       <c r="AN9" s="33"/>
-      <c r="AO9" s="34"/>
-      <c r="AP9" s="35"/>
+      <c r="AO9" s="35"/>
+      <c r="AP9" s="34"/>
       <c r="AQ9" s="33"/>
       <c r="AR9" s="33"/>
       <c r="AS9" s="33"/>
       <c r="AT9" s="33"/>
       <c r="AU9" s="33"/>
-      <c r="AV9" s="34"/>
-      <c r="AW9" s="35"/>
+      <c r="AV9" s="35"/>
+      <c r="AW9" s="34"/>
       <c r="AX9" s="33"/>
       <c r="AY9" s="33"/>
       <c r="AZ9" s="33"/>
       <c r="BA9" s="33"/>
       <c r="BB9" s="33"/>
-      <c r="BC9" s="34"/>
-      <c r="BD9" s="35"/>
+      <c r="BC9" s="35"/>
+      <c r="BD9" s="34"/>
       <c r="BE9" s="33"/>
       <c r="BF9" s="33"/>
       <c r="BG9" s="33"/>
       <c r="BH9" s="33"/>
       <c r="BI9" s="33"/>
-      <c r="BJ9" s="34"/>
-      <c r="BK9" s="35"/>
+      <c r="BJ9" s="35"/>
+      <c r="BK9" s="34"/>
       <c r="BL9" s="33"/>
       <c r="BM9" s="33"/>
       <c r="BN9" s="33"/>
       <c r="BO9" s="33"/>
       <c r="BP9" s="33"/>
-      <c r="BQ9" s="34"/>
-      <c r="BR9" s="35"/>
+      <c r="BQ9" s="35"/>
+      <c r="BR9" s="34"/>
       <c r="BS9" s="33"/>
       <c r="BT9" s="33"/>
       <c r="BU9" s="33"/>
       <c r="BV9" s="33"/>
       <c r="BW9" s="33"/>
-      <c r="BX9" s="34"/>
-      <c r="BY9" s="35"/>
+      <c r="BX9" s="35"/>
+      <c r="BY9" s="34"/>
       <c r="BZ9" s="33"/>
       <c r="CA9" s="33"/>
       <c r="CB9" s="33"/>
       <c r="CC9" s="33"/>
       <c r="CD9" s="33"/>
-      <c r="CE9" s="34"/>
-      <c r="CF9" s="35"/>
+      <c r="CE9" s="35"/>
+      <c r="CF9" s="34"/>
       <c r="CG9" s="33"/>
       <c r="CH9" s="33"/>
       <c r="CI9" s="33"/>
       <c r="CJ9" s="33"/>
       <c r="CK9" s="33"/>
-      <c r="CL9" s="34"/>
-      <c r="CM9" s="35"/>
+      <c r="CL9" s="35"/>
+      <c r="CM9" s="34"/>
       <c r="CN9" s="33"/>
       <c r="CO9" s="33"/>
       <c r="CP9" s="33"/>
       <c r="CQ9" s="33"/>
       <c r="CR9" s="33"/>
-      <c r="CS9" s="34"/>
-      <c r="CT9" s="35"/>
+      <c r="CS9" s="35"/>
+      <c r="CT9" s="34"/>
       <c r="CU9" s="33"/>
       <c r="CV9" s="33"/>
     </row>
@@ -2693,7 +2703,7 @@
       <c r="F10" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G10" s="35"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="33"/>
       <c r="I10" s="33"/>
       <c r="J10" s="33"/>
@@ -2741,78 +2751,80 @@
       <c r="Z10" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AA10" s="34"/>
-      <c r="AB10" s="35"/>
+      <c r="AA10" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB10" s="34"/>
       <c r="AC10" s="33"/>
       <c r="AD10" s="33"/>
       <c r="AE10" s="33"/>
       <c r="AF10" s="33"/>
       <c r="AG10" s="33"/>
-      <c r="AH10" s="34"/>
-      <c r="AI10" s="35"/>
+      <c r="AH10" s="35"/>
+      <c r="AI10" s="34"/>
       <c r="AJ10" s="33"/>
       <c r="AK10" s="33"/>
       <c r="AL10" s="33"/>
       <c r="AM10" s="33"/>
       <c r="AN10" s="33"/>
-      <c r="AO10" s="34"/>
-      <c r="AP10" s="35"/>
+      <c r="AO10" s="35"/>
+      <c r="AP10" s="34"/>
       <c r="AQ10" s="33"/>
       <c r="AR10" s="33"/>
       <c r="AS10" s="33"/>
       <c r="AT10" s="33"/>
       <c r="AU10" s="33"/>
-      <c r="AV10" s="34"/>
-      <c r="AW10" s="35"/>
+      <c r="AV10" s="35"/>
+      <c r="AW10" s="34"/>
       <c r="AX10" s="33"/>
       <c r="AY10" s="33"/>
       <c r="AZ10" s="33"/>
       <c r="BA10" s="33"/>
       <c r="BB10" s="33"/>
-      <c r="BC10" s="34"/>
-      <c r="BD10" s="35"/>
+      <c r="BC10" s="35"/>
+      <c r="BD10" s="34"/>
       <c r="BE10" s="33"/>
       <c r="BF10" s="33"/>
       <c r="BG10" s="33"/>
       <c r="BH10" s="33"/>
       <c r="BI10" s="33"/>
-      <c r="BJ10" s="34"/>
-      <c r="BK10" s="35"/>
+      <c r="BJ10" s="35"/>
+      <c r="BK10" s="34"/>
       <c r="BL10" s="33"/>
       <c r="BM10" s="33"/>
       <c r="BN10" s="33"/>
       <c r="BO10" s="33"/>
       <c r="BP10" s="33"/>
-      <c r="BQ10" s="34"/>
-      <c r="BR10" s="35"/>
+      <c r="BQ10" s="35"/>
+      <c r="BR10" s="34"/>
       <c r="BS10" s="33"/>
       <c r="BT10" s="33"/>
       <c r="BU10" s="33"/>
       <c r="BV10" s="33"/>
       <c r="BW10" s="33"/>
-      <c r="BX10" s="34"/>
-      <c r="BY10" s="35"/>
+      <c r="BX10" s="35"/>
+      <c r="BY10" s="34"/>
       <c r="BZ10" s="33"/>
       <c r="CA10" s="33"/>
       <c r="CB10" s="33"/>
       <c r="CC10" s="33"/>
       <c r="CD10" s="33"/>
-      <c r="CE10" s="34"/>
-      <c r="CF10" s="35"/>
+      <c r="CE10" s="35"/>
+      <c r="CF10" s="34"/>
       <c r="CG10" s="33"/>
       <c r="CH10" s="33"/>
       <c r="CI10" s="33"/>
       <c r="CJ10" s="33"/>
       <c r="CK10" s="33"/>
-      <c r="CL10" s="34"/>
-      <c r="CM10" s="35"/>
+      <c r="CL10" s="35"/>
+      <c r="CM10" s="34"/>
       <c r="CN10" s="33"/>
       <c r="CO10" s="33"/>
       <c r="CP10" s="33"/>
       <c r="CQ10" s="33"/>
       <c r="CR10" s="33"/>
-      <c r="CS10" s="34"/>
-      <c r="CT10" s="35"/>
+      <c r="CS10" s="35"/>
+      <c r="CT10" s="34"/>
       <c r="CU10" s="33"/>
       <c r="CV10" s="33"/>
     </row>
@@ -2835,13 +2847,13 @@
       <c r="F11" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G11" s="35"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="33"/>
       <c r="I11" s="33"/>
       <c r="J11" s="33"/>
       <c r="K11" s="33"/>
       <c r="L11" s="33"/>
-      <c r="M11" s="34"/>
+      <c r="M11" s="35"/>
       <c r="N11" s="33" t="s">
         <v>173</v>
       </c>
@@ -2881,78 +2893,80 @@
       <c r="Z11" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AA11" s="34"/>
-      <c r="AB11" s="35"/>
+      <c r="AA11" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB11" s="34"/>
       <c r="AC11" s="33"/>
       <c r="AD11" s="33"/>
       <c r="AE11" s="33"/>
       <c r="AF11" s="33"/>
       <c r="AG11" s="33"/>
-      <c r="AH11" s="34"/>
-      <c r="AI11" s="35"/>
+      <c r="AH11" s="35"/>
+      <c r="AI11" s="34"/>
       <c r="AJ11" s="33"/>
       <c r="AK11" s="33"/>
       <c r="AL11" s="33"/>
       <c r="AM11" s="33"/>
       <c r="AN11" s="33"/>
-      <c r="AO11" s="34"/>
-      <c r="AP11" s="35"/>
+      <c r="AO11" s="35"/>
+      <c r="AP11" s="34"/>
       <c r="AQ11" s="33"/>
       <c r="AR11" s="33"/>
       <c r="AS11" s="33"/>
       <c r="AT11" s="33"/>
       <c r="AU11" s="33"/>
-      <c r="AV11" s="34"/>
-      <c r="AW11" s="35"/>
+      <c r="AV11" s="35"/>
+      <c r="AW11" s="34"/>
       <c r="AX11" s="33"/>
       <c r="AY11" s="33"/>
       <c r="AZ11" s="33"/>
       <c r="BA11" s="33"/>
       <c r="BB11" s="33"/>
-      <c r="BC11" s="34"/>
-      <c r="BD11" s="35"/>
+      <c r="BC11" s="35"/>
+      <c r="BD11" s="34"/>
       <c r="BE11" s="33"/>
       <c r="BF11" s="33"/>
       <c r="BG11" s="33"/>
       <c r="BH11" s="33"/>
       <c r="BI11" s="33"/>
-      <c r="BJ11" s="34"/>
-      <c r="BK11" s="35"/>
+      <c r="BJ11" s="35"/>
+      <c r="BK11" s="34"/>
       <c r="BL11" s="33"/>
       <c r="BM11" s="33"/>
       <c r="BN11" s="33"/>
       <c r="BO11" s="33"/>
       <c r="BP11" s="33"/>
-      <c r="BQ11" s="34"/>
-      <c r="BR11" s="35"/>
+      <c r="BQ11" s="35"/>
+      <c r="BR11" s="34"/>
       <c r="BS11" s="33"/>
       <c r="BT11" s="33"/>
       <c r="BU11" s="33"/>
       <c r="BV11" s="33"/>
       <c r="BW11" s="33"/>
-      <c r="BX11" s="34"/>
-      <c r="BY11" s="35"/>
+      <c r="BX11" s="35"/>
+      <c r="BY11" s="34"/>
       <c r="BZ11" s="33"/>
       <c r="CA11" s="33"/>
       <c r="CB11" s="33"/>
       <c r="CC11" s="33"/>
       <c r="CD11" s="33"/>
-      <c r="CE11" s="34"/>
-      <c r="CF11" s="35"/>
+      <c r="CE11" s="35"/>
+      <c r="CF11" s="34"/>
       <c r="CG11" s="33"/>
       <c r="CH11" s="33"/>
       <c r="CI11" s="33"/>
       <c r="CJ11" s="33"/>
       <c r="CK11" s="33"/>
-      <c r="CL11" s="34"/>
-      <c r="CM11" s="35"/>
+      <c r="CL11" s="35"/>
+      <c r="CM11" s="34"/>
       <c r="CN11" s="33"/>
       <c r="CO11" s="33"/>
       <c r="CP11" s="33"/>
       <c r="CQ11" s="33"/>
       <c r="CR11" s="33"/>
-      <c r="CS11" s="34"/>
-      <c r="CT11" s="35"/>
+      <c r="CS11" s="35"/>
+      <c r="CT11" s="34"/>
       <c r="CU11" s="33"/>
       <c r="CV11" s="33"/>
     </row>
@@ -2975,14 +2989,14 @@
       <c r="F12" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G12" s="35"/>
+      <c r="G12" s="34"/>
       <c r="H12" s="33"/>
       <c r="I12" s="33"/>
       <c r="J12" s="33"/>
       <c r="K12" s="33"/>
       <c r="L12" s="33"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="34"/>
       <c r="O12" s="33" t="s">
         <v>173</v>
       </c>
@@ -3019,78 +3033,80 @@
       <c r="Z12" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AA12" s="34"/>
-      <c r="AB12" s="35"/>
+      <c r="AA12" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB12" s="34"/>
       <c r="AC12" s="33"/>
       <c r="AD12" s="33"/>
       <c r="AE12" s="33"/>
       <c r="AF12" s="33"/>
       <c r="AG12" s="33"/>
-      <c r="AH12" s="34"/>
-      <c r="AI12" s="35"/>
+      <c r="AH12" s="35"/>
+      <c r="AI12" s="34"/>
       <c r="AJ12" s="33"/>
       <c r="AK12" s="33"/>
       <c r="AL12" s="33"/>
       <c r="AM12" s="33"/>
       <c r="AN12" s="33"/>
-      <c r="AO12" s="34"/>
-      <c r="AP12" s="35"/>
+      <c r="AO12" s="35"/>
+      <c r="AP12" s="34"/>
       <c r="AQ12" s="33"/>
       <c r="AR12" s="33"/>
       <c r="AS12" s="33"/>
       <c r="AT12" s="33"/>
       <c r="AU12" s="33"/>
-      <c r="AV12" s="34"/>
-      <c r="AW12" s="35"/>
+      <c r="AV12" s="35"/>
+      <c r="AW12" s="34"/>
       <c r="AX12" s="33"/>
       <c r="AY12" s="33"/>
       <c r="AZ12" s="33"/>
       <c r="BA12" s="33"/>
       <c r="BB12" s="33"/>
-      <c r="BC12" s="34"/>
-      <c r="BD12" s="35"/>
+      <c r="BC12" s="35"/>
+      <c r="BD12" s="34"/>
       <c r="BE12" s="33"/>
       <c r="BF12" s="33"/>
       <c r="BG12" s="33"/>
       <c r="BH12" s="33"/>
       <c r="BI12" s="33"/>
-      <c r="BJ12" s="34"/>
-      <c r="BK12" s="35"/>
+      <c r="BJ12" s="35"/>
+      <c r="BK12" s="34"/>
       <c r="BL12" s="33"/>
       <c r="BM12" s="33"/>
       <c r="BN12" s="33"/>
       <c r="BO12" s="33"/>
       <c r="BP12" s="33"/>
-      <c r="BQ12" s="34"/>
-      <c r="BR12" s="35"/>
+      <c r="BQ12" s="35"/>
+      <c r="BR12" s="34"/>
       <c r="BS12" s="33"/>
       <c r="BT12" s="33"/>
       <c r="BU12" s="33"/>
       <c r="BV12" s="33"/>
       <c r="BW12" s="33"/>
-      <c r="BX12" s="34"/>
-      <c r="BY12" s="35"/>
+      <c r="BX12" s="35"/>
+      <c r="BY12" s="34"/>
       <c r="BZ12" s="33"/>
       <c r="CA12" s="33"/>
       <c r="CB12" s="33"/>
       <c r="CC12" s="33"/>
       <c r="CD12" s="33"/>
-      <c r="CE12" s="34"/>
-      <c r="CF12" s="35"/>
+      <c r="CE12" s="35"/>
+      <c r="CF12" s="34"/>
       <c r="CG12" s="33"/>
       <c r="CH12" s="33"/>
       <c r="CI12" s="33"/>
       <c r="CJ12" s="33"/>
       <c r="CK12" s="33"/>
-      <c r="CL12" s="34"/>
-      <c r="CM12" s="35"/>
+      <c r="CL12" s="35"/>
+      <c r="CM12" s="34"/>
       <c r="CN12" s="33"/>
       <c r="CO12" s="33"/>
       <c r="CP12" s="33"/>
       <c r="CQ12" s="33"/>
       <c r="CR12" s="33"/>
-      <c r="CS12" s="34"/>
-      <c r="CT12" s="35"/>
+      <c r="CS12" s="35"/>
+      <c r="CT12" s="34"/>
       <c r="CU12" s="33"/>
       <c r="CV12" s="33"/>
     </row>
@@ -3113,14 +3129,14 @@
       <c r="F13" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G13" s="35"/>
+      <c r="G13" s="34"/>
       <c r="H13" s="33"/>
       <c r="I13" s="33"/>
       <c r="J13" s="33"/>
       <c r="K13" s="33"/>
       <c r="L13" s="33"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="34"/>
       <c r="O13" s="33"/>
       <c r="P13" s="33" t="s">
         <v>173</v>
@@ -3155,78 +3171,80 @@
       <c r="Z13" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AA13" s="34"/>
-      <c r="AB13" s="35"/>
+      <c r="AA13" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB13" s="34"/>
       <c r="AC13" s="33"/>
       <c r="AD13" s="33"/>
       <c r="AE13" s="33"/>
       <c r="AF13" s="33"/>
       <c r="AG13" s="33"/>
-      <c r="AH13" s="34"/>
-      <c r="AI13" s="35"/>
+      <c r="AH13" s="35"/>
+      <c r="AI13" s="34"/>
       <c r="AJ13" s="33"/>
       <c r="AK13" s="33"/>
       <c r="AL13" s="33"/>
       <c r="AM13" s="33"/>
       <c r="AN13" s="33"/>
-      <c r="AO13" s="34"/>
-      <c r="AP13" s="35"/>
+      <c r="AO13" s="35"/>
+      <c r="AP13" s="34"/>
       <c r="AQ13" s="33"/>
       <c r="AR13" s="33"/>
       <c r="AS13" s="33"/>
       <c r="AT13" s="33"/>
       <c r="AU13" s="33"/>
-      <c r="AV13" s="34"/>
-      <c r="AW13" s="35"/>
+      <c r="AV13" s="35"/>
+      <c r="AW13" s="34"/>
       <c r="AX13" s="33"/>
       <c r="AY13" s="33"/>
       <c r="AZ13" s="33"/>
       <c r="BA13" s="33"/>
       <c r="BB13" s="33"/>
-      <c r="BC13" s="34"/>
-      <c r="BD13" s="35"/>
+      <c r="BC13" s="35"/>
+      <c r="BD13" s="34"/>
       <c r="BE13" s="33"/>
       <c r="BF13" s="33"/>
       <c r="BG13" s="33"/>
       <c r="BH13" s="33"/>
       <c r="BI13" s="33"/>
-      <c r="BJ13" s="34"/>
-      <c r="BK13" s="35"/>
+      <c r="BJ13" s="35"/>
+      <c r="BK13" s="34"/>
       <c r="BL13" s="33"/>
       <c r="BM13" s="33"/>
       <c r="BN13" s="33"/>
       <c r="BO13" s="33"/>
       <c r="BP13" s="33"/>
-      <c r="BQ13" s="34"/>
-      <c r="BR13" s="35"/>
+      <c r="BQ13" s="35"/>
+      <c r="BR13" s="34"/>
       <c r="BS13" s="33"/>
       <c r="BT13" s="33"/>
       <c r="BU13" s="33"/>
       <c r="BV13" s="33"/>
       <c r="BW13" s="33"/>
-      <c r="BX13" s="34"/>
-      <c r="BY13" s="35"/>
+      <c r="BX13" s="35"/>
+      <c r="BY13" s="34"/>
       <c r="BZ13" s="33"/>
       <c r="CA13" s="33"/>
       <c r="CB13" s="33"/>
       <c r="CC13" s="33"/>
       <c r="CD13" s="33"/>
-      <c r="CE13" s="34"/>
-      <c r="CF13" s="35"/>
+      <c r="CE13" s="35"/>
+      <c r="CF13" s="34"/>
       <c r="CG13" s="33"/>
       <c r="CH13" s="33"/>
       <c r="CI13" s="33"/>
       <c r="CJ13" s="33"/>
       <c r="CK13" s="33"/>
-      <c r="CL13" s="34"/>
-      <c r="CM13" s="35"/>
+      <c r="CL13" s="35"/>
+      <c r="CM13" s="34"/>
       <c r="CN13" s="33"/>
       <c r="CO13" s="33"/>
       <c r="CP13" s="33"/>
       <c r="CQ13" s="33"/>
       <c r="CR13" s="33"/>
-      <c r="CS13" s="34"/>
-      <c r="CT13" s="35"/>
+      <c r="CS13" s="35"/>
+      <c r="CT13" s="34"/>
       <c r="CU13" s="33"/>
       <c r="CV13" s="33"/>
     </row>
@@ -3249,14 +3267,14 @@
       <c r="F14" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G14" s="35"/>
+      <c r="G14" s="34"/>
       <c r="H14" s="33"/>
       <c r="I14" s="33"/>
       <c r="J14" s="33"/>
       <c r="K14" s="33"/>
       <c r="L14" s="33"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="34"/>
       <c r="O14" s="33"/>
       <c r="P14" s="33"/>
       <c r="Q14" s="33" t="s">
@@ -3289,78 +3307,80 @@
       <c r="Z14" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AA14" s="34"/>
-      <c r="AB14" s="35"/>
+      <c r="AA14" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB14" s="34"/>
       <c r="AC14" s="33"/>
       <c r="AD14" s="33"/>
       <c r="AE14" s="33"/>
       <c r="AF14" s="33"/>
       <c r="AG14" s="33"/>
-      <c r="AH14" s="34"/>
-      <c r="AI14" s="35"/>
+      <c r="AH14" s="35"/>
+      <c r="AI14" s="34"/>
       <c r="AJ14" s="33"/>
       <c r="AK14" s="33"/>
       <c r="AL14" s="33"/>
       <c r="AM14" s="33"/>
       <c r="AN14" s="33"/>
-      <c r="AO14" s="34"/>
-      <c r="AP14" s="35"/>
+      <c r="AO14" s="35"/>
+      <c r="AP14" s="34"/>
       <c r="AQ14" s="33"/>
       <c r="AR14" s="33"/>
       <c r="AS14" s="33"/>
       <c r="AT14" s="33"/>
       <c r="AU14" s="33"/>
-      <c r="AV14" s="34"/>
-      <c r="AW14" s="35"/>
+      <c r="AV14" s="35"/>
+      <c r="AW14" s="34"/>
       <c r="AX14" s="33"/>
       <c r="AY14" s="33"/>
       <c r="AZ14" s="33"/>
       <c r="BA14" s="33"/>
       <c r="BB14" s="33"/>
-      <c r="BC14" s="34"/>
-      <c r="BD14" s="35"/>
+      <c r="BC14" s="35"/>
+      <c r="BD14" s="34"/>
       <c r="BE14" s="33"/>
       <c r="BF14" s="33"/>
       <c r="BG14" s="33"/>
       <c r="BH14" s="33"/>
       <c r="BI14" s="33"/>
-      <c r="BJ14" s="34"/>
-      <c r="BK14" s="35"/>
+      <c r="BJ14" s="35"/>
+      <c r="BK14" s="34"/>
       <c r="BL14" s="33"/>
       <c r="BM14" s="33"/>
       <c r="BN14" s="33"/>
       <c r="BO14" s="33"/>
       <c r="BP14" s="33"/>
-      <c r="BQ14" s="34"/>
-      <c r="BR14" s="35"/>
+      <c r="BQ14" s="35"/>
+      <c r="BR14" s="34"/>
       <c r="BS14" s="33"/>
       <c r="BT14" s="33"/>
       <c r="BU14" s="33"/>
       <c r="BV14" s="33"/>
       <c r="BW14" s="33"/>
-      <c r="BX14" s="34"/>
-      <c r="BY14" s="35"/>
+      <c r="BX14" s="35"/>
+      <c r="BY14" s="34"/>
       <c r="BZ14" s="33"/>
       <c r="CA14" s="33"/>
       <c r="CB14" s="33"/>
       <c r="CC14" s="33"/>
       <c r="CD14" s="33"/>
-      <c r="CE14" s="34"/>
-      <c r="CF14" s="35"/>
+      <c r="CE14" s="35"/>
+      <c r="CF14" s="34"/>
       <c r="CG14" s="33"/>
       <c r="CH14" s="33"/>
       <c r="CI14" s="33"/>
       <c r="CJ14" s="33"/>
       <c r="CK14" s="33"/>
-      <c r="CL14" s="34"/>
-      <c r="CM14" s="35"/>
+      <c r="CL14" s="35"/>
+      <c r="CM14" s="34"/>
       <c r="CN14" s="33"/>
       <c r="CO14" s="33"/>
       <c r="CP14" s="33"/>
       <c r="CQ14" s="33"/>
       <c r="CR14" s="33"/>
-      <c r="CS14" s="34"/>
-      <c r="CT14" s="35"/>
+      <c r="CS14" s="35"/>
+      <c r="CT14" s="34"/>
       <c r="CU14" s="33"/>
       <c r="CV14" s="33"/>
     </row>
@@ -3383,14 +3403,14 @@
       <c r="F15" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G15" s="35"/>
+      <c r="G15" s="34"/>
       <c r="H15" s="33"/>
       <c r="I15" s="33"/>
       <c r="J15" s="33"/>
       <c r="K15" s="33"/>
       <c r="L15" s="33"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="34"/>
       <c r="O15" s="33"/>
       <c r="P15" s="33"/>
       <c r="Q15" s="33"/>
@@ -3421,78 +3441,80 @@
       <c r="Z15" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AA15" s="34"/>
-      <c r="AB15" s="35"/>
+      <c r="AA15" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB15" s="34"/>
       <c r="AC15" s="33"/>
       <c r="AD15" s="33"/>
       <c r="AE15" s="33"/>
       <c r="AF15" s="33"/>
       <c r="AG15" s="33"/>
-      <c r="AH15" s="34"/>
-      <c r="AI15" s="35"/>
+      <c r="AH15" s="35"/>
+      <c r="AI15" s="34"/>
       <c r="AJ15" s="33"/>
       <c r="AK15" s="33"/>
       <c r="AL15" s="33"/>
       <c r="AM15" s="33"/>
       <c r="AN15" s="33"/>
-      <c r="AO15" s="34"/>
-      <c r="AP15" s="35"/>
+      <c r="AO15" s="35"/>
+      <c r="AP15" s="34"/>
       <c r="AQ15" s="33"/>
       <c r="AR15" s="33"/>
       <c r="AS15" s="33"/>
       <c r="AT15" s="33"/>
       <c r="AU15" s="33"/>
-      <c r="AV15" s="34"/>
-      <c r="AW15" s="35"/>
+      <c r="AV15" s="35"/>
+      <c r="AW15" s="34"/>
       <c r="AX15" s="33"/>
       <c r="AY15" s="33"/>
       <c r="AZ15" s="33"/>
       <c r="BA15" s="33"/>
       <c r="BB15" s="33"/>
-      <c r="BC15" s="34"/>
-      <c r="BD15" s="35"/>
+      <c r="BC15" s="35"/>
+      <c r="BD15" s="34"/>
       <c r="BE15" s="33"/>
       <c r="BF15" s="33"/>
       <c r="BG15" s="33"/>
       <c r="BH15" s="33"/>
       <c r="BI15" s="33"/>
-      <c r="BJ15" s="34"/>
-      <c r="BK15" s="35"/>
+      <c r="BJ15" s="35"/>
+      <c r="BK15" s="34"/>
       <c r="BL15" s="33"/>
       <c r="BM15" s="33"/>
       <c r="BN15" s="33"/>
       <c r="BO15" s="33"/>
       <c r="BP15" s="33"/>
-      <c r="BQ15" s="34"/>
-      <c r="BR15" s="35"/>
+      <c r="BQ15" s="35"/>
+      <c r="BR15" s="34"/>
       <c r="BS15" s="33"/>
       <c r="BT15" s="33"/>
       <c r="BU15" s="33"/>
       <c r="BV15" s="33"/>
       <c r="BW15" s="33"/>
-      <c r="BX15" s="34"/>
-      <c r="BY15" s="35"/>
+      <c r="BX15" s="35"/>
+      <c r="BY15" s="34"/>
       <c r="BZ15" s="33"/>
       <c r="CA15" s="33"/>
       <c r="CB15" s="33"/>
       <c r="CC15" s="33"/>
       <c r="CD15" s="33"/>
-      <c r="CE15" s="34"/>
-      <c r="CF15" s="35"/>
+      <c r="CE15" s="35"/>
+      <c r="CF15" s="34"/>
       <c r="CG15" s="33"/>
       <c r="CH15" s="33"/>
       <c r="CI15" s="33"/>
       <c r="CJ15" s="33"/>
       <c r="CK15" s="33"/>
-      <c r="CL15" s="34"/>
-      <c r="CM15" s="35"/>
+      <c r="CL15" s="35"/>
+      <c r="CM15" s="34"/>
       <c r="CN15" s="33"/>
       <c r="CO15" s="33"/>
       <c r="CP15" s="33"/>
       <c r="CQ15" s="33"/>
       <c r="CR15" s="33"/>
-      <c r="CS15" s="34"/>
-      <c r="CT15" s="35"/>
+      <c r="CS15" s="35"/>
+      <c r="CT15" s="34"/>
       <c r="CU15" s="33"/>
       <c r="CV15" s="33"/>
     </row>
@@ -3515,14 +3537,14 @@
       <c r="F16" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G16" s="35"/>
+      <c r="G16" s="34"/>
       <c r="H16" s="33"/>
       <c r="I16" s="33"/>
       <c r="J16" s="33"/>
       <c r="K16" s="33"/>
       <c r="L16" s="33"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="34"/>
       <c r="O16" s="33"/>
       <c r="P16" s="33"/>
       <c r="Q16" s="33"/>
@@ -3551,78 +3573,80 @@
       <c r="Z16" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AA16" s="34"/>
-      <c r="AB16" s="35"/>
+      <c r="AA16" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB16" s="34"/>
       <c r="AC16" s="33"/>
       <c r="AD16" s="33"/>
       <c r="AE16" s="33"/>
       <c r="AF16" s="33"/>
       <c r="AG16" s="33"/>
-      <c r="AH16" s="34"/>
-      <c r="AI16" s="35"/>
+      <c r="AH16" s="35"/>
+      <c r="AI16" s="34"/>
       <c r="AJ16" s="33"/>
       <c r="AK16" s="33"/>
       <c r="AL16" s="33"/>
       <c r="AM16" s="33"/>
       <c r="AN16" s="33"/>
-      <c r="AO16" s="34"/>
-      <c r="AP16" s="35"/>
+      <c r="AO16" s="35"/>
+      <c r="AP16" s="34"/>
       <c r="AQ16" s="33"/>
       <c r="AR16" s="33"/>
       <c r="AS16" s="33"/>
       <c r="AT16" s="33"/>
       <c r="AU16" s="33"/>
-      <c r="AV16" s="34"/>
-      <c r="AW16" s="35"/>
+      <c r="AV16" s="35"/>
+      <c r="AW16" s="34"/>
       <c r="AX16" s="33"/>
       <c r="AY16" s="33"/>
       <c r="AZ16" s="33"/>
       <c r="BA16" s="33"/>
       <c r="BB16" s="33"/>
-      <c r="BC16" s="34"/>
-      <c r="BD16" s="35"/>
+      <c r="BC16" s="35"/>
+      <c r="BD16" s="34"/>
       <c r="BE16" s="33"/>
       <c r="BF16" s="33"/>
       <c r="BG16" s="33"/>
       <c r="BH16" s="33"/>
       <c r="BI16" s="33"/>
-      <c r="BJ16" s="34"/>
-      <c r="BK16" s="35"/>
+      <c r="BJ16" s="35"/>
+      <c r="BK16" s="34"/>
       <c r="BL16" s="33"/>
       <c r="BM16" s="33"/>
       <c r="BN16" s="33"/>
       <c r="BO16" s="33"/>
       <c r="BP16" s="33"/>
-      <c r="BQ16" s="34"/>
-      <c r="BR16" s="35"/>
+      <c r="BQ16" s="35"/>
+      <c r="BR16" s="34"/>
       <c r="BS16" s="33"/>
       <c r="BT16" s="33"/>
       <c r="BU16" s="33"/>
       <c r="BV16" s="33"/>
       <c r="BW16" s="33"/>
-      <c r="BX16" s="34"/>
-      <c r="BY16" s="35"/>
+      <c r="BX16" s="35"/>
+      <c r="BY16" s="34"/>
       <c r="BZ16" s="33"/>
       <c r="CA16" s="33"/>
       <c r="CB16" s="33"/>
       <c r="CC16" s="33"/>
       <c r="CD16" s="33"/>
-      <c r="CE16" s="34"/>
-      <c r="CF16" s="35"/>
+      <c r="CE16" s="35"/>
+      <c r="CF16" s="34"/>
       <c r="CG16" s="33"/>
       <c r="CH16" s="33"/>
       <c r="CI16" s="33"/>
       <c r="CJ16" s="33"/>
       <c r="CK16" s="33"/>
-      <c r="CL16" s="34"/>
-      <c r="CM16" s="35"/>
+      <c r="CL16" s="35"/>
+      <c r="CM16" s="34"/>
       <c r="CN16" s="33"/>
       <c r="CO16" s="33"/>
       <c r="CP16" s="33"/>
       <c r="CQ16" s="33"/>
       <c r="CR16" s="33"/>
-      <c r="CS16" s="34"/>
-      <c r="CT16" s="35"/>
+      <c r="CS16" s="35"/>
+      <c r="CT16" s="34"/>
       <c r="CU16" s="33"/>
       <c r="CV16" s="33"/>
     </row>
@@ -3645,14 +3669,14 @@
       <c r="F17" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G17" s="35"/>
+      <c r="G17" s="34"/>
       <c r="H17" s="33"/>
       <c r="I17" s="33"/>
       <c r="J17" s="33"/>
       <c r="K17" s="33"/>
       <c r="L17" s="33"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="34"/>
       <c r="O17" s="33"/>
       <c r="P17" s="33"/>
       <c r="Q17" s="33"/>
@@ -3679,78 +3703,80 @@
       <c r="Z17" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AA17" s="34"/>
-      <c r="AB17" s="35"/>
+      <c r="AA17" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB17" s="34"/>
       <c r="AC17" s="33"/>
       <c r="AD17" s="33"/>
       <c r="AE17" s="33"/>
       <c r="AF17" s="33"/>
       <c r="AG17" s="33"/>
-      <c r="AH17" s="34"/>
-      <c r="AI17" s="35"/>
+      <c r="AH17" s="35"/>
+      <c r="AI17" s="34"/>
       <c r="AJ17" s="33"/>
       <c r="AK17" s="33"/>
       <c r="AL17" s="33"/>
       <c r="AM17" s="33"/>
       <c r="AN17" s="33"/>
-      <c r="AO17" s="34"/>
-      <c r="AP17" s="35"/>
+      <c r="AO17" s="35"/>
+      <c r="AP17" s="34"/>
       <c r="AQ17" s="33"/>
       <c r="AR17" s="33"/>
       <c r="AS17" s="33"/>
       <c r="AT17" s="33"/>
       <c r="AU17" s="33"/>
-      <c r="AV17" s="34"/>
-      <c r="AW17" s="35"/>
+      <c r="AV17" s="35"/>
+      <c r="AW17" s="34"/>
       <c r="AX17" s="33"/>
       <c r="AY17" s="33"/>
       <c r="AZ17" s="33"/>
       <c r="BA17" s="33"/>
       <c r="BB17" s="33"/>
-      <c r="BC17" s="34"/>
-      <c r="BD17" s="35"/>
+      <c r="BC17" s="35"/>
+      <c r="BD17" s="34"/>
       <c r="BE17" s="33"/>
       <c r="BF17" s="33"/>
       <c r="BG17" s="33"/>
       <c r="BH17" s="33"/>
       <c r="BI17" s="33"/>
-      <c r="BJ17" s="34"/>
-      <c r="BK17" s="35"/>
+      <c r="BJ17" s="35"/>
+      <c r="BK17" s="34"/>
       <c r="BL17" s="33"/>
       <c r="BM17" s="33"/>
       <c r="BN17" s="33"/>
       <c r="BO17" s="33"/>
       <c r="BP17" s="33"/>
-      <c r="BQ17" s="34"/>
-      <c r="BR17" s="35"/>
+      <c r="BQ17" s="35"/>
+      <c r="BR17" s="34"/>
       <c r="BS17" s="33"/>
       <c r="BT17" s="33"/>
       <c r="BU17" s="33"/>
       <c r="BV17" s="33"/>
       <c r="BW17" s="33"/>
-      <c r="BX17" s="34"/>
-      <c r="BY17" s="35"/>
+      <c r="BX17" s="35"/>
+      <c r="BY17" s="34"/>
       <c r="BZ17" s="33"/>
       <c r="CA17" s="33"/>
       <c r="CB17" s="33"/>
       <c r="CC17" s="33"/>
       <c r="CD17" s="33"/>
-      <c r="CE17" s="34"/>
-      <c r="CF17" s="35"/>
+      <c r="CE17" s="35"/>
+      <c r="CF17" s="34"/>
       <c r="CG17" s="33"/>
       <c r="CH17" s="33"/>
       <c r="CI17" s="33"/>
       <c r="CJ17" s="33"/>
       <c r="CK17" s="33"/>
-      <c r="CL17" s="34"/>
-      <c r="CM17" s="35"/>
+      <c r="CL17" s="35"/>
+      <c r="CM17" s="34"/>
       <c r="CN17" s="33"/>
       <c r="CO17" s="33"/>
       <c r="CP17" s="33"/>
       <c r="CQ17" s="33"/>
       <c r="CR17" s="33"/>
-      <c r="CS17" s="34"/>
-      <c r="CT17" s="35"/>
+      <c r="CS17" s="35"/>
+      <c r="CT17" s="34"/>
       <c r="CU17" s="33"/>
       <c r="CV17" s="33"/>
     </row>
@@ -3773,20 +3799,20 @@
       <c r="F18" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G18" s="35"/>
+      <c r="G18" s="34"/>
       <c r="H18" s="33"/>
       <c r="I18" s="33"/>
       <c r="J18" s="33"/>
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="34"/>
       <c r="O18" s="33"/>
       <c r="P18" s="33"/>
       <c r="Q18" s="33"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
-      <c r="T18" s="34"/>
+      <c r="T18" s="35"/>
       <c r="U18" s="33" t="s">
         <v>173</v>
       </c>
@@ -3805,78 +3831,80 @@
       <c r="Z18" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AA18" s="34"/>
-      <c r="AB18" s="35"/>
+      <c r="AA18" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB18" s="34"/>
       <c r="AC18" s="33"/>
       <c r="AD18" s="33"/>
       <c r="AE18" s="33"/>
       <c r="AF18" s="33"/>
       <c r="AG18" s="33"/>
-      <c r="AH18" s="34"/>
-      <c r="AI18" s="35"/>
+      <c r="AH18" s="35"/>
+      <c r="AI18" s="34"/>
       <c r="AJ18" s="33"/>
       <c r="AK18" s="33"/>
       <c r="AL18" s="33"/>
       <c r="AM18" s="33"/>
       <c r="AN18" s="33"/>
-      <c r="AO18" s="34"/>
-      <c r="AP18" s="35"/>
+      <c r="AO18" s="35"/>
+      <c r="AP18" s="34"/>
       <c r="AQ18" s="33"/>
       <c r="AR18" s="33"/>
       <c r="AS18" s="33"/>
       <c r="AT18" s="33"/>
       <c r="AU18" s="33"/>
-      <c r="AV18" s="34"/>
-      <c r="AW18" s="35"/>
+      <c r="AV18" s="35"/>
+      <c r="AW18" s="34"/>
       <c r="AX18" s="33"/>
       <c r="AY18" s="33"/>
       <c r="AZ18" s="33"/>
       <c r="BA18" s="33"/>
       <c r="BB18" s="33"/>
-      <c r="BC18" s="34"/>
-      <c r="BD18" s="35"/>
+      <c r="BC18" s="35"/>
+      <c r="BD18" s="34"/>
       <c r="BE18" s="33"/>
       <c r="BF18" s="33"/>
       <c r="BG18" s="33"/>
       <c r="BH18" s="33"/>
       <c r="BI18" s="33"/>
-      <c r="BJ18" s="34"/>
-      <c r="BK18" s="35"/>
+      <c r="BJ18" s="35"/>
+      <c r="BK18" s="34"/>
       <c r="BL18" s="33"/>
       <c r="BM18" s="33"/>
       <c r="BN18" s="33"/>
       <c r="BO18" s="33"/>
       <c r="BP18" s="33"/>
-      <c r="BQ18" s="34"/>
-      <c r="BR18" s="35"/>
+      <c r="BQ18" s="35"/>
+      <c r="BR18" s="34"/>
       <c r="BS18" s="33"/>
       <c r="BT18" s="33"/>
       <c r="BU18" s="33"/>
       <c r="BV18" s="33"/>
       <c r="BW18" s="33"/>
-      <c r="BX18" s="34"/>
-      <c r="BY18" s="35"/>
+      <c r="BX18" s="35"/>
+      <c r="BY18" s="34"/>
       <c r="BZ18" s="33"/>
       <c r="CA18" s="33"/>
       <c r="CB18" s="33"/>
       <c r="CC18" s="33"/>
       <c r="CD18" s="33"/>
-      <c r="CE18" s="34"/>
-      <c r="CF18" s="35"/>
+      <c r="CE18" s="35"/>
+      <c r="CF18" s="34"/>
       <c r="CG18" s="33"/>
       <c r="CH18" s="33"/>
       <c r="CI18" s="33"/>
       <c r="CJ18" s="33"/>
       <c r="CK18" s="33"/>
-      <c r="CL18" s="34"/>
-      <c r="CM18" s="35"/>
+      <c r="CL18" s="35"/>
+      <c r="CM18" s="34"/>
       <c r="CN18" s="33"/>
       <c r="CO18" s="33"/>
       <c r="CP18" s="33"/>
       <c r="CQ18" s="33"/>
       <c r="CR18" s="33"/>
-      <c r="CS18" s="34"/>
-      <c r="CT18" s="35"/>
+      <c r="CS18" s="35"/>
+      <c r="CT18" s="34"/>
       <c r="CU18" s="33"/>
       <c r="CV18" s="33"/>
     </row>
@@ -3899,21 +3927,21 @@
       <c r="F19" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G19" s="35"/>
+      <c r="G19" s="34"/>
       <c r="H19" s="33"/>
       <c r="I19" s="33"/>
       <c r="J19" s="33"/>
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="34"/>
       <c r="O19" s="33"/>
       <c r="P19" s="33"/>
       <c r="Q19" s="33"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
-      <c r="T19" s="34"/>
-      <c r="U19" s="35"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="34"/>
       <c r="V19" s="33" t="s">
         <v>173</v>
       </c>
@@ -3929,78 +3957,80 @@
       <c r="Z19" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AA19" s="34"/>
-      <c r="AB19" s="35"/>
+      <c r="AA19" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB19" s="34"/>
       <c r="AC19" s="33"/>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
       <c r="AF19" s="33"/>
       <c r="AG19" s="33"/>
-      <c r="AH19" s="34"/>
-      <c r="AI19" s="35"/>
+      <c r="AH19" s="35"/>
+      <c r="AI19" s="34"/>
       <c r="AJ19" s="33"/>
       <c r="AK19" s="33"/>
       <c r="AL19" s="33"/>
       <c r="AM19" s="33"/>
       <c r="AN19" s="33"/>
-      <c r="AO19" s="34"/>
-      <c r="AP19" s="35"/>
+      <c r="AO19" s="35"/>
+      <c r="AP19" s="34"/>
       <c r="AQ19" s="33"/>
       <c r="AR19" s="33"/>
       <c r="AS19" s="33"/>
       <c r="AT19" s="33"/>
       <c r="AU19" s="33"/>
-      <c r="AV19" s="34"/>
-      <c r="AW19" s="35"/>
+      <c r="AV19" s="35"/>
+      <c r="AW19" s="34"/>
       <c r="AX19" s="33"/>
       <c r="AY19" s="33"/>
       <c r="AZ19" s="33"/>
       <c r="BA19" s="33"/>
       <c r="BB19" s="33"/>
-      <c r="BC19" s="34"/>
-      <c r="BD19" s="35"/>
+      <c r="BC19" s="35"/>
+      <c r="BD19" s="34"/>
       <c r="BE19" s="33"/>
       <c r="BF19" s="33"/>
       <c r="BG19" s="33"/>
       <c r="BH19" s="33"/>
       <c r="BI19" s="33"/>
-      <c r="BJ19" s="34"/>
-      <c r="BK19" s="35"/>
+      <c r="BJ19" s="35"/>
+      <c r="BK19" s="34"/>
       <c r="BL19" s="33"/>
       <c r="BM19" s="33"/>
       <c r="BN19" s="33"/>
       <c r="BO19" s="33"/>
       <c r="BP19" s="33"/>
-      <c r="BQ19" s="34"/>
-      <c r="BR19" s="35"/>
+      <c r="BQ19" s="35"/>
+      <c r="BR19" s="34"/>
       <c r="BS19" s="33"/>
       <c r="BT19" s="33"/>
       <c r="BU19" s="33"/>
       <c r="BV19" s="33"/>
       <c r="BW19" s="33"/>
-      <c r="BX19" s="34"/>
-      <c r="BY19" s="35"/>
+      <c r="BX19" s="35"/>
+      <c r="BY19" s="34"/>
       <c r="BZ19" s="33"/>
       <c r="CA19" s="33"/>
       <c r="CB19" s="33"/>
       <c r="CC19" s="33"/>
       <c r="CD19" s="33"/>
-      <c r="CE19" s="34"/>
-      <c r="CF19" s="35"/>
+      <c r="CE19" s="35"/>
+      <c r="CF19" s="34"/>
       <c r="CG19" s="33"/>
       <c r="CH19" s="33"/>
       <c r="CI19" s="33"/>
       <c r="CJ19" s="33"/>
       <c r="CK19" s="33"/>
-      <c r="CL19" s="34"/>
-      <c r="CM19" s="35"/>
+      <c r="CL19" s="35"/>
+      <c r="CM19" s="34"/>
       <c r="CN19" s="33"/>
       <c r="CO19" s="33"/>
       <c r="CP19" s="33"/>
       <c r="CQ19" s="33"/>
       <c r="CR19" s="33"/>
-      <c r="CS19" s="34"/>
-      <c r="CT19" s="35"/>
+      <c r="CS19" s="35"/>
+      <c r="CT19" s="34"/>
       <c r="CU19" s="33"/>
       <c r="CV19" s="33"/>
     </row>
@@ -4023,21 +4053,21 @@
       <c r="F20" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G20" s="35"/>
+      <c r="G20" s="34"/>
       <c r="H20" s="33"/>
       <c r="I20" s="33"/>
       <c r="J20" s="33"/>
       <c r="K20" s="33"/>
       <c r="L20" s="33"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="34"/>
       <c r="O20" s="33"/>
       <c r="P20" s="33"/>
       <c r="Q20" s="33"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
-      <c r="T20" s="34"/>
-      <c r="U20" s="35"/>
+      <c r="T20" s="35"/>
+      <c r="U20" s="34"/>
       <c r="V20" s="33"/>
       <c r="W20" s="33" t="s">
         <v>173</v>
@@ -4051,78 +4081,80 @@
       <c r="Z20" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AA20" s="34"/>
-      <c r="AB20" s="35"/>
+      <c r="AA20" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB20" s="34"/>
       <c r="AC20" s="33"/>
       <c r="AD20" s="33"/>
       <c r="AE20" s="33"/>
       <c r="AF20" s="33"/>
       <c r="AG20" s="33"/>
-      <c r="AH20" s="34"/>
-      <c r="AI20" s="35"/>
+      <c r="AH20" s="35"/>
+      <c r="AI20" s="34"/>
       <c r="AJ20" s="33"/>
       <c r="AK20" s="33"/>
       <c r="AL20" s="33"/>
       <c r="AM20" s="33"/>
       <c r="AN20" s="33"/>
-      <c r="AO20" s="34"/>
-      <c r="AP20" s="35"/>
+      <c r="AO20" s="35"/>
+      <c r="AP20" s="34"/>
       <c r="AQ20" s="33"/>
       <c r="AR20" s="33"/>
       <c r="AS20" s="33"/>
       <c r="AT20" s="33"/>
       <c r="AU20" s="33"/>
-      <c r="AV20" s="34"/>
-      <c r="AW20" s="35"/>
+      <c r="AV20" s="35"/>
+      <c r="AW20" s="34"/>
       <c r="AX20" s="33"/>
       <c r="AY20" s="33"/>
       <c r="AZ20" s="33"/>
       <c r="BA20" s="33"/>
       <c r="BB20" s="33"/>
-      <c r="BC20" s="34"/>
-      <c r="BD20" s="35"/>
+      <c r="BC20" s="35"/>
+      <c r="BD20" s="34"/>
       <c r="BE20" s="33"/>
       <c r="BF20" s="33"/>
       <c r="BG20" s="33"/>
       <c r="BH20" s="33"/>
       <c r="BI20" s="33"/>
-      <c r="BJ20" s="34"/>
-      <c r="BK20" s="35"/>
+      <c r="BJ20" s="35"/>
+      <c r="BK20" s="34"/>
       <c r="BL20" s="33"/>
       <c r="BM20" s="33"/>
       <c r="BN20" s="33"/>
       <c r="BO20" s="33"/>
       <c r="BP20" s="33"/>
-      <c r="BQ20" s="34"/>
-      <c r="BR20" s="35"/>
+      <c r="BQ20" s="35"/>
+      <c r="BR20" s="34"/>
       <c r="BS20" s="33"/>
       <c r="BT20" s="33"/>
       <c r="BU20" s="33"/>
       <c r="BV20" s="33"/>
       <c r="BW20" s="33"/>
-      <c r="BX20" s="34"/>
-      <c r="BY20" s="35"/>
+      <c r="BX20" s="35"/>
+      <c r="BY20" s="34"/>
       <c r="BZ20" s="33"/>
       <c r="CA20" s="33"/>
       <c r="CB20" s="33"/>
       <c r="CC20" s="33"/>
       <c r="CD20" s="33"/>
-      <c r="CE20" s="34"/>
-      <c r="CF20" s="35"/>
+      <c r="CE20" s="35"/>
+      <c r="CF20" s="34"/>
       <c r="CG20" s="33"/>
       <c r="CH20" s="33"/>
       <c r="CI20" s="33"/>
       <c r="CJ20" s="33"/>
       <c r="CK20" s="33"/>
-      <c r="CL20" s="34"/>
-      <c r="CM20" s="35"/>
+      <c r="CL20" s="35"/>
+      <c r="CM20" s="34"/>
       <c r="CN20" s="33"/>
       <c r="CO20" s="33"/>
       <c r="CP20" s="33"/>
       <c r="CQ20" s="33"/>
       <c r="CR20" s="33"/>
-      <c r="CS20" s="34"/>
-      <c r="CT20" s="35"/>
+      <c r="CS20" s="35"/>
+      <c r="CT20" s="34"/>
       <c r="CU20" s="33"/>
       <c r="CV20" s="33"/>
     </row>
@@ -4145,21 +4177,21 @@
       <c r="F21" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G21" s="35"/>
+      <c r="G21" s="34"/>
       <c r="H21" s="33"/>
       <c r="I21" s="33"/>
       <c r="J21" s="33"/>
       <c r="K21" s="33"/>
       <c r="L21" s="33"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="34"/>
       <c r="O21" s="33"/>
       <c r="P21" s="33"/>
       <c r="Q21" s="33"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
-      <c r="T21" s="34"/>
-      <c r="U21" s="35"/>
+      <c r="T21" s="35"/>
+      <c r="U21" s="34"/>
       <c r="V21" s="33"/>
       <c r="W21" s="33"/>
       <c r="X21" s="33" t="s">
@@ -4171,78 +4203,80 @@
       <c r="Z21" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AA21" s="34"/>
-      <c r="AB21" s="35"/>
+      <c r="AA21" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB21" s="34"/>
       <c r="AC21" s="33"/>
       <c r="AD21" s="33"/>
       <c r="AE21" s="33"/>
       <c r="AF21" s="33"/>
       <c r="AG21" s="33"/>
-      <c r="AH21" s="34"/>
-      <c r="AI21" s="35"/>
+      <c r="AH21" s="35"/>
+      <c r="AI21" s="34"/>
       <c r="AJ21" s="33"/>
       <c r="AK21" s="33"/>
       <c r="AL21" s="33"/>
       <c r="AM21" s="33"/>
       <c r="AN21" s="33"/>
-      <c r="AO21" s="34"/>
-      <c r="AP21" s="35"/>
+      <c r="AO21" s="35"/>
+      <c r="AP21" s="34"/>
       <c r="AQ21" s="33"/>
       <c r="AR21" s="33"/>
       <c r="AS21" s="33"/>
       <c r="AT21" s="33"/>
       <c r="AU21" s="33"/>
-      <c r="AV21" s="34"/>
-      <c r="AW21" s="35"/>
+      <c r="AV21" s="35"/>
+      <c r="AW21" s="34"/>
       <c r="AX21" s="33"/>
       <c r="AY21" s="33"/>
       <c r="AZ21" s="33"/>
       <c r="BA21" s="33"/>
       <c r="BB21" s="33"/>
-      <c r="BC21" s="34"/>
-      <c r="BD21" s="35"/>
+      <c r="BC21" s="35"/>
+      <c r="BD21" s="34"/>
       <c r="BE21" s="33"/>
       <c r="BF21" s="33"/>
       <c r="BG21" s="33"/>
       <c r="BH21" s="33"/>
       <c r="BI21" s="33"/>
-      <c r="BJ21" s="34"/>
-      <c r="BK21" s="35"/>
+      <c r="BJ21" s="35"/>
+      <c r="BK21" s="34"/>
       <c r="BL21" s="33"/>
       <c r="BM21" s="33"/>
       <c r="BN21" s="33"/>
       <c r="BO21" s="33"/>
       <c r="BP21" s="33"/>
-      <c r="BQ21" s="34"/>
-      <c r="BR21" s="35"/>
+      <c r="BQ21" s="35"/>
+      <c r="BR21" s="34"/>
       <c r="BS21" s="33"/>
       <c r="BT21" s="33"/>
       <c r="BU21" s="33"/>
       <c r="BV21" s="33"/>
       <c r="BW21" s="33"/>
-      <c r="BX21" s="34"/>
-      <c r="BY21" s="35"/>
+      <c r="BX21" s="35"/>
+      <c r="BY21" s="34"/>
       <c r="BZ21" s="33"/>
       <c r="CA21" s="33"/>
       <c r="CB21" s="33"/>
       <c r="CC21" s="33"/>
       <c r="CD21" s="33"/>
-      <c r="CE21" s="34"/>
-      <c r="CF21" s="35"/>
+      <c r="CE21" s="35"/>
+      <c r="CF21" s="34"/>
       <c r="CG21" s="33"/>
       <c r="CH21" s="33"/>
       <c r="CI21" s="33"/>
       <c r="CJ21" s="33"/>
       <c r="CK21" s="33"/>
-      <c r="CL21" s="34"/>
-      <c r="CM21" s="35"/>
+      <c r="CL21" s="35"/>
+      <c r="CM21" s="34"/>
       <c r="CN21" s="33"/>
       <c r="CO21" s="33"/>
       <c r="CP21" s="33"/>
       <c r="CQ21" s="33"/>
       <c r="CR21" s="33"/>
-      <c r="CS21" s="34"/>
-      <c r="CT21" s="35"/>
+      <c r="CS21" s="35"/>
+      <c r="CT21" s="34"/>
       <c r="CU21" s="33"/>
       <c r="CV21" s="33"/>
     </row>
@@ -4265,21 +4299,21 @@
       <c r="F22" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G22" s="35"/>
+      <c r="G22" s="34"/>
       <c r="H22" s="33"/>
       <c r="I22" s="33"/>
       <c r="J22" s="33"/>
       <c r="K22" s="33"/>
       <c r="L22" s="33"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="34"/>
       <c r="O22" s="33"/>
       <c r="P22" s="33"/>
       <c r="Q22" s="33"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
-      <c r="T22" s="34"/>
-      <c r="U22" s="35"/>
+      <c r="T22" s="35"/>
+      <c r="U22" s="34"/>
       <c r="V22" s="33"/>
       <c r="W22" s="33"/>
       <c r="X22" s="33"/>
@@ -4289,78 +4323,80 @@
       <c r="Z22" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AA22" s="34"/>
-      <c r="AB22" s="35"/>
+      <c r="AA22" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB22" s="34"/>
       <c r="AC22" s="33"/>
       <c r="AD22" s="33"/>
       <c r="AE22" s="33"/>
       <c r="AF22" s="33"/>
       <c r="AG22" s="33"/>
-      <c r="AH22" s="34"/>
-      <c r="AI22" s="35"/>
+      <c r="AH22" s="35"/>
+      <c r="AI22" s="34"/>
       <c r="AJ22" s="33"/>
       <c r="AK22" s="33"/>
       <c r="AL22" s="33"/>
       <c r="AM22" s="33"/>
       <c r="AN22" s="33"/>
-      <c r="AO22" s="34"/>
-      <c r="AP22" s="35"/>
+      <c r="AO22" s="35"/>
+      <c r="AP22" s="34"/>
       <c r="AQ22" s="33"/>
       <c r="AR22" s="33"/>
       <c r="AS22" s="33"/>
       <c r="AT22" s="33"/>
       <c r="AU22" s="33"/>
-      <c r="AV22" s="34"/>
-      <c r="AW22" s="35"/>
+      <c r="AV22" s="35"/>
+      <c r="AW22" s="34"/>
       <c r="AX22" s="33"/>
       <c r="AY22" s="33"/>
       <c r="AZ22" s="33"/>
       <c r="BA22" s="33"/>
       <c r="BB22" s="33"/>
-      <c r="BC22" s="34"/>
-      <c r="BD22" s="35"/>
+      <c r="BC22" s="35"/>
+      <c r="BD22" s="34"/>
       <c r="BE22" s="33"/>
       <c r="BF22" s="33"/>
       <c r="BG22" s="33"/>
       <c r="BH22" s="33"/>
       <c r="BI22" s="33"/>
-      <c r="BJ22" s="34"/>
-      <c r="BK22" s="35"/>
+      <c r="BJ22" s="35"/>
+      <c r="BK22" s="34"/>
       <c r="BL22" s="33"/>
       <c r="BM22" s="33"/>
       <c r="BN22" s="33"/>
       <c r="BO22" s="33"/>
       <c r="BP22" s="33"/>
-      <c r="BQ22" s="34"/>
-      <c r="BR22" s="35"/>
+      <c r="BQ22" s="35"/>
+      <c r="BR22" s="34"/>
       <c r="BS22" s="33"/>
       <c r="BT22" s="33"/>
       <c r="BU22" s="33"/>
       <c r="BV22" s="33"/>
       <c r="BW22" s="33"/>
-      <c r="BX22" s="34"/>
-      <c r="BY22" s="35"/>
+      <c r="BX22" s="35"/>
+      <c r="BY22" s="34"/>
       <c r="BZ22" s="33"/>
       <c r="CA22" s="33"/>
       <c r="CB22" s="33"/>
       <c r="CC22" s="33"/>
       <c r="CD22" s="33"/>
-      <c r="CE22" s="34"/>
-      <c r="CF22" s="35"/>
+      <c r="CE22" s="35"/>
+      <c r="CF22" s="34"/>
       <c r="CG22" s="33"/>
       <c r="CH22" s="33"/>
       <c r="CI22" s="33"/>
       <c r="CJ22" s="33"/>
       <c r="CK22" s="33"/>
-      <c r="CL22" s="34"/>
-      <c r="CM22" s="35"/>
+      <c r="CL22" s="35"/>
+      <c r="CM22" s="34"/>
       <c r="CN22" s="33"/>
       <c r="CO22" s="33"/>
       <c r="CP22" s="33"/>
       <c r="CQ22" s="33"/>
       <c r="CR22" s="33"/>
-      <c r="CS22" s="34"/>
-      <c r="CT22" s="35"/>
+      <c r="CS22" s="35"/>
+      <c r="CT22" s="34"/>
       <c r="CU22" s="33"/>
       <c r="CV22" s="33"/>
     </row>
@@ -4383,21 +4419,21 @@
       <c r="F23" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G23" s="35"/>
+      <c r="G23" s="34"/>
       <c r="H23" s="33"/>
       <c r="I23" s="33"/>
       <c r="J23" s="33"/>
       <c r="K23" s="33"/>
       <c r="L23" s="33"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="34"/>
       <c r="O23" s="33"/>
       <c r="P23" s="33"/>
       <c r="Q23" s="33"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
-      <c r="T23" s="34"/>
-      <c r="U23" s="35"/>
+      <c r="T23" s="35"/>
+      <c r="U23" s="34"/>
       <c r="V23" s="33"/>
       <c r="W23" s="33"/>
       <c r="X23" s="33"/>
@@ -4405,78 +4441,80 @@
       <c r="Z23" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="AA23" s="34"/>
-      <c r="AB23" s="35"/>
+      <c r="AA23" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB23" s="34"/>
       <c r="AC23" s="33"/>
       <c r="AD23" s="33"/>
       <c r="AE23" s="33"/>
       <c r="AF23" s="33"/>
       <c r="AG23" s="33"/>
-      <c r="AH23" s="34"/>
-      <c r="AI23" s="35"/>
+      <c r="AH23" s="35"/>
+      <c r="AI23" s="34"/>
       <c r="AJ23" s="33"/>
       <c r="AK23" s="33"/>
       <c r="AL23" s="33"/>
       <c r="AM23" s="33"/>
       <c r="AN23" s="33"/>
-      <c r="AO23" s="34"/>
-      <c r="AP23" s="35"/>
+      <c r="AO23" s="35"/>
+      <c r="AP23" s="34"/>
       <c r="AQ23" s="33"/>
       <c r="AR23" s="33"/>
       <c r="AS23" s="33"/>
       <c r="AT23" s="33"/>
       <c r="AU23" s="33"/>
-      <c r="AV23" s="34"/>
-      <c r="AW23" s="35"/>
+      <c r="AV23" s="35"/>
+      <c r="AW23" s="34"/>
       <c r="AX23" s="33"/>
       <c r="AY23" s="33"/>
       <c r="AZ23" s="33"/>
       <c r="BA23" s="33"/>
       <c r="BB23" s="33"/>
-      <c r="BC23" s="34"/>
-      <c r="BD23" s="35"/>
+      <c r="BC23" s="35"/>
+      <c r="BD23" s="34"/>
       <c r="BE23" s="33"/>
       <c r="BF23" s="33"/>
       <c r="BG23" s="33"/>
       <c r="BH23" s="33"/>
       <c r="BI23" s="33"/>
-      <c r="BJ23" s="34"/>
-      <c r="BK23" s="35"/>
+      <c r="BJ23" s="35"/>
+      <c r="BK23" s="34"/>
       <c r="BL23" s="33"/>
       <c r="BM23" s="33"/>
       <c r="BN23" s="33"/>
       <c r="BO23" s="33"/>
       <c r="BP23" s="33"/>
-      <c r="BQ23" s="34"/>
-      <c r="BR23" s="35"/>
+      <c r="BQ23" s="35"/>
+      <c r="BR23" s="34"/>
       <c r="BS23" s="33"/>
       <c r="BT23" s="33"/>
       <c r="BU23" s="33"/>
       <c r="BV23" s="33"/>
       <c r="BW23" s="33"/>
-      <c r="BX23" s="34"/>
-      <c r="BY23" s="35"/>
+      <c r="BX23" s="35"/>
+      <c r="BY23" s="34"/>
       <c r="BZ23" s="33"/>
       <c r="CA23" s="33"/>
       <c r="CB23" s="33"/>
       <c r="CC23" s="33"/>
       <c r="CD23" s="33"/>
-      <c r="CE23" s="34"/>
-      <c r="CF23" s="35"/>
+      <c r="CE23" s="35"/>
+      <c r="CF23" s="34"/>
       <c r="CG23" s="33"/>
       <c r="CH23" s="33"/>
       <c r="CI23" s="33"/>
       <c r="CJ23" s="33"/>
       <c r="CK23" s="33"/>
-      <c r="CL23" s="34"/>
-      <c r="CM23" s="35"/>
+      <c r="CL23" s="35"/>
+      <c r="CM23" s="34"/>
       <c r="CN23" s="33"/>
       <c r="CO23" s="33"/>
       <c r="CP23" s="33"/>
       <c r="CQ23" s="33"/>
       <c r="CR23" s="33"/>
-      <c r="CS23" s="34"/>
-      <c r="CT23" s="35"/>
+      <c r="CS23" s="35"/>
+      <c r="CT23" s="34"/>
       <c r="CU23" s="33"/>
       <c r="CV23" s="33"/>
     </row>
@@ -4499,98 +4537,100 @@
       <c r="F24" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G24" s="35"/>
+      <c r="G24" s="34"/>
       <c r="H24" s="33"/>
       <c r="I24" s="33"/>
       <c r="J24" s="33"/>
       <c r="K24" s="33"/>
       <c r="L24" s="33"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="34"/>
       <c r="O24" s="33"/>
       <c r="P24" s="33"/>
       <c r="Q24" s="33"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
-      <c r="T24" s="34"/>
-      <c r="U24" s="35"/>
+      <c r="T24" s="35"/>
+      <c r="U24" s="34"/>
       <c r="V24" s="33"/>
       <c r="W24" s="33"/>
       <c r="X24" s="33"/>
       <c r="Y24" s="33"/>
       <c r="Z24" s="33"/>
-      <c r="AA24" s="34"/>
-      <c r="AB24" s="35"/>
+      <c r="AA24" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB24" s="34"/>
       <c r="AC24" s="33"/>
       <c r="AD24" s="33"/>
       <c r="AE24" s="33"/>
       <c r="AF24" s="33"/>
       <c r="AG24" s="33"/>
-      <c r="AH24" s="34"/>
-      <c r="AI24" s="35"/>
+      <c r="AH24" s="35"/>
+      <c r="AI24" s="34"/>
       <c r="AJ24" s="33"/>
       <c r="AK24" s="33"/>
       <c r="AL24" s="33"/>
       <c r="AM24" s="33"/>
       <c r="AN24" s="33"/>
-      <c r="AO24" s="34"/>
-      <c r="AP24" s="35"/>
+      <c r="AO24" s="35"/>
+      <c r="AP24" s="34"/>
       <c r="AQ24" s="33"/>
       <c r="AR24" s="33"/>
       <c r="AS24" s="33"/>
       <c r="AT24" s="33"/>
       <c r="AU24" s="33"/>
-      <c r="AV24" s="34"/>
-      <c r="AW24" s="35"/>
+      <c r="AV24" s="35"/>
+      <c r="AW24" s="34"/>
       <c r="AX24" s="33"/>
       <c r="AY24" s="33"/>
       <c r="AZ24" s="33"/>
       <c r="BA24" s="33"/>
       <c r="BB24" s="33"/>
-      <c r="BC24" s="34"/>
-      <c r="BD24" s="35"/>
+      <c r="BC24" s="35"/>
+      <c r="BD24" s="34"/>
       <c r="BE24" s="33"/>
       <c r="BF24" s="33"/>
       <c r="BG24" s="33"/>
       <c r="BH24" s="33"/>
       <c r="BI24" s="33"/>
-      <c r="BJ24" s="34"/>
-      <c r="BK24" s="35"/>
+      <c r="BJ24" s="35"/>
+      <c r="BK24" s="34"/>
       <c r="BL24" s="33"/>
       <c r="BM24" s="33"/>
       <c r="BN24" s="33"/>
       <c r="BO24" s="33"/>
       <c r="BP24" s="33"/>
-      <c r="BQ24" s="34"/>
-      <c r="BR24" s="35"/>
+      <c r="BQ24" s="35"/>
+      <c r="BR24" s="34"/>
       <c r="BS24" s="33"/>
       <c r="BT24" s="33"/>
       <c r="BU24" s="33"/>
       <c r="BV24" s="33"/>
       <c r="BW24" s="33"/>
-      <c r="BX24" s="34"/>
-      <c r="BY24" s="35"/>
+      <c r="BX24" s="35"/>
+      <c r="BY24" s="34"/>
       <c r="BZ24" s="33"/>
       <c r="CA24" s="33"/>
       <c r="CB24" s="33"/>
       <c r="CC24" s="33"/>
       <c r="CD24" s="33"/>
-      <c r="CE24" s="34"/>
-      <c r="CF24" s="35"/>
+      <c r="CE24" s="35"/>
+      <c r="CF24" s="34"/>
       <c r="CG24" s="33"/>
       <c r="CH24" s="33"/>
       <c r="CI24" s="33"/>
       <c r="CJ24" s="33"/>
       <c r="CK24" s="33"/>
-      <c r="CL24" s="34"/>
-      <c r="CM24" s="35"/>
+      <c r="CL24" s="35"/>
+      <c r="CM24" s="34"/>
       <c r="CN24" s="33"/>
       <c r="CO24" s="33"/>
       <c r="CP24" s="33"/>
       <c r="CQ24" s="33"/>
       <c r="CR24" s="33"/>
-      <c r="CS24" s="34"/>
-      <c r="CT24" s="35"/>
+      <c r="CS24" s="35"/>
+      <c r="CT24" s="34"/>
       <c r="CU24" s="33"/>
       <c r="CV24" s="33"/>
     </row>
